--- a/data/diagnostico_coincidencias.xlsx
+++ b/data/diagnostico_coincidencias.xlsx
@@ -621,7 +621,7 @@
         <v>10</v>
       </c>
       <c r="H3" t="n">
-        <v>59.44</v>
+        <v>73.33</v>
       </c>
     </row>
     <row r="4">
@@ -685,7 +685,7 @@
         <v>8</v>
       </c>
       <c r="H5" t="n">
-        <v>69.45</v>
+        <v>73.61</v>
       </c>
     </row>
     <row r="6">
@@ -781,7 +781,7 @@
         <v>9</v>
       </c>
       <c r="H8" t="n">
-        <v>73.87</v>
+        <v>74.28</v>
       </c>
     </row>
     <row r="9">
@@ -1037,7 +1037,7 @@
         <v>12</v>
       </c>
       <c r="H16" t="n">
-        <v>26.39</v>
+        <v>32.87</v>
       </c>
     </row>
     <row r="17">
@@ -1069,7 +1069,7 @@
         <v>41</v>
       </c>
       <c r="H17" t="n">
-        <v>20.51</v>
+        <v>25.88</v>
       </c>
     </row>
     <row r="18">
@@ -1133,7 +1133,7 @@
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>71.59999999999999</v>
+        <v>72.53</v>
       </c>
     </row>
     <row r="20">
@@ -1165,7 +1165,7 @@
         <v>25</v>
       </c>
       <c r="H20" t="n">
-        <v>21.48</v>
+        <v>23.85</v>
       </c>
     </row>
     <row r="21">
@@ -1197,7 +1197,7 @@
         <v>15</v>
       </c>
       <c r="H21" t="n">
-        <v>18.52</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22">
@@ -1293,7 +1293,7 @@
         <v>23</v>
       </c>
       <c r="H24" t="n">
-        <v>25.12</v>
+        <v>27.62</v>
       </c>
     </row>
     <row r="25">
@@ -1389,7 +1389,7 @@
         <v>9</v>
       </c>
       <c r="H27" t="n">
-        <v>87.04000000000001</v>
+        <v>88.27</v>
       </c>
     </row>
     <row r="28">
@@ -1421,7 +1421,7 @@
         <v>29</v>
       </c>
       <c r="H28" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
     </row>
     <row r="29">
@@ -1485,7 +1485,7 @@
         <v>9</v>
       </c>
       <c r="H30" t="n">
-        <v>80.25</v>
+        <v>83.33</v>
       </c>
     </row>
     <row r="31">
@@ -1517,7 +1517,7 @@
         <v>23</v>
       </c>
       <c r="H31" t="n">
-        <v>18.52</v>
+        <v>23.35</v>
       </c>
     </row>
     <row r="32">
@@ -1549,7 +1549,7 @@
         <v>12</v>
       </c>
       <c r="H32" t="n">
-        <v>69.45</v>
+        <v>71.3</v>
       </c>
     </row>
     <row r="33">
@@ -1677,7 +1677,7 @@
         <v>13</v>
       </c>
       <c r="H36" t="n">
-        <v>31.48</v>
+        <v>24.07</v>
       </c>
     </row>
     <row r="37">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -2097,14 +2097,14 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P3" t="n">
         <v>100</v>
       </c>
       <c r="Q3" t="n">
-        <v>59.44</v>
+        <v>73.33</v>
       </c>
       <c r="R3" t="n">
         <v>10</v>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -2263,14 +2263,14 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P5" t="n">
         <v>100</v>
       </c>
       <c r="Q5" t="n">
-        <v>69.45</v>
+        <v>73.61</v>
       </c>
       <c r="R5" t="n">
         <v>8</v>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -2713,14 +2713,14 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P11" t="n">
         <v>100</v>
       </c>
       <c r="Q11" t="n">
-        <v>59.44</v>
+        <v>73.33</v>
       </c>
       <c r="R11" t="n">
         <v>10</v>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -2879,14 +2879,14 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P13" t="n">
         <v>100</v>
       </c>
       <c r="Q13" t="n">
-        <v>69.45</v>
+        <v>73.61</v>
       </c>
       <c r="R13" t="n">
         <v>8</v>
@@ -3328,7 +3328,7 @@
         <v>20</v>
       </c>
       <c r="Q19" t="n">
-        <v>59.44</v>
+        <v>73.33</v>
       </c>
       <c r="R19" t="n">
         <v>2</v>
@@ -3486,7 +3486,7 @@
         <v>25</v>
       </c>
       <c r="Q21" t="n">
-        <v>69.45</v>
+        <v>73.61</v>
       </c>
       <c r="R21" t="n">
         <v>2</v>
@@ -3928,7 +3928,7 @@
         <v>20</v>
       </c>
       <c r="Q27" t="n">
-        <v>59.44</v>
+        <v>73.33</v>
       </c>
       <c r="R27" t="n">
         <v>2</v>
@@ -4086,7 +4086,7 @@
         <v>25</v>
       </c>
       <c r="Q29" t="n">
-        <v>69.45</v>
+        <v>73.61</v>
       </c>
       <c r="R29" t="n">
         <v>2</v>
@@ -4525,14 +4525,14 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P35" t="n">
         <v>100</v>
       </c>
       <c r="Q35" t="n">
-        <v>59.44</v>
+        <v>73.33</v>
       </c>
       <c r="R35" t="n">
         <v>10</v>
@@ -4687,14 +4687,14 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P37" t="n">
         <v>100</v>
       </c>
       <c r="Q37" t="n">
-        <v>69.45</v>
+        <v>73.61</v>
       </c>
       <c r="R37" t="n">
         <v>8</v>
@@ -5133,14 +5133,14 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P43" t="n">
         <v>100</v>
       </c>
       <c r="Q43" t="n">
-        <v>59.44</v>
+        <v>73.33</v>
       </c>
       <c r="R43" t="n">
         <v>10</v>
@@ -5295,14 +5295,14 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P45" t="n">
         <v>100</v>
       </c>
       <c r="Q45" t="n">
-        <v>69.45</v>
+        <v>73.61</v>
       </c>
       <c r="R45" t="n">
         <v>8</v>
@@ -5739,15 +5739,19 @@
           <t>programada</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
       <c r="P51" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="Q51" t="n">
-        <v>59.44</v>
+        <v>73.33</v>
       </c>
       <c r="R51" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5899,14 +5903,14 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P53" t="n">
         <v>100</v>
       </c>
       <c r="Q53" t="n">
-        <v>69.45</v>
+        <v>73.61</v>
       </c>
       <c r="R53" t="n">
         <v>8</v>
@@ -6343,15 +6347,19 @@
           <t>programada</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr"/>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
       <c r="P59" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="Q59" t="n">
-        <v>59.44</v>
+        <v>73.33</v>
       </c>
       <c r="R59" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6503,14 +6511,14 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P61" t="n">
         <v>100</v>
       </c>
       <c r="Q61" t="n">
-        <v>69.45</v>
+        <v>73.61</v>
       </c>
       <c r="R61" t="n">
         <v>8</v>
@@ -6947,15 +6955,19 @@
           <t>programada</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr"/>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q67" t="n">
-        <v>59.44</v>
+        <v>73.33</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7105,15 +7117,19 @@
           <t>programada</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr"/>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
       <c r="P69" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="Q69" t="n">
-        <v>69.45</v>
+        <v>73.61</v>
       </c>
       <c r="R69" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="S69" t="n">
         <v>8</v>
@@ -7547,15 +7563,19 @@
           <t>programada</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr"/>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q75" t="n">
-        <v>59.44</v>
+        <v>73.33</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7705,15 +7725,19 @@
           <t>programada</t>
         </is>
       </c>
-      <c r="O77" t="inlineStr"/>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
       <c r="P77" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="Q77" t="n">
-        <v>69.45</v>
+        <v>73.61</v>
       </c>
       <c r="R77" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="S77" t="n">
         <v>8</v>
@@ -8147,15 +8171,19 @@
           <t>programada</t>
         </is>
       </c>
-      <c r="O83" t="inlineStr"/>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q83" t="n">
-        <v>59.44</v>
+        <v>73.33</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8305,15 +8333,19 @@
           <t>programada</t>
         </is>
       </c>
-      <c r="O85" t="inlineStr"/>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
       <c r="P85" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="Q85" t="n">
-        <v>69.45</v>
+        <v>73.61</v>
       </c>
       <c r="R85" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="S85" t="n">
         <v>8</v>
@@ -8747,15 +8779,19 @@
           <t>programada</t>
         </is>
       </c>
-      <c r="O91" t="inlineStr"/>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q91" t="n">
-        <v>59.44</v>
+        <v>73.33</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -8905,15 +8941,19 @@
           <t>programada</t>
         </is>
       </c>
-      <c r="O93" t="inlineStr"/>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
       <c r="P93" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="Q93" t="n">
-        <v>69.45</v>
+        <v>73.61</v>
       </c>
       <c r="R93" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="S93" t="n">
         <v>8</v>
@@ -9352,7 +9392,7 @@
         <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>59.44</v>
+        <v>73.33</v>
       </c>
       <c r="R99" t="n">
         <v>0</v>
@@ -9510,7 +9550,7 @@
         <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>69.45</v>
+        <v>73.61</v>
       </c>
       <c r="R101" t="n">
         <v>0</v>
@@ -9952,7 +9992,7 @@
         <v>0</v>
       </c>
       <c r="Q107" t="n">
-        <v>59.44</v>
+        <v>73.33</v>
       </c>
       <c r="R107" t="n">
         <v>0</v>
@@ -10110,7 +10150,7 @@
         <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>69.45</v>
+        <v>73.61</v>
       </c>
       <c r="R109" t="n">
         <v>0</v>
@@ -10552,7 +10592,7 @@
         <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>59.44</v>
+        <v>73.33</v>
       </c>
       <c r="R115" t="n">
         <v>0</v>
@@ -10710,7 +10750,7 @@
         <v>0</v>
       </c>
       <c r="Q117" t="n">
-        <v>69.45</v>
+        <v>73.61</v>
       </c>
       <c r="R117" t="n">
         <v>0</v>
@@ -11152,7 +11192,7 @@
         <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>59.44</v>
+        <v>73.33</v>
       </c>
       <c r="R123" t="n">
         <v>0</v>
@@ -11310,7 +11350,7 @@
         <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>69.45</v>
+        <v>73.61</v>
       </c>
       <c r="R125" t="n">
         <v>0</v>
@@ -11749,10 +11789,10 @@
       </c>
       <c r="O131" t="inlineStr"/>
       <c r="P131" t="n">
-        <v>59.4</v>
+        <v>73.3</v>
       </c>
       <c r="Q131" t="n">
-        <v>59.44</v>
+        <v>73.33</v>
       </c>
       <c r="R131" t="n">
         <v>0</v>
@@ -11907,10 +11947,10 @@
       </c>
       <c r="O133" t="inlineStr"/>
       <c r="P133" t="n">
-        <v>69.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="Q133" t="n">
-        <v>69.45</v>
+        <v>73.61</v>
       </c>
       <c r="R133" t="n">
         <v>0</v>
@@ -12270,14 +12310,14 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P138" t="n">
         <v>100</v>
       </c>
       <c r="Q138" t="n">
-        <v>73.87</v>
+        <v>74.28</v>
       </c>
       <c r="R138" t="n">
         <v>9</v>
@@ -12353,7 +12393,7 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P139" t="n">
@@ -12440,7 +12480,7 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P140" t="n">
@@ -12527,7 +12567,7 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P141" t="n">
@@ -12610,14 +12650,14 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P142" t="n">
         <v>100</v>
       </c>
       <c r="Q142" t="n">
-        <v>73.87</v>
+        <v>74.28</v>
       </c>
       <c r="R142" t="n">
         <v>9</v>
@@ -12693,7 +12733,7 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P143" t="n">
@@ -12776,7 +12816,7 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P144" t="n">
@@ -12859,7 +12899,7 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P145" t="n">
@@ -12945,7 +12985,7 @@
         <v>88.90000000000001</v>
       </c>
       <c r="Q146" t="n">
-        <v>73.87</v>
+        <v>74.28</v>
       </c>
       <c r="R146" t="n">
         <v>8</v>
@@ -13261,7 +13301,7 @@
         <v>88.90000000000001</v>
       </c>
       <c r="Q150" t="n">
-        <v>73.87</v>
+        <v>74.28</v>
       </c>
       <c r="R150" t="n">
         <v>8</v>
@@ -13585,7 +13625,7 @@
         <v>88.90000000000001</v>
       </c>
       <c r="Q154" t="n">
-        <v>73.87</v>
+        <v>74.28</v>
       </c>
       <c r="R154" t="n">
         <v>8</v>
@@ -13896,15 +13936,19 @@
           <t>programada</t>
         </is>
       </c>
-      <c r="O158" t="inlineStr"/>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
       <c r="P158" t="n">
-        <v>88.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="Q158" t="n">
-        <v>73.87</v>
+        <v>74.28</v>
       </c>
       <c r="R158" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S158" t="n">
         <v>9</v>
@@ -14217,7 +14261,7 @@
         <v>88.90000000000001</v>
       </c>
       <c r="Q162" t="n">
-        <v>73.87</v>
+        <v>74.28</v>
       </c>
       <c r="R162" t="n">
         <v>8</v>
@@ -14533,7 +14577,7 @@
         <v>88.90000000000001</v>
       </c>
       <c r="Q166" t="n">
-        <v>73.87</v>
+        <v>74.28</v>
       </c>
       <c r="R166" t="n">
         <v>8</v>
@@ -14849,7 +14893,7 @@
         <v>88.90000000000001</v>
       </c>
       <c r="Q170" t="n">
-        <v>73.87</v>
+        <v>74.28</v>
       </c>
       <c r="R170" t="n">
         <v>8</v>
@@ -15165,7 +15209,7 @@
         <v>88.90000000000001</v>
       </c>
       <c r="Q174" t="n">
-        <v>73.87</v>
+        <v>74.28</v>
       </c>
       <c r="R174" t="n">
         <v>8</v>
@@ -15481,7 +15525,7 @@
         <v>88.90000000000001</v>
       </c>
       <c r="Q178" t="n">
-        <v>73.87</v>
+        <v>74.28</v>
       </c>
       <c r="R178" t="n">
         <v>8</v>
@@ -15797,7 +15841,7 @@
         <v>88.90000000000001</v>
       </c>
       <c r="Q182" t="n">
-        <v>73.87</v>
+        <v>74.28</v>
       </c>
       <c r="R182" t="n">
         <v>8</v>
@@ -16113,7 +16157,7 @@
         <v>0</v>
       </c>
       <c r="Q186" t="n">
-        <v>73.87</v>
+        <v>74.28</v>
       </c>
       <c r="R186" t="n">
         <v>0</v>
@@ -16429,7 +16473,7 @@
         <v>11.1</v>
       </c>
       <c r="Q190" t="n">
-        <v>73.87</v>
+        <v>74.28</v>
       </c>
       <c r="R190" t="n">
         <v>1</v>
@@ -16745,7 +16789,7 @@
         <v>11.1</v>
       </c>
       <c r="Q194" t="n">
-        <v>73.87</v>
+        <v>74.28</v>
       </c>
       <c r="R194" t="n">
         <v>1</v>
@@ -17061,7 +17105,7 @@
         <v>11.1</v>
       </c>
       <c r="Q198" t="n">
-        <v>73.87</v>
+        <v>74.28</v>
       </c>
       <c r="R198" t="n">
         <v>1</v>
@@ -17374,10 +17418,10 @@
       </c>
       <c r="O202" t="inlineStr"/>
       <c r="P202" t="n">
-        <v>73.90000000000001</v>
+        <v>74.3</v>
       </c>
       <c r="Q202" t="n">
-        <v>73.87</v>
+        <v>74.28</v>
       </c>
       <c r="R202" t="n">
         <v>0</v>
@@ -17690,7 +17734,7 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P206" t="n">
@@ -17773,7 +17817,7 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P207" t="n">
@@ -17856,7 +17900,7 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P208" t="n">
@@ -17939,7 +17983,7 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P209" t="n">
@@ -18022,14 +18066,14 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P210" t="n">
         <v>100</v>
       </c>
       <c r="Q210" t="n">
-        <v>26.39</v>
+        <v>32.87</v>
       </c>
       <c r="R210" t="n">
         <v>12</v>
@@ -18105,7 +18149,7 @@
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P211" t="n">
@@ -18267,7 +18311,7 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P213" t="n">
@@ -18350,7 +18394,7 @@
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P214" t="n">
@@ -18436,7 +18480,7 @@
         <v>91.7</v>
       </c>
       <c r="Q215" t="n">
-        <v>26.39</v>
+        <v>32.87</v>
       </c>
       <c r="R215" t="n">
         <v>11</v>
@@ -18831,7 +18875,7 @@
         <v>0</v>
       </c>
       <c r="Q220" t="n">
-        <v>26.39</v>
+        <v>32.87</v>
       </c>
       <c r="R220" t="n">
         <v>0</v>
@@ -19226,7 +19270,7 @@
         <v>0</v>
       </c>
       <c r="Q225" t="n">
-        <v>26.39</v>
+        <v>32.87</v>
       </c>
       <c r="R225" t="n">
         <v>0</v>
@@ -19302,7 +19346,7 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P226" t="n">
@@ -19543,7 +19587,7 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P229" t="n">
@@ -19626,13 +19670,13 @@
       </c>
       <c r="O230" t="inlineStr"/>
       <c r="P230" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Q230" t="n">
-        <v>26.39</v>
+        <v>32.87</v>
       </c>
       <c r="R230" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S230" t="n">
         <v>12</v>
@@ -19705,7 +19749,7 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P231" t="n">
@@ -19946,7 +19990,7 @@
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P234" t="n">
@@ -20029,13 +20073,13 @@
       </c>
       <c r="O235" t="inlineStr"/>
       <c r="P235" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Q235" t="n">
-        <v>26.39</v>
+        <v>32.87</v>
       </c>
       <c r="R235" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S235" t="n">
         <v>12</v>
@@ -20345,7 +20389,7 @@
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P239" t="n">
@@ -20428,13 +20472,13 @@
       </c>
       <c r="O240" t="inlineStr"/>
       <c r="P240" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="Q240" t="n">
-        <v>26.39</v>
+        <v>32.87</v>
       </c>
       <c r="R240" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S240" t="n">
         <v>12</v>
@@ -20507,7 +20551,7 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P241" t="n">
@@ -20748,7 +20792,7 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P244" t="n">
@@ -20831,13 +20875,13 @@
       </c>
       <c r="O245" t="inlineStr"/>
       <c r="P245" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="Q245" t="n">
-        <v>26.39</v>
+        <v>32.87</v>
       </c>
       <c r="R245" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S245" t="n">
         <v>12</v>
@@ -21147,7 +21191,7 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P249" t="n">
@@ -21233,7 +21277,7 @@
         <v>0</v>
       </c>
       <c r="Q250" t="n">
-        <v>26.39</v>
+        <v>32.87</v>
       </c>
       <c r="R250" t="n">
         <v>0</v>
@@ -21546,7 +21590,7 @@
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P254" t="n">
@@ -21632,7 +21676,7 @@
         <v>0</v>
       </c>
       <c r="Q255" t="n">
-        <v>26.39</v>
+        <v>32.87</v>
       </c>
       <c r="R255" t="n">
         <v>0</v>
@@ -21945,7 +21989,7 @@
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P259" t="n">
@@ -22031,7 +22075,7 @@
         <v>0</v>
       </c>
       <c r="Q260" t="n">
-        <v>26.39</v>
+        <v>32.87</v>
       </c>
       <c r="R260" t="n">
         <v>0</v>
@@ -22344,7 +22388,7 @@
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P264" t="n">
@@ -22430,7 +22474,7 @@
         <v>0</v>
       </c>
       <c r="Q265" t="n">
-        <v>26.39</v>
+        <v>32.87</v>
       </c>
       <c r="R265" t="n">
         <v>0</v>
@@ -22825,7 +22869,7 @@
         <v>0</v>
       </c>
       <c r="Q270" t="n">
-        <v>26.39</v>
+        <v>32.87</v>
       </c>
       <c r="R270" t="n">
         <v>0</v>
@@ -23220,7 +23264,7 @@
         <v>0</v>
       </c>
       <c r="Q275" t="n">
-        <v>26.39</v>
+        <v>32.87</v>
       </c>
       <c r="R275" t="n">
         <v>0</v>
@@ -23615,7 +23659,7 @@
         <v>0</v>
       </c>
       <c r="Q280" t="n">
-        <v>26.39</v>
+        <v>32.87</v>
       </c>
       <c r="R280" t="n">
         <v>0</v>
@@ -24010,7 +24054,7 @@
         <v>0</v>
       </c>
       <c r="Q285" t="n">
-        <v>26.39</v>
+        <v>32.87</v>
       </c>
       <c r="R285" t="n">
         <v>0</v>
@@ -24402,10 +24446,10 @@
       </c>
       <c r="O290" t="inlineStr"/>
       <c r="P290" t="n">
-        <v>26.4</v>
+        <v>32.9</v>
       </c>
       <c r="Q290" t="n">
-        <v>26.39</v>
+        <v>32.87</v>
       </c>
       <c r="R290" t="n">
         <v>0</v>
@@ -24481,14 +24525,14 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P291" t="n">
         <v>100</v>
       </c>
       <c r="Q291" t="n">
-        <v>20.51</v>
+        <v>25.88</v>
       </c>
       <c r="R291" t="n">
         <v>41</v>
@@ -24564,7 +24608,7 @@
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P292" t="n">
@@ -24647,14 +24691,14 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P293" t="n">
         <v>100</v>
       </c>
       <c r="Q293" t="n">
-        <v>71.59999999999999</v>
+        <v>72.53</v>
       </c>
       <c r="R293" t="n">
         <v>18</v>
@@ -24730,14 +24774,14 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P294" t="n">
         <v>100</v>
       </c>
       <c r="Q294" t="n">
-        <v>20.51</v>
+        <v>25.88</v>
       </c>
       <c r="R294" t="n">
         <v>41</v>
@@ -24813,7 +24857,7 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P295" t="n">
@@ -24896,14 +24940,14 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P296" t="n">
         <v>100</v>
       </c>
       <c r="Q296" t="n">
-        <v>71.59999999999999</v>
+        <v>72.53</v>
       </c>
       <c r="R296" t="n">
         <v>18</v>
@@ -24982,7 +25026,7 @@
         <v>0</v>
       </c>
       <c r="Q297" t="n">
-        <v>20.51</v>
+        <v>25.88</v>
       </c>
       <c r="R297" t="n">
         <v>0</v>
@@ -25058,7 +25102,7 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P298" t="n">
@@ -25141,14 +25185,14 @@
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P299" t="n">
         <v>100</v>
       </c>
       <c r="Q299" t="n">
-        <v>71.59999999999999</v>
+        <v>72.53</v>
       </c>
       <c r="R299" t="n">
         <v>18</v>
@@ -25227,7 +25271,7 @@
         <v>0</v>
       </c>
       <c r="Q300" t="n">
-        <v>20.51</v>
+        <v>25.88</v>
       </c>
       <c r="R300" t="n">
         <v>0</v>
@@ -25303,7 +25347,7 @@
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P301" t="n">
@@ -25386,14 +25430,14 @@
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P302" t="n">
         <v>100</v>
       </c>
       <c r="Q302" t="n">
-        <v>71.59999999999999</v>
+        <v>72.53</v>
       </c>
       <c r="R302" t="n">
         <v>18</v>
@@ -25469,14 +25513,14 @@
       </c>
       <c r="O303" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P303" t="n">
         <v>100</v>
       </c>
       <c r="Q303" t="n">
-        <v>71.59999999999999</v>
+        <v>72.53</v>
       </c>
       <c r="R303" t="n">
         <v>18</v>
@@ -25555,7 +25599,7 @@
         <v>0</v>
       </c>
       <c r="Q304" t="n">
-        <v>20.51</v>
+        <v>25.88</v>
       </c>
       <c r="R304" t="n">
         <v>0</v>
@@ -25631,7 +25675,7 @@
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P305" t="n">
@@ -25714,14 +25758,14 @@
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P306" t="n">
         <v>100</v>
       </c>
       <c r="Q306" t="n">
-        <v>71.59999999999999</v>
+        <v>72.53</v>
       </c>
       <c r="R306" t="n">
         <v>18</v>
@@ -25797,14 +25841,14 @@
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P307" t="n">
         <v>100</v>
       </c>
       <c r="Q307" t="n">
-        <v>71.59999999999999</v>
+        <v>72.53</v>
       </c>
       <c r="R307" t="n">
         <v>18</v>
@@ -25883,7 +25927,7 @@
         <v>0</v>
       </c>
       <c r="Q308" t="n">
-        <v>20.51</v>
+        <v>25.88</v>
       </c>
       <c r="R308" t="n">
         <v>0</v>
@@ -25959,7 +26003,7 @@
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P309" t="n">
@@ -26042,14 +26086,14 @@
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P310" t="n">
         <v>100</v>
       </c>
       <c r="Q310" t="n">
-        <v>71.59999999999999</v>
+        <v>72.53</v>
       </c>
       <c r="R310" t="n">
         <v>18</v>
@@ -26125,14 +26169,14 @@
       </c>
       <c r="O311" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P311" t="n">
         <v>100</v>
       </c>
       <c r="Q311" t="n">
-        <v>71.59999999999999</v>
+        <v>72.53</v>
       </c>
       <c r="R311" t="n">
         <v>18</v>
@@ -26211,7 +26255,7 @@
         <v>0</v>
       </c>
       <c r="Q312" t="n">
-        <v>20.51</v>
+        <v>25.88</v>
       </c>
       <c r="R312" t="n">
         <v>0</v>
@@ -26287,7 +26331,7 @@
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P313" t="n">
@@ -26368,15 +26412,19 @@
           <t>programada</t>
         </is>
       </c>
-      <c r="O314" t="inlineStr"/>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
       <c r="P314" t="n">
-        <v>94.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="Q314" t="n">
-        <v>71.59999999999999</v>
+        <v>72.53</v>
       </c>
       <c r="R314" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S314" t="n">
         <v>18</v>
@@ -26447,15 +26495,19 @@
           <t>programada</t>
         </is>
       </c>
-      <c r="O315" t="inlineStr"/>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
       <c r="P315" t="n">
-        <v>94.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="Q315" t="n">
-        <v>71.59999999999999</v>
+        <v>72.53</v>
       </c>
       <c r="R315" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S315" t="n">
         <v>18</v>
@@ -26531,7 +26583,7 @@
         <v>0</v>
       </c>
       <c r="Q316" t="n">
-        <v>20.51</v>
+        <v>25.88</v>
       </c>
       <c r="R316" t="n">
         <v>0</v>
@@ -26607,7 +26659,7 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P317" t="n">
@@ -26688,15 +26740,19 @@
           <t>programada</t>
         </is>
       </c>
-      <c r="O318" t="inlineStr"/>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
       <c r="P318" t="n">
-        <v>94.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="Q318" t="n">
-        <v>71.59999999999999</v>
+        <v>72.53</v>
       </c>
       <c r="R318" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S318" t="n">
         <v>18</v>
@@ -26767,15 +26823,19 @@
           <t>programada</t>
         </is>
       </c>
-      <c r="O319" t="inlineStr"/>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
       <c r="P319" t="n">
-        <v>94.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="Q319" t="n">
-        <v>71.59999999999999</v>
+        <v>72.53</v>
       </c>
       <c r="R319" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S319" t="n">
         <v>18</v>
@@ -26851,7 +26911,7 @@
         <v>0</v>
       </c>
       <c r="Q320" t="n">
-        <v>20.51</v>
+        <v>25.88</v>
       </c>
       <c r="R320" t="n">
         <v>0</v>
@@ -26927,7 +26987,7 @@
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P321" t="n">
@@ -27010,13 +27070,13 @@
       </c>
       <c r="O322" t="inlineStr"/>
       <c r="P322" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="Q322" t="n">
-        <v>71.59999999999999</v>
+        <v>72.53</v>
       </c>
       <c r="R322" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S322" t="n">
         <v>18</v>
@@ -27089,13 +27149,13 @@
       </c>
       <c r="O323" t="inlineStr"/>
       <c r="P323" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="Q323" t="n">
-        <v>71.59999999999999</v>
+        <v>72.53</v>
       </c>
       <c r="R323" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S323" t="n">
         <v>18</v>
@@ -27171,7 +27231,7 @@
         <v>0</v>
       </c>
       <c r="Q324" t="n">
-        <v>20.51</v>
+        <v>25.88</v>
       </c>
       <c r="R324" t="n">
         <v>0</v>
@@ -27247,7 +27307,7 @@
       </c>
       <c r="O325" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P325" t="n">
@@ -27330,13 +27390,13 @@
       </c>
       <c r="O326" t="inlineStr"/>
       <c r="P326" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="Q326" t="n">
-        <v>71.59999999999999</v>
+        <v>72.53</v>
       </c>
       <c r="R326" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S326" t="n">
         <v>18</v>
@@ -27409,13 +27469,13 @@
       </c>
       <c r="O327" t="inlineStr"/>
       <c r="P327" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="Q327" t="n">
-        <v>71.59999999999999</v>
+        <v>72.53</v>
       </c>
       <c r="R327" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S327" t="n">
         <v>18</v>
@@ -27491,7 +27551,7 @@
         <v>0</v>
       </c>
       <c r="Q328" t="n">
-        <v>20.51</v>
+        <v>25.88</v>
       </c>
       <c r="R328" t="n">
         <v>0</v>
@@ -27567,7 +27627,7 @@
       </c>
       <c r="O329" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P329" t="n">
@@ -27650,13 +27710,13 @@
       </c>
       <c r="O330" t="inlineStr"/>
       <c r="P330" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="Q330" t="n">
-        <v>71.59999999999999</v>
+        <v>72.53</v>
       </c>
       <c r="R330" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S330" t="n">
         <v>18</v>
@@ -27729,13 +27789,13 @@
       </c>
       <c r="O331" t="inlineStr"/>
       <c r="P331" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="Q331" t="n">
-        <v>71.59999999999999</v>
+        <v>72.53</v>
       </c>
       <c r="R331" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S331" t="n">
         <v>18</v>
@@ -27811,7 +27871,7 @@
         <v>0</v>
       </c>
       <c r="Q332" t="n">
-        <v>20.51</v>
+        <v>25.88</v>
       </c>
       <c r="R332" t="n">
         <v>0</v>
@@ -27887,7 +27947,7 @@
       </c>
       <c r="O333" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P333" t="n">
@@ -27970,13 +28030,13 @@
       </c>
       <c r="O334" t="inlineStr"/>
       <c r="P334" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="Q334" t="n">
-        <v>71.59999999999999</v>
+        <v>72.53</v>
       </c>
       <c r="R334" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S334" t="n">
         <v>18</v>
@@ -28049,13 +28109,13 @@
       </c>
       <c r="O335" t="inlineStr"/>
       <c r="P335" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="Q335" t="n">
-        <v>71.59999999999999</v>
+        <v>72.53</v>
       </c>
       <c r="R335" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S335" t="n">
         <v>18</v>
@@ -28131,7 +28191,7 @@
         <v>0</v>
       </c>
       <c r="Q336" t="n">
-        <v>20.51</v>
+        <v>25.88</v>
       </c>
       <c r="R336" t="n">
         <v>0</v>
@@ -28289,7 +28349,7 @@
         <v>0</v>
       </c>
       <c r="Q338" t="n">
-        <v>71.59999999999999</v>
+        <v>72.53</v>
       </c>
       <c r="R338" t="n">
         <v>0</v>
@@ -28368,7 +28428,7 @@
         <v>0</v>
       </c>
       <c r="Q339" t="n">
-        <v>71.59999999999999</v>
+        <v>72.53</v>
       </c>
       <c r="R339" t="n">
         <v>0</v>
@@ -28447,7 +28507,7 @@
         <v>0</v>
       </c>
       <c r="Q340" t="n">
-        <v>20.51</v>
+        <v>25.88</v>
       </c>
       <c r="R340" t="n">
         <v>0</v>
@@ -28605,7 +28665,7 @@
         <v>0</v>
       </c>
       <c r="Q342" t="n">
-        <v>71.59999999999999</v>
+        <v>72.53</v>
       </c>
       <c r="R342" t="n">
         <v>0</v>
@@ -28684,7 +28744,7 @@
         <v>0</v>
       </c>
       <c r="Q343" t="n">
-        <v>71.59999999999999</v>
+        <v>72.53</v>
       </c>
       <c r="R343" t="n">
         <v>0</v>
@@ -28763,7 +28823,7 @@
         <v>0</v>
       </c>
       <c r="Q344" t="n">
-        <v>20.51</v>
+        <v>25.88</v>
       </c>
       <c r="R344" t="n">
         <v>0</v>
@@ -28921,7 +28981,7 @@
         <v>0</v>
       </c>
       <c r="Q346" t="n">
-        <v>71.59999999999999</v>
+        <v>72.53</v>
       </c>
       <c r="R346" t="n">
         <v>0</v>
@@ -29000,7 +29060,7 @@
         <v>0</v>
       </c>
       <c r="Q347" t="n">
-        <v>71.59999999999999</v>
+        <v>72.53</v>
       </c>
       <c r="R347" t="n">
         <v>0</v>
@@ -29079,7 +29139,7 @@
         <v>0</v>
       </c>
       <c r="Q348" t="n">
-        <v>20.51</v>
+        <v>25.88</v>
       </c>
       <c r="R348" t="n">
         <v>0</v>
@@ -29237,7 +29297,7 @@
         <v>0</v>
       </c>
       <c r="Q350" t="n">
-        <v>71.59999999999999</v>
+        <v>72.53</v>
       </c>
       <c r="R350" t="n">
         <v>0</v>
@@ -29316,7 +29376,7 @@
         <v>0</v>
       </c>
       <c r="Q351" t="n">
-        <v>71.59999999999999</v>
+        <v>72.53</v>
       </c>
       <c r="R351" t="n">
         <v>0</v>
@@ -29392,10 +29452,10 @@
       </c>
       <c r="O352" t="inlineStr"/>
       <c r="P352" t="n">
-        <v>20.5</v>
+        <v>25.9</v>
       </c>
       <c r="Q352" t="n">
-        <v>20.51</v>
+        <v>25.88</v>
       </c>
       <c r="R352" t="n">
         <v>0</v>
@@ -29550,10 +29610,10 @@
       </c>
       <c r="O354" t="inlineStr"/>
       <c r="P354" t="n">
-        <v>71.59999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="Q354" t="n">
-        <v>71.59999999999999</v>
+        <v>72.53</v>
       </c>
       <c r="R354" t="n">
         <v>0</v>
@@ -29629,10 +29689,10 @@
       </c>
       <c r="O355" t="inlineStr"/>
       <c r="P355" t="n">
-        <v>71.59999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="Q355" t="n">
-        <v>71.59999999999999</v>
+        <v>72.53</v>
       </c>
       <c r="R355" t="n">
         <v>0</v>
@@ -29708,14 +29768,14 @@
       </c>
       <c r="O356" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P356" t="n">
         <v>100</v>
       </c>
       <c r="Q356" t="n">
-        <v>21.48</v>
+        <v>23.85</v>
       </c>
       <c r="R356" t="n">
         <v>25</v>
@@ -29791,14 +29851,14 @@
       </c>
       <c r="O357" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P357" t="n">
         <v>100</v>
       </c>
       <c r="Q357" t="n">
-        <v>18.52</v>
+        <v>30</v>
       </c>
       <c r="R357" t="n">
         <v>15</v>
@@ -29874,7 +29934,7 @@
       </c>
       <c r="O358" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P358" t="n">
@@ -29957,14 +30017,14 @@
       </c>
       <c r="O359" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P359" t="n">
         <v>100</v>
       </c>
       <c r="Q359" t="n">
-        <v>21.48</v>
+        <v>23.85</v>
       </c>
       <c r="R359" t="n">
         <v>25</v>
@@ -30040,14 +30100,14 @@
       </c>
       <c r="O360" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P360" t="n">
         <v>100</v>
       </c>
       <c r="Q360" t="n">
-        <v>18.52</v>
+        <v>30</v>
       </c>
       <c r="R360" t="n">
         <v>15</v>
@@ -30123,7 +30183,7 @@
       </c>
       <c r="O361" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P361" t="n">
@@ -30206,14 +30266,14 @@
       </c>
       <c r="O362" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P362" t="n">
         <v>100</v>
       </c>
       <c r="Q362" t="n">
-        <v>21.48</v>
+        <v>23.85</v>
       </c>
       <c r="R362" t="n">
         <v>25</v>
@@ -30289,14 +30349,14 @@
       </c>
       <c r="O363" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P363" t="n">
         <v>100</v>
       </c>
       <c r="Q363" t="n">
-        <v>18.52</v>
+        <v>30</v>
       </c>
       <c r="R363" t="n">
         <v>15</v>
@@ -30372,7 +30432,7 @@
       </c>
       <c r="O364" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P364" t="n">
@@ -30455,14 +30515,14 @@
       </c>
       <c r="O365" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P365" t="n">
         <v>100</v>
       </c>
       <c r="Q365" t="n">
-        <v>21.48</v>
+        <v>23.85</v>
       </c>
       <c r="R365" t="n">
         <v>25</v>
@@ -30538,14 +30598,14 @@
       </c>
       <c r="O366" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P366" t="n">
         <v>100</v>
       </c>
       <c r="Q366" t="n">
-        <v>18.52</v>
+        <v>30</v>
       </c>
       <c r="R366" t="n">
         <v>15</v>
@@ -30621,7 +30681,7 @@
       </c>
       <c r="O367" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P367" t="n">
@@ -30707,7 +30767,7 @@
         <v>0</v>
       </c>
       <c r="Q368" t="n">
-        <v>21.48</v>
+        <v>23.85</v>
       </c>
       <c r="R368" t="n">
         <v>0</v>
@@ -30786,7 +30846,7 @@
         <v>0</v>
       </c>
       <c r="Q369" t="n">
-        <v>18.52</v>
+        <v>30</v>
       </c>
       <c r="R369" t="n">
         <v>0</v>
@@ -30862,7 +30922,7 @@
       </c>
       <c r="O370" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P370" t="n">
@@ -30948,7 +31008,7 @@
         <v>0</v>
       </c>
       <c r="Q371" t="n">
-        <v>21.48</v>
+        <v>23.85</v>
       </c>
       <c r="R371" t="n">
         <v>0</v>
@@ -31027,7 +31087,7 @@
         <v>0</v>
       </c>
       <c r="Q372" t="n">
-        <v>18.52</v>
+        <v>30</v>
       </c>
       <c r="R372" t="n">
         <v>0</v>
@@ -31103,7 +31163,7 @@
       </c>
       <c r="O373" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P373" t="n">
@@ -31189,7 +31249,7 @@
         <v>0</v>
       </c>
       <c r="Q374" t="n">
-        <v>21.48</v>
+        <v>23.85</v>
       </c>
       <c r="R374" t="n">
         <v>0</v>
@@ -31268,7 +31328,7 @@
         <v>0</v>
       </c>
       <c r="Q375" t="n">
-        <v>18.52</v>
+        <v>30</v>
       </c>
       <c r="R375" t="n">
         <v>0</v>
@@ -31344,7 +31404,7 @@
       </c>
       <c r="O376" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P376" t="n">
@@ -31430,7 +31490,7 @@
         <v>0</v>
       </c>
       <c r="Q377" t="n">
-        <v>21.48</v>
+        <v>23.85</v>
       </c>
       <c r="R377" t="n">
         <v>0</v>
@@ -31509,7 +31569,7 @@
         <v>0</v>
       </c>
       <c r="Q378" t="n">
-        <v>18.52</v>
+        <v>30</v>
       </c>
       <c r="R378" t="n">
         <v>0</v>
@@ -31585,7 +31645,7 @@
       </c>
       <c r="O379" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P379" t="n">
@@ -31671,7 +31731,7 @@
         <v>0</v>
       </c>
       <c r="Q380" t="n">
-        <v>21.48</v>
+        <v>23.85</v>
       </c>
       <c r="R380" t="n">
         <v>0</v>
@@ -31750,7 +31810,7 @@
         <v>0</v>
       </c>
       <c r="Q381" t="n">
-        <v>18.52</v>
+        <v>30</v>
       </c>
       <c r="R381" t="n">
         <v>0</v>
@@ -31826,7 +31886,7 @@
       </c>
       <c r="O382" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P382" t="n">
@@ -31912,7 +31972,7 @@
         <v>0</v>
       </c>
       <c r="Q383" t="n">
-        <v>21.48</v>
+        <v>23.85</v>
       </c>
       <c r="R383" t="n">
         <v>0</v>
@@ -31991,7 +32051,7 @@
         <v>0</v>
       </c>
       <c r="Q384" t="n">
-        <v>18.52</v>
+        <v>30</v>
       </c>
       <c r="R384" t="n">
         <v>0</v>
@@ -32067,7 +32127,7 @@
       </c>
       <c r="O385" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P385" t="n">
@@ -32153,7 +32213,7 @@
         <v>0</v>
       </c>
       <c r="Q386" t="n">
-        <v>21.48</v>
+        <v>23.85</v>
       </c>
       <c r="R386" t="n">
         <v>0</v>
@@ -32232,7 +32292,7 @@
         <v>0</v>
       </c>
       <c r="Q387" t="n">
-        <v>18.52</v>
+        <v>30</v>
       </c>
       <c r="R387" t="n">
         <v>0</v>
@@ -32308,7 +32368,7 @@
       </c>
       <c r="O388" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P388" t="n">
@@ -32394,7 +32454,7 @@
         <v>0</v>
       </c>
       <c r="Q389" t="n">
-        <v>21.48</v>
+        <v>23.85</v>
       </c>
       <c r="R389" t="n">
         <v>0</v>
@@ -32473,7 +32533,7 @@
         <v>0</v>
       </c>
       <c r="Q390" t="n">
-        <v>18.52</v>
+        <v>30</v>
       </c>
       <c r="R390" t="n">
         <v>0</v>
@@ -32549,7 +32609,7 @@
       </c>
       <c r="O391" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P391" t="n">
@@ -32635,7 +32695,7 @@
         <v>0</v>
       </c>
       <c r="Q392" t="n">
-        <v>21.48</v>
+        <v>23.85</v>
       </c>
       <c r="R392" t="n">
         <v>0</v>
@@ -32714,7 +32774,7 @@
         <v>0</v>
       </c>
       <c r="Q393" t="n">
-        <v>18.52</v>
+        <v>30</v>
       </c>
       <c r="R393" t="n">
         <v>0</v>
@@ -32872,7 +32932,7 @@
         <v>0</v>
       </c>
       <c r="Q395" t="n">
-        <v>21.48</v>
+        <v>23.85</v>
       </c>
       <c r="R395" t="n">
         <v>0</v>
@@ -32951,7 +33011,7 @@
         <v>0</v>
       </c>
       <c r="Q396" t="n">
-        <v>18.52</v>
+        <v>30</v>
       </c>
       <c r="R396" t="n">
         <v>0</v>
@@ -33109,7 +33169,7 @@
         <v>0</v>
       </c>
       <c r="Q398" t="n">
-        <v>21.48</v>
+        <v>23.85</v>
       </c>
       <c r="R398" t="n">
         <v>0</v>
@@ -33188,7 +33248,7 @@
         <v>0</v>
       </c>
       <c r="Q399" t="n">
-        <v>18.52</v>
+        <v>30</v>
       </c>
       <c r="R399" t="n">
         <v>0</v>
@@ -33346,7 +33406,7 @@
         <v>0</v>
       </c>
       <c r="Q401" t="n">
-        <v>21.48</v>
+        <v>23.85</v>
       </c>
       <c r="R401" t="n">
         <v>0</v>
@@ -33425,7 +33485,7 @@
         <v>0</v>
       </c>
       <c r="Q402" t="n">
-        <v>18.52</v>
+        <v>30</v>
       </c>
       <c r="R402" t="n">
         <v>0</v>
@@ -33583,7 +33643,7 @@
         <v>0</v>
       </c>
       <c r="Q404" t="n">
-        <v>21.48</v>
+        <v>23.85</v>
       </c>
       <c r="R404" t="n">
         <v>0</v>
@@ -33662,7 +33722,7 @@
         <v>0</v>
       </c>
       <c r="Q405" t="n">
-        <v>18.52</v>
+        <v>30</v>
       </c>
       <c r="R405" t="n">
         <v>0</v>
@@ -33738,7 +33798,7 @@
       </c>
       <c r="O406" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P406" t="n">
@@ -33824,7 +33884,7 @@
         <v>0</v>
       </c>
       <c r="Q407" t="n">
-        <v>21.48</v>
+        <v>23.85</v>
       </c>
       <c r="R407" t="n">
         <v>0</v>
@@ -33903,7 +33963,7 @@
         <v>0</v>
       </c>
       <c r="Q408" t="n">
-        <v>18.52</v>
+        <v>30</v>
       </c>
       <c r="R408" t="n">
         <v>0</v>
@@ -33979,7 +34039,7 @@
       </c>
       <c r="O409" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P409" t="n">
@@ -34065,7 +34125,7 @@
         <v>0</v>
       </c>
       <c r="Q410" t="n">
-        <v>21.48</v>
+        <v>23.85</v>
       </c>
       <c r="R410" t="n">
         <v>0</v>
@@ -34144,7 +34204,7 @@
         <v>0</v>
       </c>
       <c r="Q411" t="n">
-        <v>18.52</v>
+        <v>30</v>
       </c>
       <c r="R411" t="n">
         <v>0</v>
@@ -34220,7 +34280,7 @@
       </c>
       <c r="O412" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P412" t="n">
@@ -34306,7 +34366,7 @@
         <v>0</v>
       </c>
       <c r="Q413" t="n">
-        <v>21.48</v>
+        <v>23.85</v>
       </c>
       <c r="R413" t="n">
         <v>0</v>
@@ -34385,7 +34445,7 @@
         <v>0</v>
       </c>
       <c r="Q414" t="n">
-        <v>18.52</v>
+        <v>30</v>
       </c>
       <c r="R414" t="n">
         <v>0</v>
@@ -34461,7 +34521,7 @@
       </c>
       <c r="O415" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P415" t="n">
@@ -34547,7 +34607,7 @@
         <v>0</v>
       </c>
       <c r="Q416" t="n">
-        <v>21.48</v>
+        <v>23.85</v>
       </c>
       <c r="R416" t="n">
         <v>0</v>
@@ -34626,7 +34686,7 @@
         <v>0</v>
       </c>
       <c r="Q417" t="n">
-        <v>18.52</v>
+        <v>30</v>
       </c>
       <c r="R417" t="n">
         <v>0</v>
@@ -34702,7 +34762,7 @@
       </c>
       <c r="O418" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P418" t="n">
@@ -34788,7 +34848,7 @@
         <v>0</v>
       </c>
       <c r="Q419" t="n">
-        <v>21.48</v>
+        <v>23.85</v>
       </c>
       <c r="R419" t="n">
         <v>0</v>
@@ -34867,7 +34927,7 @@
         <v>0</v>
       </c>
       <c r="Q420" t="n">
-        <v>18.52</v>
+        <v>30</v>
       </c>
       <c r="R420" t="n">
         <v>0</v>
@@ -34943,7 +35003,7 @@
       </c>
       <c r="O421" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P421" t="n">
@@ -35029,7 +35089,7 @@
         <v>0</v>
       </c>
       <c r="Q422" t="n">
-        <v>21.48</v>
+        <v>23.85</v>
       </c>
       <c r="R422" t="n">
         <v>0</v>
@@ -35108,7 +35168,7 @@
         <v>0</v>
       </c>
       <c r="Q423" t="n">
-        <v>18.52</v>
+        <v>30</v>
       </c>
       <c r="R423" t="n">
         <v>0</v>
@@ -35184,7 +35244,7 @@
       </c>
       <c r="O424" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P424" t="n">
@@ -35270,7 +35330,7 @@
         <v>0</v>
       </c>
       <c r="Q425" t="n">
-        <v>21.48</v>
+        <v>23.85</v>
       </c>
       <c r="R425" t="n">
         <v>0</v>
@@ -35349,7 +35409,7 @@
         <v>0</v>
       </c>
       <c r="Q426" t="n">
-        <v>18.52</v>
+        <v>30</v>
       </c>
       <c r="R426" t="n">
         <v>0</v>
@@ -35425,7 +35485,7 @@
       </c>
       <c r="O427" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P427" t="n">
@@ -35511,7 +35571,7 @@
         <v>0</v>
       </c>
       <c r="Q428" t="n">
-        <v>21.48</v>
+        <v>23.85</v>
       </c>
       <c r="R428" t="n">
         <v>0</v>
@@ -35590,7 +35650,7 @@
         <v>0</v>
       </c>
       <c r="Q429" t="n">
-        <v>18.52</v>
+        <v>30</v>
       </c>
       <c r="R429" t="n">
         <v>0</v>
@@ -35748,7 +35808,7 @@
         <v>0</v>
       </c>
       <c r="Q431" t="n">
-        <v>21.48</v>
+        <v>23.85</v>
       </c>
       <c r="R431" t="n">
         <v>0</v>
@@ -35827,7 +35887,7 @@
         <v>0</v>
       </c>
       <c r="Q432" t="n">
-        <v>18.52</v>
+        <v>30</v>
       </c>
       <c r="R432" t="n">
         <v>0</v>
@@ -35985,7 +36045,7 @@
         <v>0</v>
       </c>
       <c r="Q434" t="n">
-        <v>21.48</v>
+        <v>23.85</v>
       </c>
       <c r="R434" t="n">
         <v>0</v>
@@ -36064,7 +36124,7 @@
         <v>0</v>
       </c>
       <c r="Q435" t="n">
-        <v>18.52</v>
+        <v>30</v>
       </c>
       <c r="R435" t="n">
         <v>0</v>
@@ -36222,7 +36282,7 @@
         <v>0</v>
       </c>
       <c r="Q437" t="n">
-        <v>21.48</v>
+        <v>23.85</v>
       </c>
       <c r="R437" t="n">
         <v>0</v>
@@ -36301,7 +36361,7 @@
         <v>0</v>
       </c>
       <c r="Q438" t="n">
-        <v>18.52</v>
+        <v>30</v>
       </c>
       <c r="R438" t="n">
         <v>0</v>
@@ -36459,7 +36519,7 @@
         <v>0</v>
       </c>
       <c r="Q440" t="n">
-        <v>21.48</v>
+        <v>23.85</v>
       </c>
       <c r="R440" t="n">
         <v>0</v>
@@ -36538,7 +36598,7 @@
         <v>0</v>
       </c>
       <c r="Q441" t="n">
-        <v>18.52</v>
+        <v>30</v>
       </c>
       <c r="R441" t="n">
         <v>0</v>
@@ -36696,7 +36756,7 @@
         <v>0</v>
       </c>
       <c r="Q443" t="n">
-        <v>21.48</v>
+        <v>23.85</v>
       </c>
       <c r="R443" t="n">
         <v>0</v>
@@ -36775,7 +36835,7 @@
         <v>0</v>
       </c>
       <c r="Q444" t="n">
-        <v>18.52</v>
+        <v>30</v>
       </c>
       <c r="R444" t="n">
         <v>0</v>
@@ -36933,7 +36993,7 @@
         <v>0</v>
       </c>
       <c r="Q446" t="n">
-        <v>21.48</v>
+        <v>23.85</v>
       </c>
       <c r="R446" t="n">
         <v>0</v>
@@ -37012,7 +37072,7 @@
         <v>0</v>
       </c>
       <c r="Q447" t="n">
-        <v>18.52</v>
+        <v>30</v>
       </c>
       <c r="R447" t="n">
         <v>0</v>
@@ -37170,7 +37230,7 @@
         <v>0</v>
       </c>
       <c r="Q449" t="n">
-        <v>21.48</v>
+        <v>23.85</v>
       </c>
       <c r="R449" t="n">
         <v>0</v>
@@ -37249,7 +37309,7 @@
         <v>0</v>
       </c>
       <c r="Q450" t="n">
-        <v>18.52</v>
+        <v>30</v>
       </c>
       <c r="R450" t="n">
         <v>0</v>
@@ -37404,10 +37464,10 @@
       </c>
       <c r="O452" t="inlineStr"/>
       <c r="P452" t="n">
-        <v>21.5</v>
+        <v>23.8</v>
       </c>
       <c r="Q452" t="n">
-        <v>21.48</v>
+        <v>23.85</v>
       </c>
       <c r="R452" t="n">
         <v>0</v>
@@ -37483,10 +37543,10 @@
       </c>
       <c r="O453" t="inlineStr"/>
       <c r="P453" t="n">
-        <v>21.5</v>
+        <v>23.8</v>
       </c>
       <c r="Q453" t="n">
-        <v>21.48</v>
+        <v>23.85</v>
       </c>
       <c r="R453" t="n">
         <v>0</v>
@@ -37562,10 +37622,10 @@
       </c>
       <c r="O454" t="inlineStr"/>
       <c r="P454" t="n">
-        <v>18.5</v>
+        <v>30</v>
       </c>
       <c r="Q454" t="n">
-        <v>18.52</v>
+        <v>30</v>
       </c>
       <c r="R454" t="n">
         <v>0</v>
@@ -37641,10 +37701,10 @@
       </c>
       <c r="O455" t="inlineStr"/>
       <c r="P455" t="n">
-        <v>18.5</v>
+        <v>30</v>
       </c>
       <c r="Q455" t="n">
-        <v>18.52</v>
+        <v>30</v>
       </c>
       <c r="R455" t="n">
         <v>0</v>
@@ -37882,10 +37942,10 @@
       </c>
       <c r="O458" t="inlineStr"/>
       <c r="P458" t="n">
-        <v>21.5</v>
+        <v>23.8</v>
       </c>
       <c r="Q458" t="n">
-        <v>21.48</v>
+        <v>23.85</v>
       </c>
       <c r="R458" t="n">
         <v>0</v>
@@ -37961,10 +38021,10 @@
       </c>
       <c r="O459" t="inlineStr"/>
       <c r="P459" t="n">
-        <v>18.5</v>
+        <v>30</v>
       </c>
       <c r="Q459" t="n">
-        <v>18.52</v>
+        <v>30</v>
       </c>
       <c r="R459" t="n">
         <v>0</v>
@@ -38040,10 +38100,10 @@
       </c>
       <c r="O460" t="inlineStr"/>
       <c r="P460" t="n">
-        <v>18.5</v>
+        <v>30</v>
       </c>
       <c r="Q460" t="n">
-        <v>18.52</v>
+        <v>30</v>
       </c>
       <c r="R460" t="n">
         <v>0</v>
@@ -38281,7 +38341,7 @@
       </c>
       <c r="O463" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P463" t="n">
@@ -38364,14 +38424,14 @@
       </c>
       <c r="O464" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P464" t="n">
         <v>100</v>
       </c>
       <c r="Q464" t="n">
-        <v>25.12</v>
+        <v>27.62</v>
       </c>
       <c r="R464" t="n">
         <v>23</v>
@@ -38526,7 +38586,7 @@
       </c>
       <c r="O466" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P466" t="n">
@@ -38609,14 +38669,14 @@
       </c>
       <c r="O467" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P467" t="n">
         <v>100</v>
       </c>
       <c r="Q467" t="n">
-        <v>25.12</v>
+        <v>27.62</v>
       </c>
       <c r="R467" t="n">
         <v>23</v>
@@ -38692,7 +38752,7 @@
       </c>
       <c r="O468" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P468" t="n">
@@ -38775,14 +38835,14 @@
       </c>
       <c r="O469" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P469" t="n">
         <v>100</v>
       </c>
       <c r="Q469" t="n">
-        <v>25.12</v>
+        <v>27.62</v>
       </c>
       <c r="R469" t="n">
         <v>23</v>
@@ -38937,7 +38997,7 @@
       </c>
       <c r="O471" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P471" t="n">
@@ -39020,14 +39080,14 @@
       </c>
       <c r="O472" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P472" t="n">
         <v>100</v>
       </c>
       <c r="Q472" t="n">
-        <v>25.12</v>
+        <v>27.62</v>
       </c>
       <c r="R472" t="n">
         <v>23</v>
@@ -39185,7 +39245,7 @@
         <v>0</v>
       </c>
       <c r="Q474" t="n">
-        <v>25.12</v>
+        <v>27.62</v>
       </c>
       <c r="R474" t="n">
         <v>0</v>
@@ -39422,7 +39482,7 @@
         <v>0</v>
       </c>
       <c r="Q477" t="n">
-        <v>25.12</v>
+        <v>27.62</v>
       </c>
       <c r="R477" t="n">
         <v>0</v>
@@ -39580,7 +39640,7 @@
         <v>0</v>
       </c>
       <c r="Q479" t="n">
-        <v>25.12</v>
+        <v>27.62</v>
       </c>
       <c r="R479" t="n">
         <v>0</v>
@@ -39817,7 +39877,7 @@
         <v>0</v>
       </c>
       <c r="Q482" t="n">
-        <v>25.12</v>
+        <v>27.62</v>
       </c>
       <c r="R482" t="n">
         <v>0</v>
@@ -39972,13 +40032,13 @@
       </c>
       <c r="O484" t="inlineStr"/>
       <c r="P484" t="n">
-        <v>13</v>
+        <v>26.1</v>
       </c>
       <c r="Q484" t="n">
-        <v>25.12</v>
+        <v>27.62</v>
       </c>
       <c r="R484" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S484" t="n">
         <v>23</v>
@@ -40209,13 +40269,13 @@
       </c>
       <c r="O487" t="inlineStr"/>
       <c r="P487" t="n">
-        <v>13</v>
+        <v>26.1</v>
       </c>
       <c r="Q487" t="n">
-        <v>25.12</v>
+        <v>27.62</v>
       </c>
       <c r="R487" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S487" t="n">
         <v>23</v>
@@ -40367,13 +40427,13 @@
       </c>
       <c r="O489" t="inlineStr"/>
       <c r="P489" t="n">
-        <v>13</v>
+        <v>26.1</v>
       </c>
       <c r="Q489" t="n">
-        <v>25.12</v>
+        <v>27.62</v>
       </c>
       <c r="R489" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S489" t="n">
         <v>23</v>
@@ -40604,13 +40664,13 @@
       </c>
       <c r="O492" t="inlineStr"/>
       <c r="P492" t="n">
-        <v>13</v>
+        <v>26.1</v>
       </c>
       <c r="Q492" t="n">
-        <v>25.12</v>
+        <v>27.62</v>
       </c>
       <c r="R492" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S492" t="n">
         <v>23</v>
@@ -40765,7 +40825,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="Q494" t="n">
-        <v>25.12</v>
+        <v>27.62</v>
       </c>
       <c r="R494" t="n">
         <v>2</v>
@@ -41002,7 +41062,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="Q497" t="n">
-        <v>25.12</v>
+        <v>27.62</v>
       </c>
       <c r="R497" t="n">
         <v>2</v>
@@ -41157,13 +41217,13 @@
       </c>
       <c r="O499" t="inlineStr"/>
       <c r="P499" t="n">
-        <v>8.699999999999999</v>
+        <v>13</v>
       </c>
       <c r="Q499" t="n">
-        <v>25.12</v>
+        <v>27.62</v>
       </c>
       <c r="R499" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S499" t="n">
         <v>23</v>
@@ -41394,13 +41454,13 @@
       </c>
       <c r="O502" t="inlineStr"/>
       <c r="P502" t="n">
-        <v>8.699999999999999</v>
+        <v>13</v>
       </c>
       <c r="Q502" t="n">
-        <v>25.12</v>
+        <v>27.62</v>
       </c>
       <c r="R502" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S502" t="n">
         <v>23</v>
@@ -41555,7 +41615,7 @@
         <v>0</v>
       </c>
       <c r="Q504" t="n">
-        <v>25.12</v>
+        <v>27.62</v>
       </c>
       <c r="R504" t="n">
         <v>0</v>
@@ -41792,7 +41852,7 @@
         <v>0</v>
       </c>
       <c r="Q507" t="n">
-        <v>25.12</v>
+        <v>27.62</v>
       </c>
       <c r="R507" t="n">
         <v>0</v>
@@ -41950,7 +42010,7 @@
         <v>0</v>
       </c>
       <c r="Q509" t="n">
-        <v>25.12</v>
+        <v>27.62</v>
       </c>
       <c r="R509" t="n">
         <v>0</v>
@@ -42187,7 +42247,7 @@
         <v>0</v>
       </c>
       <c r="Q512" t="n">
-        <v>25.12</v>
+        <v>27.62</v>
       </c>
       <c r="R512" t="n">
         <v>0</v>
@@ -42345,7 +42405,7 @@
         <v>0</v>
       </c>
       <c r="Q514" t="n">
-        <v>25.12</v>
+        <v>27.62</v>
       </c>
       <c r="R514" t="n">
         <v>0</v>
@@ -42582,7 +42642,7 @@
         <v>0</v>
       </c>
       <c r="Q517" t="n">
-        <v>25.12</v>
+        <v>27.62</v>
       </c>
       <c r="R517" t="n">
         <v>0</v>
@@ -42740,7 +42800,7 @@
         <v>0</v>
       </c>
       <c r="Q519" t="n">
-        <v>25.12</v>
+        <v>27.62</v>
       </c>
       <c r="R519" t="n">
         <v>0</v>
@@ -42977,7 +43037,7 @@
         <v>0</v>
       </c>
       <c r="Q522" t="n">
-        <v>25.12</v>
+        <v>27.62</v>
       </c>
       <c r="R522" t="n">
         <v>0</v>
@@ -43135,7 +43195,7 @@
         <v>0</v>
       </c>
       <c r="Q524" t="n">
-        <v>25.12</v>
+        <v>27.62</v>
       </c>
       <c r="R524" t="n">
         <v>0</v>
@@ -43372,7 +43432,7 @@
         <v>0</v>
       </c>
       <c r="Q527" t="n">
-        <v>25.12</v>
+        <v>27.62</v>
       </c>
       <c r="R527" t="n">
         <v>0</v>
@@ -43530,7 +43590,7 @@
         <v>0</v>
       </c>
       <c r="Q529" t="n">
-        <v>25.12</v>
+        <v>27.62</v>
       </c>
       <c r="R529" t="n">
         <v>0</v>
@@ -43767,7 +43827,7 @@
         <v>0</v>
       </c>
       <c r="Q532" t="n">
-        <v>25.12</v>
+        <v>27.62</v>
       </c>
       <c r="R532" t="n">
         <v>0</v>
@@ -43925,7 +43985,7 @@
         <v>0</v>
       </c>
       <c r="Q534" t="n">
-        <v>25.12</v>
+        <v>27.62</v>
       </c>
       <c r="R534" t="n">
         <v>0</v>
@@ -44162,7 +44222,7 @@
         <v>0</v>
       </c>
       <c r="Q537" t="n">
-        <v>25.12</v>
+        <v>27.62</v>
       </c>
       <c r="R537" t="n">
         <v>0</v>
@@ -44320,7 +44380,7 @@
         <v>0</v>
       </c>
       <c r="Q539" t="n">
-        <v>25.12</v>
+        <v>27.62</v>
       </c>
       <c r="R539" t="n">
         <v>0</v>
@@ -44557,7 +44617,7 @@
         <v>0</v>
       </c>
       <c r="Q542" t="n">
-        <v>25.12</v>
+        <v>27.62</v>
       </c>
       <c r="R542" t="n">
         <v>0</v>
@@ -44712,10 +44772,10 @@
       </c>
       <c r="O544" t="inlineStr"/>
       <c r="P544" t="n">
-        <v>25.1</v>
+        <v>27.6</v>
       </c>
       <c r="Q544" t="n">
-        <v>25.12</v>
+        <v>27.62</v>
       </c>
       <c r="R544" t="n">
         <v>0</v>
@@ -44949,10 +45009,10 @@
       </c>
       <c r="O547" t="inlineStr"/>
       <c r="P547" t="n">
-        <v>25.1</v>
+        <v>27.6</v>
       </c>
       <c r="Q547" t="n">
-        <v>25.12</v>
+        <v>27.62</v>
       </c>
       <c r="R547" t="n">
         <v>0</v>
@@ -45028,7 +45088,7 @@
       </c>
       <c r="O548" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P548" t="n">
@@ -45111,14 +45171,14 @@
       </c>
       <c r="O549" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P549" t="n">
         <v>100</v>
       </c>
       <c r="Q549" t="n">
-        <v>87.04000000000001</v>
+        <v>88.27</v>
       </c>
       <c r="R549" t="n">
         <v>9</v>
@@ -45194,14 +45254,14 @@
       </c>
       <c r="O550" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P550" t="n">
         <v>100</v>
       </c>
       <c r="Q550" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="R550" t="n">
         <v>29</v>
@@ -45356,14 +45416,14 @@
       </c>
       <c r="O552" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P552" t="n">
         <v>100</v>
       </c>
       <c r="Q552" t="n">
-        <v>87.04000000000001</v>
+        <v>88.27</v>
       </c>
       <c r="R552" t="n">
         <v>9</v>
@@ -45439,14 +45499,14 @@
       </c>
       <c r="O553" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P553" t="n">
         <v>100</v>
       </c>
       <c r="Q553" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="R553" t="n">
         <v>29</v>
@@ -45604,7 +45664,7 @@
         <v>55.6</v>
       </c>
       <c r="Q555" t="n">
-        <v>87.04000000000001</v>
+        <v>88.27</v>
       </c>
       <c r="R555" t="n">
         <v>5</v>
@@ -45683,7 +45743,7 @@
         <v>0</v>
       </c>
       <c r="Q556" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="R556" t="n">
         <v>0</v>
@@ -45841,7 +45901,7 @@
         <v>55.6</v>
       </c>
       <c r="Q558" t="n">
-        <v>87.04000000000001</v>
+        <v>88.27</v>
       </c>
       <c r="R558" t="n">
         <v>5</v>
@@ -45920,7 +45980,7 @@
         <v>0</v>
       </c>
       <c r="Q559" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="R559" t="n">
         <v>0</v>
@@ -46075,14 +46135,14 @@
       </c>
       <c r="O561" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P561" t="n">
         <v>100</v>
       </c>
       <c r="Q561" t="n">
-        <v>87.04000000000001</v>
+        <v>88.27</v>
       </c>
       <c r="R561" t="n">
         <v>9</v>
@@ -46161,7 +46221,7 @@
         <v>0</v>
       </c>
       <c r="Q562" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="R562" t="n">
         <v>0</v>
@@ -46316,14 +46376,14 @@
       </c>
       <c r="O564" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P564" t="n">
         <v>100</v>
       </c>
       <c r="Q564" t="n">
-        <v>87.04000000000001</v>
+        <v>88.27</v>
       </c>
       <c r="R564" t="n">
         <v>9</v>
@@ -46402,7 +46462,7 @@
         <v>0</v>
       </c>
       <c r="Q565" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="R565" t="n">
         <v>0</v>
@@ -46557,14 +46617,14 @@
       </c>
       <c r="O567" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P567" t="n">
         <v>100</v>
       </c>
       <c r="Q567" t="n">
-        <v>87.04000000000001</v>
+        <v>88.27</v>
       </c>
       <c r="R567" t="n">
         <v>9</v>
@@ -46643,7 +46703,7 @@
         <v>0</v>
       </c>
       <c r="Q568" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="R568" t="n">
         <v>0</v>
@@ -46801,7 +46861,7 @@
         <v>88.90000000000001</v>
       </c>
       <c r="Q570" t="n">
-        <v>87.04000000000001</v>
+        <v>88.27</v>
       </c>
       <c r="R570" t="n">
         <v>8</v>
@@ -46880,7 +46940,7 @@
         <v>0</v>
       </c>
       <c r="Q571" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="R571" t="n">
         <v>0</v>
@@ -47035,14 +47095,14 @@
       </c>
       <c r="O573" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P573" t="n">
         <v>100</v>
       </c>
       <c r="Q573" t="n">
-        <v>87.04000000000001</v>
+        <v>88.27</v>
       </c>
       <c r="R573" t="n">
         <v>9</v>
@@ -47121,7 +47181,7 @@
         <v>0</v>
       </c>
       <c r="Q574" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="R574" t="n">
         <v>0</v>
@@ -47276,14 +47336,14 @@
       </c>
       <c r="O576" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P576" t="n">
         <v>100</v>
       </c>
       <c r="Q576" t="n">
-        <v>87.04000000000001</v>
+        <v>88.27</v>
       </c>
       <c r="R576" t="n">
         <v>9</v>
@@ -47362,7 +47422,7 @@
         <v>0</v>
       </c>
       <c r="Q577" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="R577" t="n">
         <v>0</v>
@@ -47517,14 +47577,14 @@
       </c>
       <c r="O579" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P579" t="n">
         <v>100</v>
       </c>
       <c r="Q579" t="n">
-        <v>87.04000000000001</v>
+        <v>88.27</v>
       </c>
       <c r="R579" t="n">
         <v>9</v>
@@ -47603,7 +47663,7 @@
         <v>0</v>
       </c>
       <c r="Q580" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="R580" t="n">
         <v>0</v>
@@ -47758,14 +47818,14 @@
       </c>
       <c r="O582" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P582" t="n">
         <v>100</v>
       </c>
       <c r="Q582" t="n">
-        <v>87.04000000000001</v>
+        <v>88.27</v>
       </c>
       <c r="R582" t="n">
         <v>9</v>
@@ -47844,7 +47904,7 @@
         <v>0</v>
       </c>
       <c r="Q583" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="R583" t="n">
         <v>0</v>
@@ -47999,13 +48059,13 @@
       </c>
       <c r="O585" t="inlineStr"/>
       <c r="P585" t="n">
-        <v>66.7</v>
+        <v>77.8</v>
       </c>
       <c r="Q585" t="n">
-        <v>87.04000000000001</v>
+        <v>88.27</v>
       </c>
       <c r="R585" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S585" t="n">
         <v>9</v>
@@ -48081,7 +48141,7 @@
         <v>0</v>
       </c>
       <c r="Q586" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="R586" t="n">
         <v>0</v>
@@ -48239,7 +48299,7 @@
         <v>44.4</v>
       </c>
       <c r="Q588" t="n">
-        <v>87.04000000000001</v>
+        <v>88.27</v>
       </c>
       <c r="R588" t="n">
         <v>4</v>
@@ -48318,7 +48378,7 @@
         <v>0</v>
       </c>
       <c r="Q589" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="R589" t="n">
         <v>0</v>
@@ -48476,7 +48536,7 @@
         <v>44.4</v>
       </c>
       <c r="Q591" t="n">
-        <v>87.04000000000001</v>
+        <v>88.27</v>
       </c>
       <c r="R591" t="n">
         <v>4</v>
@@ -48555,7 +48615,7 @@
         <v>0</v>
       </c>
       <c r="Q592" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="R592" t="n">
         <v>0</v>
@@ -48713,7 +48773,7 @@
         <v>44.4</v>
       </c>
       <c r="Q594" t="n">
-        <v>87.04000000000001</v>
+        <v>88.27</v>
       </c>
       <c r="R594" t="n">
         <v>4</v>
@@ -48792,7 +48852,7 @@
         <v>0</v>
       </c>
       <c r="Q595" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="R595" t="n">
         <v>0</v>
@@ -48947,10 +49007,10 @@
       </c>
       <c r="O597" t="inlineStr"/>
       <c r="P597" t="n">
-        <v>87</v>
+        <v>88.3</v>
       </c>
       <c r="Q597" t="n">
-        <v>87.04000000000001</v>
+        <v>88.27</v>
       </c>
       <c r="R597" t="n">
         <v>4</v>
@@ -49026,10 +49086,10 @@
       </c>
       <c r="O598" t="inlineStr"/>
       <c r="P598" t="n">
-        <v>18.5</v>
+        <v>31.5</v>
       </c>
       <c r="Q598" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="R598" t="n">
         <v>0</v>
@@ -49105,7 +49165,7 @@
       </c>
       <c r="O599" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P599" t="n">
@@ -49188,14 +49248,14 @@
       </c>
       <c r="O600" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P600" t="n">
         <v>100</v>
       </c>
       <c r="Q600" t="n">
-        <v>80.25</v>
+        <v>83.33</v>
       </c>
       <c r="R600" t="n">
         <v>9</v>
@@ -49271,14 +49331,14 @@
       </c>
       <c r="O601" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P601" t="n">
         <v>100</v>
       </c>
       <c r="Q601" t="n">
-        <v>18.52</v>
+        <v>23.35</v>
       </c>
       <c r="R601" t="n">
         <v>23</v>
@@ -49354,14 +49414,14 @@
       </c>
       <c r="O602" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P602" t="n">
         <v>100</v>
       </c>
       <c r="Q602" t="n">
-        <v>18.52</v>
+        <v>23.35</v>
       </c>
       <c r="R602" t="n">
         <v>23</v>
@@ -49516,14 +49576,14 @@
       </c>
       <c r="O604" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P604" t="n">
         <v>100</v>
       </c>
       <c r="Q604" t="n">
-        <v>80.25</v>
+        <v>83.33</v>
       </c>
       <c r="R604" t="n">
         <v>9</v>
@@ -49599,14 +49659,14 @@
       </c>
       <c r="O605" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P605" t="n">
         <v>100</v>
       </c>
       <c r="Q605" t="n">
-        <v>18.52</v>
+        <v>23.35</v>
       </c>
       <c r="R605" t="n">
         <v>23</v>
@@ -49682,14 +49742,14 @@
       </c>
       <c r="O606" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P606" t="n">
         <v>100</v>
       </c>
       <c r="Q606" t="n">
-        <v>18.52</v>
+        <v>23.35</v>
       </c>
       <c r="R606" t="n">
         <v>23</v>
@@ -49844,13 +49904,13 @@
       </c>
       <c r="O608" t="inlineStr"/>
       <c r="P608" t="n">
-        <v>33.3</v>
+        <v>44.4</v>
       </c>
       <c r="Q608" t="n">
-        <v>80.25</v>
+        <v>83.33</v>
       </c>
       <c r="R608" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S608" t="n">
         <v>9</v>
@@ -49926,7 +49986,7 @@
         <v>0</v>
       </c>
       <c r="Q609" t="n">
-        <v>18.52</v>
+        <v>23.35</v>
       </c>
       <c r="R609" t="n">
         <v>0</v>
@@ -50005,7 +50065,7 @@
         <v>0</v>
       </c>
       <c r="Q610" t="n">
-        <v>18.52</v>
+        <v>23.35</v>
       </c>
       <c r="R610" t="n">
         <v>0</v>
@@ -50160,13 +50220,13 @@
       </c>
       <c r="O612" t="inlineStr"/>
       <c r="P612" t="n">
-        <v>33.3</v>
+        <v>44.4</v>
       </c>
       <c r="Q612" t="n">
-        <v>80.25</v>
+        <v>83.33</v>
       </c>
       <c r="R612" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S612" t="n">
         <v>9</v>
@@ -50242,7 +50302,7 @@
         <v>0</v>
       </c>
       <c r="Q613" t="n">
-        <v>18.52</v>
+        <v>23.35</v>
       </c>
       <c r="R613" t="n">
         <v>0</v>
@@ -50321,7 +50381,7 @@
         <v>0</v>
       </c>
       <c r="Q614" t="n">
-        <v>18.52</v>
+        <v>23.35</v>
       </c>
       <c r="R614" t="n">
         <v>0</v>
@@ -50476,14 +50536,14 @@
       </c>
       <c r="O616" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P616" t="n">
         <v>100</v>
       </c>
       <c r="Q616" t="n">
-        <v>80.25</v>
+        <v>83.33</v>
       </c>
       <c r="R616" t="n">
         <v>9</v>
@@ -50562,7 +50622,7 @@
         <v>0</v>
       </c>
       <c r="Q617" t="n">
-        <v>18.52</v>
+        <v>23.35</v>
       </c>
       <c r="R617" t="n">
         <v>0</v>
@@ -50641,7 +50701,7 @@
         <v>0</v>
       </c>
       <c r="Q618" t="n">
-        <v>18.52</v>
+        <v>23.35</v>
       </c>
       <c r="R618" t="n">
         <v>0</v>
@@ -50796,14 +50856,14 @@
       </c>
       <c r="O620" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P620" t="n">
         <v>100</v>
       </c>
       <c r="Q620" t="n">
-        <v>80.25</v>
+        <v>83.33</v>
       </c>
       <c r="R620" t="n">
         <v>9</v>
@@ -50882,7 +50942,7 @@
         <v>0</v>
       </c>
       <c r="Q621" t="n">
-        <v>18.52</v>
+        <v>23.35</v>
       </c>
       <c r="R621" t="n">
         <v>0</v>
@@ -50961,7 +51021,7 @@
         <v>0</v>
       </c>
       <c r="Q622" t="n">
-        <v>18.52</v>
+        <v>23.35</v>
       </c>
       <c r="R622" t="n">
         <v>0</v>
@@ -51116,14 +51176,14 @@
       </c>
       <c r="O624" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P624" t="n">
         <v>100</v>
       </c>
       <c r="Q624" t="n">
-        <v>80.25</v>
+        <v>83.33</v>
       </c>
       <c r="R624" t="n">
         <v>9</v>
@@ -51202,7 +51262,7 @@
         <v>0</v>
       </c>
       <c r="Q625" t="n">
-        <v>18.52</v>
+        <v>23.35</v>
       </c>
       <c r="R625" t="n">
         <v>0</v>
@@ -51281,7 +51341,7 @@
         <v>0</v>
       </c>
       <c r="Q626" t="n">
-        <v>18.52</v>
+        <v>23.35</v>
       </c>
       <c r="R626" t="n">
         <v>0</v>
@@ -51436,14 +51496,14 @@
       </c>
       <c r="O628" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P628" t="n">
         <v>100</v>
       </c>
       <c r="Q628" t="n">
-        <v>80.25</v>
+        <v>83.33</v>
       </c>
       <c r="R628" t="n">
         <v>9</v>
@@ -51522,7 +51582,7 @@
         <v>0</v>
       </c>
       <c r="Q629" t="n">
-        <v>18.52</v>
+        <v>23.35</v>
       </c>
       <c r="R629" t="n">
         <v>0</v>
@@ -51601,7 +51661,7 @@
         <v>0</v>
       </c>
       <c r="Q630" t="n">
-        <v>18.52</v>
+        <v>23.35</v>
       </c>
       <c r="R630" t="n">
         <v>0</v>
@@ -51756,14 +51816,14 @@
       </c>
       <c r="O632" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P632" t="n">
         <v>100</v>
       </c>
       <c r="Q632" t="n">
-        <v>80.25</v>
+        <v>83.33</v>
       </c>
       <c r="R632" t="n">
         <v>9</v>
@@ -51842,7 +51902,7 @@
         <v>0</v>
       </c>
       <c r="Q633" t="n">
-        <v>18.52</v>
+        <v>23.35</v>
       </c>
       <c r="R633" t="n">
         <v>0</v>
@@ -51921,7 +51981,7 @@
         <v>0</v>
       </c>
       <c r="Q634" t="n">
-        <v>18.52</v>
+        <v>23.35</v>
       </c>
       <c r="R634" t="n">
         <v>0</v>
@@ -52076,14 +52136,14 @@
       </c>
       <c r="O636" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P636" t="n">
         <v>100</v>
       </c>
       <c r="Q636" t="n">
-        <v>80.25</v>
+        <v>83.33</v>
       </c>
       <c r="R636" t="n">
         <v>9</v>
@@ -52162,7 +52222,7 @@
         <v>0</v>
       </c>
       <c r="Q637" t="n">
-        <v>18.52</v>
+        <v>23.35</v>
       </c>
       <c r="R637" t="n">
         <v>0</v>
@@ -52241,7 +52301,7 @@
         <v>0</v>
       </c>
       <c r="Q638" t="n">
-        <v>18.52</v>
+        <v>23.35</v>
       </c>
       <c r="R638" t="n">
         <v>0</v>
@@ -52396,14 +52456,14 @@
       </c>
       <c r="O640" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P640" t="n">
         <v>100</v>
       </c>
       <c r="Q640" t="n">
-        <v>80.25</v>
+        <v>83.33</v>
       </c>
       <c r="R640" t="n">
         <v>9</v>
@@ -52482,7 +52542,7 @@
         <v>0</v>
       </c>
       <c r="Q641" t="n">
-        <v>18.52</v>
+        <v>23.35</v>
       </c>
       <c r="R641" t="n">
         <v>0</v>
@@ -52561,7 +52621,7 @@
         <v>0</v>
       </c>
       <c r="Q642" t="n">
-        <v>18.52</v>
+        <v>23.35</v>
       </c>
       <c r="R642" t="n">
         <v>0</v>
@@ -52716,14 +52776,14 @@
       </c>
       <c r="O644" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P644" t="n">
         <v>100</v>
       </c>
       <c r="Q644" t="n">
-        <v>80.25</v>
+        <v>83.33</v>
       </c>
       <c r="R644" t="n">
         <v>9</v>
@@ -52802,7 +52862,7 @@
         <v>0</v>
       </c>
       <c r="Q645" t="n">
-        <v>18.52</v>
+        <v>23.35</v>
       </c>
       <c r="R645" t="n">
         <v>0</v>
@@ -52881,7 +52941,7 @@
         <v>0</v>
       </c>
       <c r="Q646" t="n">
-        <v>18.52</v>
+        <v>23.35</v>
       </c>
       <c r="R646" t="n">
         <v>0</v>
@@ -53036,13 +53096,13 @@
       </c>
       <c r="O648" t="inlineStr"/>
       <c r="P648" t="n">
-        <v>44.4</v>
+        <v>55.6</v>
       </c>
       <c r="Q648" t="n">
-        <v>80.25</v>
+        <v>83.33</v>
       </c>
       <c r="R648" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S648" t="n">
         <v>9</v>
@@ -53118,7 +53178,7 @@
         <v>0</v>
       </c>
       <c r="Q649" t="n">
-        <v>18.52</v>
+        <v>23.35</v>
       </c>
       <c r="R649" t="n">
         <v>0</v>
@@ -53197,7 +53257,7 @@
         <v>0</v>
       </c>
       <c r="Q650" t="n">
-        <v>18.52</v>
+        <v>23.35</v>
       </c>
       <c r="R650" t="n">
         <v>0</v>
@@ -53352,13 +53412,13 @@
       </c>
       <c r="O652" t="inlineStr"/>
       <c r="P652" t="n">
-        <v>11.1</v>
+        <v>22.2</v>
       </c>
       <c r="Q652" t="n">
-        <v>80.25</v>
+        <v>83.33</v>
       </c>
       <c r="R652" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S652" t="n">
         <v>9</v>
@@ -53434,7 +53494,7 @@
         <v>0</v>
       </c>
       <c r="Q653" t="n">
-        <v>18.52</v>
+        <v>23.35</v>
       </c>
       <c r="R653" t="n">
         <v>0</v>
@@ -53513,7 +53573,7 @@
         <v>0</v>
       </c>
       <c r="Q654" t="n">
-        <v>18.52</v>
+        <v>23.35</v>
       </c>
       <c r="R654" t="n">
         <v>0</v>
@@ -53668,13 +53728,13 @@
       </c>
       <c r="O656" t="inlineStr"/>
       <c r="P656" t="n">
-        <v>11.1</v>
+        <v>22.2</v>
       </c>
       <c r="Q656" t="n">
-        <v>80.25</v>
+        <v>83.33</v>
       </c>
       <c r="R656" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S656" t="n">
         <v>9</v>
@@ -53750,7 +53810,7 @@
         <v>0</v>
       </c>
       <c r="Q657" t="n">
-        <v>18.52</v>
+        <v>23.35</v>
       </c>
       <c r="R657" t="n">
         <v>0</v>
@@ -53829,7 +53889,7 @@
         <v>0</v>
       </c>
       <c r="Q658" t="n">
-        <v>18.52</v>
+        <v>23.35</v>
       </c>
       <c r="R658" t="n">
         <v>0</v>
@@ -53984,13 +54044,13 @@
       </c>
       <c r="O660" t="inlineStr"/>
       <c r="P660" t="n">
-        <v>11.1</v>
+        <v>22.2</v>
       </c>
       <c r="Q660" t="n">
-        <v>80.25</v>
+        <v>83.33</v>
       </c>
       <c r="R660" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S660" t="n">
         <v>9</v>
@@ -54066,7 +54126,7 @@
         <v>0</v>
       </c>
       <c r="Q661" t="n">
-        <v>18.52</v>
+        <v>23.35</v>
       </c>
       <c r="R661" t="n">
         <v>0</v>
@@ -54145,7 +54205,7 @@
         <v>0</v>
       </c>
       <c r="Q662" t="n">
-        <v>18.52</v>
+        <v>23.35</v>
       </c>
       <c r="R662" t="n">
         <v>0</v>
@@ -54300,10 +54360,10 @@
       </c>
       <c r="O664" t="inlineStr"/>
       <c r="P664" t="n">
-        <v>80.2</v>
+        <v>83.3</v>
       </c>
       <c r="Q664" t="n">
-        <v>80.25</v>
+        <v>83.33</v>
       </c>
       <c r="R664" t="n">
         <v>1</v>
@@ -54379,10 +54439,10 @@
       </c>
       <c r="O665" t="inlineStr"/>
       <c r="P665" t="n">
-        <v>18.5</v>
+        <v>23.4</v>
       </c>
       <c r="Q665" t="n">
-        <v>18.52</v>
+        <v>23.35</v>
       </c>
       <c r="R665" t="n">
         <v>0</v>
@@ -54458,10 +54518,10 @@
       </c>
       <c r="O666" t="inlineStr"/>
       <c r="P666" t="n">
-        <v>18.5</v>
+        <v>23.4</v>
       </c>
       <c r="Q666" t="n">
-        <v>18.52</v>
+        <v>23.35</v>
       </c>
       <c r="R666" t="n">
         <v>0</v>
@@ -54537,14 +54597,14 @@
       </c>
       <c r="O667" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P667" t="n">
         <v>100</v>
       </c>
       <c r="Q667" t="n">
-        <v>69.45</v>
+        <v>71.3</v>
       </c>
       <c r="R667" t="n">
         <v>12</v>
@@ -54620,7 +54680,7 @@
       </c>
       <c r="O668" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P668" t="n">
@@ -54703,7 +54763,7 @@
       </c>
       <c r="O669" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P669" t="n">
@@ -54786,7 +54846,7 @@
       </c>
       <c r="O670" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P670" t="n">
@@ -54869,7 +54929,7 @@
       </c>
       <c r="O671" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P671" t="n">
@@ -54952,7 +55012,7 @@
       </c>
       <c r="O672" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P672" t="n">
@@ -55035,14 +55095,14 @@
       </c>
       <c r="O673" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P673" t="n">
         <v>100</v>
       </c>
       <c r="Q673" t="n">
-        <v>69.45</v>
+        <v>71.3</v>
       </c>
       <c r="R673" t="n">
         <v>12</v>
@@ -55118,7 +55178,7 @@
       </c>
       <c r="O674" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P674" t="n">
@@ -55201,7 +55261,7 @@
       </c>
       <c r="O675" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P675" t="n">
@@ -55363,7 +55423,7 @@
       </c>
       <c r="O677" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P677" t="n">
@@ -55525,13 +55585,13 @@
       </c>
       <c r="O679" t="inlineStr"/>
       <c r="P679" t="n">
-        <v>8.300000000000001</v>
+        <v>41.7</v>
       </c>
       <c r="Q679" t="n">
-        <v>69.45</v>
+        <v>71.3</v>
       </c>
       <c r="R679" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S679" t="n">
         <v>12</v>
@@ -56019,13 +56079,13 @@
       </c>
       <c r="O685" t="inlineStr"/>
       <c r="P685" t="n">
-        <v>8.300000000000001</v>
+        <v>41.7</v>
       </c>
       <c r="Q685" t="n">
-        <v>69.45</v>
+        <v>71.3</v>
       </c>
       <c r="R685" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S685" t="n">
         <v>12</v>
@@ -56505,14 +56565,14 @@
       </c>
       <c r="O691" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P691" t="n">
         <v>100</v>
       </c>
       <c r="Q691" t="n">
-        <v>69.45</v>
+        <v>71.3</v>
       </c>
       <c r="R691" t="n">
         <v>12</v>
@@ -56983,14 +57043,14 @@
       </c>
       <c r="O697" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P697" t="n">
         <v>100</v>
       </c>
       <c r="Q697" t="n">
-        <v>69.45</v>
+        <v>71.3</v>
       </c>
       <c r="R697" t="n">
         <v>12</v>
@@ -57461,14 +57521,14 @@
       </c>
       <c r="O703" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P703" t="n">
         <v>100</v>
       </c>
       <c r="Q703" t="n">
-        <v>69.45</v>
+        <v>71.3</v>
       </c>
       <c r="R703" t="n">
         <v>12</v>
@@ -57939,14 +57999,14 @@
       </c>
       <c r="O709" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P709" t="n">
         <v>100</v>
       </c>
       <c r="Q709" t="n">
-        <v>69.45</v>
+        <v>71.3</v>
       </c>
       <c r="R709" t="n">
         <v>12</v>
@@ -58424,7 +58484,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="Q715" t="n">
-        <v>69.45</v>
+        <v>71.3</v>
       </c>
       <c r="R715" t="n">
         <v>1</v>
@@ -58898,7 +58958,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="Q721" t="n">
-        <v>69.45</v>
+        <v>71.3</v>
       </c>
       <c r="R721" t="n">
         <v>1</v>
@@ -59372,7 +59432,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="Q727" t="n">
-        <v>69.45</v>
+        <v>71.3</v>
       </c>
       <c r="R727" t="n">
         <v>1</v>
@@ -59846,7 +59906,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="Q733" t="n">
-        <v>69.45</v>
+        <v>71.3</v>
       </c>
       <c r="R733" t="n">
         <v>1</v>
@@ -60320,7 +60380,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="Q739" t="n">
-        <v>69.45</v>
+        <v>71.3</v>
       </c>
       <c r="R739" t="n">
         <v>1</v>
@@ -60802,7 +60862,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="Q745" t="n">
-        <v>69.45</v>
+        <v>71.3</v>
       </c>
       <c r="R745" t="n">
         <v>1</v>
@@ -61276,7 +61336,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="Q751" t="n">
-        <v>69.45</v>
+        <v>71.3</v>
       </c>
       <c r="R751" t="n">
         <v>1</v>
@@ -61750,7 +61810,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="Q757" t="n">
-        <v>69.45</v>
+        <v>71.3</v>
       </c>
       <c r="R757" t="n">
         <v>1</v>
@@ -62221,10 +62281,10 @@
       </c>
       <c r="O763" t="inlineStr"/>
       <c r="P763" t="n">
-        <v>69.40000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="Q763" t="n">
-        <v>69.45</v>
+        <v>71.3</v>
       </c>
       <c r="R763" t="n">
         <v>1</v>
@@ -62695,14 +62755,14 @@
       </c>
       <c r="O769" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P769" t="n">
         <v>100</v>
       </c>
       <c r="Q769" t="n">
-        <v>31.48</v>
+        <v>24.07</v>
       </c>
       <c r="R769" t="n">
         <v>13</v>
@@ -62778,7 +62838,7 @@
       </c>
       <c r="O770" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P770" t="n">
@@ -62861,14 +62921,14 @@
       </c>
       <c r="O771" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P771" t="n">
         <v>100</v>
       </c>
       <c r="Q771" t="n">
-        <v>31.48</v>
+        <v>24.07</v>
       </c>
       <c r="R771" t="n">
         <v>13</v>
@@ -62944,7 +63004,7 @@
       </c>
       <c r="O772" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P772" t="n">
@@ -63030,7 +63090,7 @@
         <v>0</v>
       </c>
       <c r="Q773" t="n">
-        <v>31.48</v>
+        <v>24.07</v>
       </c>
       <c r="R773" t="n">
         <v>0</v>
@@ -63106,7 +63166,7 @@
       </c>
       <c r="O774" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P774" t="n">
@@ -63192,7 +63252,7 @@
         <v>0</v>
       </c>
       <c r="Q775" t="n">
-        <v>31.48</v>
+        <v>24.07</v>
       </c>
       <c r="R775" t="n">
         <v>0</v>
@@ -63268,7 +63328,7 @@
       </c>
       <c r="O776" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P776" t="n">
@@ -63354,7 +63414,7 @@
         <v>0</v>
       </c>
       <c r="Q777" t="n">
-        <v>31.48</v>
+        <v>24.07</v>
       </c>
       <c r="R777" t="n">
         <v>0</v>
@@ -63430,7 +63490,7 @@
       </c>
       <c r="O778" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P778" t="n">
@@ -63516,7 +63576,7 @@
         <v>0</v>
       </c>
       <c r="Q779" t="n">
-        <v>31.48</v>
+        <v>24.07</v>
       </c>
       <c r="R779" t="n">
         <v>0</v>
@@ -63592,7 +63652,7 @@
       </c>
       <c r="O780" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P780" t="n">
@@ -63678,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="Q781" t="n">
-        <v>31.48</v>
+        <v>24.07</v>
       </c>
       <c r="R781" t="n">
         <v>0</v>
@@ -63754,7 +63814,7 @@
       </c>
       <c r="O782" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P782" t="n">
@@ -63840,7 +63900,7 @@
         <v>0</v>
       </c>
       <c r="Q783" t="n">
-        <v>31.48</v>
+        <v>24.07</v>
       </c>
       <c r="R783" t="n">
         <v>0</v>
@@ -63916,7 +63976,7 @@
       </c>
       <c r="O784" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P784" t="n">
@@ -64002,7 +64062,7 @@
         <v>0</v>
       </c>
       <c r="Q785" t="n">
-        <v>31.48</v>
+        <v>24.07</v>
       </c>
       <c r="R785" t="n">
         <v>0</v>
@@ -64078,7 +64138,7 @@
       </c>
       <c r="O786" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P786" t="n">
@@ -64164,7 +64224,7 @@
         <v>0</v>
       </c>
       <c r="Q787" t="n">
-        <v>31.48</v>
+        <v>24.07</v>
       </c>
       <c r="R787" t="n">
         <v>0</v>
@@ -64240,7 +64300,7 @@
       </c>
       <c r="O788" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P788" t="n">
@@ -64326,7 +64386,7 @@
         <v>0</v>
       </c>
       <c r="Q789" t="n">
-        <v>31.48</v>
+        <v>24.07</v>
       </c>
       <c r="R789" t="n">
         <v>0</v>
@@ -64402,7 +64462,7 @@
       </c>
       <c r="O790" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P790" t="n">
@@ -64488,7 +64548,7 @@
         <v>0</v>
       </c>
       <c r="Q791" t="n">
-        <v>31.48</v>
+        <v>24.07</v>
       </c>
       <c r="R791" t="n">
         <v>0</v>
@@ -64564,7 +64624,7 @@
       </c>
       <c r="O792" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P792" t="n">
@@ -64650,7 +64710,7 @@
         <v>0</v>
       </c>
       <c r="Q793" t="n">
-        <v>31.48</v>
+        <v>24.07</v>
       </c>
       <c r="R793" t="n">
         <v>0</v>
@@ -64812,7 +64872,7 @@
         <v>0</v>
       </c>
       <c r="Q795" t="n">
-        <v>31.48</v>
+        <v>24.07</v>
       </c>
       <c r="R795" t="n">
         <v>0</v>
@@ -64974,7 +65034,7 @@
         <v>0</v>
       </c>
       <c r="Q797" t="n">
-        <v>31.48</v>
+        <v>24.07</v>
       </c>
       <c r="R797" t="n">
         <v>0</v>
@@ -65136,7 +65196,7 @@
         <v>0</v>
       </c>
       <c r="Q799" t="n">
-        <v>31.48</v>
+        <v>24.07</v>
       </c>
       <c r="R799" t="n">
         <v>0</v>
@@ -65295,10 +65355,10 @@
       </c>
       <c r="O801" t="inlineStr"/>
       <c r="P801" t="n">
-        <v>31.5</v>
+        <v>24.1</v>
       </c>
       <c r="Q801" t="n">
-        <v>31.48</v>
+        <v>24.07</v>
       </c>
       <c r="R801" t="n">
         <v>0</v>
@@ -65464,7 +65524,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>72.22</v>
+        <v>77.78</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -65494,7 +65554,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>72.22</v>
+        <v>77.78</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -65524,7 +65584,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>50</v>
+        <v>72.22</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -65554,7 +65614,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>61.11</v>
+        <v>72.22</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -65584,7 +65644,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>50</v>
+        <v>72.22</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -65614,7 +65674,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>61.11</v>
+        <v>72.22</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -65644,7 +65704,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>61.11</v>
+        <v>72.22</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -65674,7 +65734,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>55.56</v>
+        <v>72.22</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -65704,7 +65764,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>61.11</v>
+        <v>72.22</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -65734,7 +65794,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>50</v>
+        <v>72.22</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -65745,7 +65805,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BSIMB000503</t>
+          <t>BSIMB000754</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -65768,7 +65828,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>HOSPITAL COMUNITARIO DE LORETO</t>
+          <t>HOSPITAL GENERAL DE CIUDAD CONSTITUCIÓN</t>
         </is>
       </c>
     </row>
@@ -65805,7 +65865,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BSIMB000812</t>
+          <t>BSIMB000520</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -65824,18 +65884,18 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>77.78</v>
+        <v>72.22</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>HOSPITAL GENERAL DE SANTA ROSALÍA</t>
+          <t>UNEME HEMODIÁLISIS</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BSIMB000754</t>
+          <t>BSIMB000783</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -65858,14 +65918,14 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>HOSPITAL GENERAL DE CIUDAD CONSTITUCIÓN</t>
+          <t>HOSPITAL PSIQUIÁTRICO DE BAJA CALIFORNIA SUR</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BSIMB000346</t>
+          <t>BSIMB000672</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -65884,18 +65944,18 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>77.78</v>
+        <v>51.85</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>HOSPITAL GENERAL  RAÚL A. CARRILLO</t>
+          <t>B. HOSPITAL GENERAL CON ESPECIALIDADES JUAN MARÍA DE SALVATIERRA</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BSIMB000643</t>
+          <t>BSIMB000503</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -65918,14 +65978,14 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>HOSPITAL GENERAL DE CABO SAN LUCAS</t>
+          <t>HOSPITAL COMUNITARIO DE LORETO</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BSIMB000520</t>
+          <t>BSIMB000346</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -65944,18 +66004,18 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>72.22</v>
+        <v>77.78</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>UNEME HEMODIÁLISIS</t>
+          <t>HOSPITAL GENERAL  RAÚL A. CARRILLO</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BSIMB000783</t>
+          <t>BSIMB000643</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -65978,14 +66038,14 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>HOSPITAL PSIQUIÁTRICO DE BAJA CALIFORNIA SUR</t>
+          <t>HOSPITAL GENERAL DE CABO SAN LUCAS</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BSIMB000672</t>
+          <t>BSIMB000812</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -66004,11 +66064,11 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>48.15</v>
+        <v>77.78</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>B. HOSPITAL GENERAL CON ESPECIALIDADES JUAN MARÍA DE SALVATIERRA</t>
+          <t>HOSPITAL GENERAL DE SANTA ROSALÍA</t>
         </is>
       </c>
     </row>
@@ -66034,7 +66094,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>31.48</v>
+        <v>24.07</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -66064,7 +66124,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>31.48</v>
+        <v>24.07</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -66094,7 +66154,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>31.48</v>
+        <v>24.07</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -66124,7 +66184,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>31.48</v>
+        <v>24.07</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -66154,7 +66214,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>31.48</v>
+        <v>24.07</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -66184,7 +66244,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>31.48</v>
+        <v>24.07</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -66214,7 +66274,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>31.48</v>
+        <v>24.07</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -66244,7 +66304,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>31.48</v>
+        <v>24.07</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -66274,7 +66334,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>31.48</v>
+        <v>24.07</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -66304,7 +66364,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>31.48</v>
+        <v>24.07</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -66334,7 +66394,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>31.48</v>
+        <v>24.07</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -66364,7 +66424,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>31.48</v>
+        <v>24.07</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -66394,7 +66454,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>31.48</v>
+        <v>24.07</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -67794,7 +67854,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>72.22</v>
+        <v>83.33</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -67854,7 +67914,7 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>72.22</v>
+        <v>83.33</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -67914,7 +67974,7 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>72.22</v>
+        <v>88.89</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -68694,7 +68754,7 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>18.52</v>
+        <v>24.07</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -68724,7 +68784,7 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>25.93</v>
+        <v>24.07</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -68754,7 +68814,7 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>18.52</v>
+        <v>24.07</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -68784,7 +68844,7 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>18.52</v>
+        <v>24.07</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -68814,7 +68874,7 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>25.93</v>
+        <v>31.48</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -68844,7 +68904,7 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>18.52</v>
+        <v>24.07</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -68874,7 +68934,7 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>18.52</v>
+        <v>24.07</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -68904,7 +68964,7 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>18.52</v>
+        <v>24.07</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -68934,7 +68994,7 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>18.52</v>
+        <v>24.07</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -68964,7 +69024,7 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>18.52</v>
+        <v>24.07</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -68994,7 +69054,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>25.93</v>
+        <v>31.48</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -69024,7 +69084,7 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>18.52</v>
+        <v>24.07</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -69054,7 +69114,7 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>18.52</v>
+        <v>24.07</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -69084,7 +69144,7 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>18.52</v>
+        <v>24.07</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -69114,7 +69174,7 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>18.52</v>
+        <v>24.07</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -69144,7 +69204,7 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>25.93</v>
+        <v>31.48</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -69174,7 +69234,7 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>25.93</v>
+        <v>31.48</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -69204,7 +69264,7 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>18.52</v>
+        <v>24.07</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -69234,7 +69294,7 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>18.52</v>
+        <v>24.07</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -69264,7 +69324,7 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>25.93</v>
+        <v>31.48</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -69294,7 +69354,7 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>25.93</v>
+        <v>31.48</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -69324,7 +69384,7 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>18.52</v>
+        <v>24.07</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -69354,7 +69414,7 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>18.52</v>
+        <v>24.07</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -69384,7 +69444,7 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>18.52</v>
+        <v>24.07</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -69414,7 +69474,7 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>18.52</v>
+        <v>24.07</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -69444,7 +69504,7 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>18.52</v>
+        <v>24.07</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -69474,7 +69534,7 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>18.52</v>
+        <v>24.07</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -69504,7 +69564,7 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>18.52</v>
+        <v>24.07</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -69534,7 +69594,7 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>18.52</v>
+        <v>24.07</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -69564,7 +69624,7 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>18.52</v>
+        <v>24.07</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -69594,7 +69654,7 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>18.52</v>
+        <v>24.07</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -69624,7 +69684,7 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>18.52</v>
+        <v>24.07</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -69654,7 +69714,7 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>18.52</v>
+        <v>24.07</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -69684,7 +69744,7 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>25.93</v>
+        <v>31.48</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -69714,7 +69774,7 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>18.52</v>
+        <v>24.07</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -69744,7 +69804,7 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>25.93</v>
+        <v>31.48</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -69774,7 +69834,7 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>18.52</v>
+        <v>24.07</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -69804,7 +69864,7 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>25.93</v>
+        <v>31.48</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -69834,7 +69894,7 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>25.93</v>
+        <v>31.48</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -69864,7 +69924,7 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>18.52</v>
+        <v>24.07</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -69894,7 +69954,7 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>18.52</v>
+        <v>24.07</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -70838,7 +70898,7 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>66.67</v>
+        <v>72.22</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -70928,7 +70988,7 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>66.67</v>
+        <v>72.22</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -70958,7 +71018,7 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>66.67</v>
+        <v>72.22</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -71168,7 +71228,7 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>66.67</v>
+        <v>72.22</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -71258,7 +71318,7 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>66.67</v>
+        <v>72.22</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -71318,7 +71378,7 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>66.67</v>
+        <v>72.22</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -73718,7 +73778,7 @@
         </is>
       </c>
       <c r="E283" t="n">
-        <v>66.67</v>
+        <v>72.22</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -73748,7 +73808,7 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>66.67</v>
+        <v>72.22</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -73808,7 +73868,7 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>66.67</v>
+        <v>72.22</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -73838,7 +73898,7 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>66.67</v>
+        <v>72.22</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -75578,7 +75638,7 @@
         </is>
       </c>
       <c r="E345" t="n">
-        <v>25.93</v>
+        <v>24.07</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -75608,7 +75668,7 @@
         </is>
       </c>
       <c r="E346" t="n">
-        <v>25.93</v>
+        <v>24.07</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -75638,7 +75698,7 @@
         </is>
       </c>
       <c r="E347" t="n">
-        <v>25.93</v>
+        <v>24.07</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -75668,7 +75728,7 @@
         </is>
       </c>
       <c r="E348" t="n">
-        <v>25.93</v>
+        <v>24.07</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -75698,7 +75758,7 @@
         </is>
       </c>
       <c r="E349" t="n">
-        <v>25.93</v>
+        <v>24.07</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -75728,7 +75788,7 @@
         </is>
       </c>
       <c r="E350" t="n">
-        <v>25.93</v>
+        <v>24.07</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -75758,7 +75818,7 @@
         </is>
       </c>
       <c r="E351" t="n">
-        <v>25.93</v>
+        <v>24.07</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -75788,7 +75848,7 @@
         </is>
       </c>
       <c r="E352" t="n">
-        <v>25.93</v>
+        <v>24.07</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -75818,7 +75878,7 @@
         </is>
       </c>
       <c r="E353" t="n">
-        <v>25.93</v>
+        <v>24.07</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -75848,7 +75908,7 @@
         </is>
       </c>
       <c r="E354" t="n">
-        <v>25.93</v>
+        <v>24.07</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -75859,7 +75919,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>PLIMB000100</t>
+          <t>PLIMB001780</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -75869,27 +75929,27 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Puebla (2)</t>
+          <t>Puebla (1)</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>Célula 7</t>
+          <t>Célula 5</t>
         </is>
       </c>
       <c r="E355" t="n">
-        <v>18.52</v>
+        <v>24.07</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>HOSPITAL COMUNITARIO AHUACATLÁN</t>
+          <t>HOSPITAL GENERAL DR EDUARDO VAZQUEZ N</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>PLIMB000351</t>
+          <t>PLIMB001792</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -75899,27 +75959,27 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Puebla (2)</t>
+          <t>Puebla (1)</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>Célula 7</t>
+          <t>Célula 5</t>
         </is>
       </c>
       <c r="E356" t="n">
-        <v>18.52</v>
+        <v>24.07</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>HOSPITAL COMUNITARIO DE AYOTOXCO</t>
+          <t>HOSPITAL PSIQUIÁTRICO DR. RAFAEL SERRANO</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>PLIMB000602</t>
+          <t>PLIMB002516</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -75929,27 +75989,27 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Puebla (2)</t>
+          <t>Puebla (1)</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>Célula 7</t>
+          <t>Célula 5</t>
         </is>
       </c>
       <c r="E357" t="n">
-        <v>18.52</v>
+        <v>24.07</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>HOSPITAL COMUNITARIO CUYOACO</t>
+          <t>HOSPITAL GENERAL TEHUACAN</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>PLIMB000626</t>
+          <t>PLIMB003706</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -75959,27 +76019,27 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Puebla (2)</t>
+          <t>Puebla (1)</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>Célula 7</t>
+          <t>Célula 5</t>
         </is>
       </c>
       <c r="E358" t="n">
-        <v>18.52</v>
+        <v>24.07</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>HOSPITAL GENERAL CIUDAD SERDÁN</t>
+          <t>HOSPITAL COMUNITARIO ZOQUITLAN</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>PLIMB001121</t>
+          <t>PLIMB004126</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -75989,27 +76049,27 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Puebla (2)</t>
+          <t>Puebla (1)</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>Célula 7</t>
+          <t>Célula 5</t>
         </is>
       </c>
       <c r="E359" t="n">
-        <v>18.52</v>
+        <v>24.07</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>HOSPITAL COMUNITARIO HUEHUETLA</t>
+          <t>HOSPITAL DE LA MUJER</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>PLIMB001285</t>
+          <t>PLIMB004131</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -76019,27 +76079,27 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Puebla (2)</t>
+          <t>Puebla (1)</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>Célula 7</t>
+          <t>Célula 5</t>
         </is>
       </c>
       <c r="E360" t="n">
-        <v>18.52</v>
+        <v>24.07</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>HOSPITAL COMUNITARIO  IXTACAMAXTITLAN</t>
+          <t>HOSPITAL COMUNITARIO VICENTE GUERRERO</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>PLIMB001536</t>
+          <t>PLIMB004143</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -76049,27 +76109,27 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Puebla (2)</t>
+          <t>Puebla (1)</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>Célula 7</t>
+          <t>Célula 5</t>
         </is>
       </c>
       <c r="E361" t="n">
-        <v>18.52</v>
+        <v>24.07</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>HOSPITAL GENERAL DE LIBRES</t>
+          <t>HOSPITAL COMUNITARIO TLACOTEPEC DE PORFIRÍO DÍAZ</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>PLIMB001710</t>
+          <t>PLIMB004172</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -76079,12 +76139,12 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Puebla (2)</t>
+          <t>Puebla (1)</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Célula 7</t>
+          <t>Célula 5</t>
         </is>
       </c>
       <c r="E362" t="n">
@@ -76092,14 +76152,14 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>HOSPITAL COMUNITARIO CUACNOPALAN</t>
+          <t>UNIDAD DE ONCOLOGÍA</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>PLIMB001780</t>
+          <t>PLIMB004720</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -76118,18 +76178,18 @@
         </is>
       </c>
       <c r="E363" t="n">
-        <v>18.52</v>
+        <v>24.07</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>HOSPITAL GENERAL DR EDUARDO VAZQUEZ N</t>
+          <t>HOSPITAL DE LA MUJER Y NEONATOLOGÍA</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>PLIMB001792</t>
+          <t>PLIMB005012</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -76148,18 +76208,18 @@
         </is>
       </c>
       <c r="E364" t="n">
-        <v>18.52</v>
+        <v>24.07</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>HOSPITAL PSIQUIÁTRICO DR. RAFAEL SERRANO</t>
+          <t>HOSPITAL GENERAL DE ACATLÁN DE OSORIO</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>PLIMB002516</t>
+          <t>PLIMB005321</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -76178,18 +76238,18 @@
         </is>
       </c>
       <c r="E365" t="n">
-        <v>18.52</v>
+        <v>24.07</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>HOSPITAL GENERAL TEHUACAN</t>
+          <t>HOSPITAL GENERAL DE HUEJOTZINGO</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>PLIMB003571</t>
+          <t>PLIMB005613</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -76199,27 +76259,27 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Puebla (2)</t>
+          <t>Puebla (1)</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>Célula 7</t>
+          <t>Célula 5</t>
         </is>
       </c>
       <c r="E366" t="n">
-        <v>18.52</v>
+        <v>24.07</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>HOSPITAL INTEGRAL ZAPOTITLAN DE MENDEZ</t>
+          <t>HOSPITAL GENERAL DE ATLIXCO GONZALO RÍO ARRONTE</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>PLIMB003706</t>
+          <t>PLIMB005700</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -76238,18 +76298,18 @@
         </is>
       </c>
       <c r="E367" t="n">
-        <v>18.52</v>
+        <v>24.07</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>HOSPITAL COMUNITARIO ZOQUITLAN</t>
+          <t>HOSPITAL DE TRAUMATOLOGÍA Y ORTOPEDIA DOCTOR Y GENERAL RAFAEL MORENO VALLE</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>PLIMB004020</t>
+          <t>PLIMB007083</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -76259,27 +76319,27 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Puebla (2)</t>
+          <t>Puebla (1)</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>Célula 7</t>
+          <t>Célula 5</t>
         </is>
       </c>
       <c r="E368" t="n">
-        <v>18.52</v>
+        <v>24.07</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>HOSPITAL COMUNITARIO TLAOLA</t>
+          <t>HOSPITAL GENERAL DE IZUCAR DE MATAMOROS</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>PLIMB004056</t>
+          <t>PLIMB007095</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -76289,27 +76349,27 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Puebla (2)</t>
+          <t>Puebla (1)</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>Célula 7</t>
+          <t>Célula 5</t>
         </is>
       </c>
       <c r="E369" t="n">
-        <v>18.52</v>
+        <v>24.07</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>HOSPITAL COMUNITARIO ACATZINGO</t>
+          <t>HOSPITAL COMUNITARIO ZACAPALA</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>PLIMB004102</t>
+          <t>PLIMB000100</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -76328,18 +76388,18 @@
         </is>
       </c>
       <c r="E370" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>HOSPITAL COMUNITARIO MECAPALAPA</t>
+          <t>HOSPITAL COMUNITARIO AHUACATLÁN</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>PLIMB004126</t>
+          <t>PLIMB000351</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -76349,27 +76409,27 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Puebla (1)</t>
+          <t>Puebla (2)</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Célula 5</t>
+          <t>Célula 7</t>
         </is>
       </c>
       <c r="E371" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LA MUJER</t>
+          <t>HOSPITAL COMUNITARIO DE AYOTOXCO</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>PLIMB004131</t>
+          <t>PLIMB000602</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -76379,27 +76439,27 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Puebla (1)</t>
+          <t>Puebla (2)</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>Célula 5</t>
+          <t>Célula 7</t>
         </is>
       </c>
       <c r="E372" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>HOSPITAL COMUNITARIO VICENTE GUERRERO</t>
+          <t>HOSPITAL COMUNITARIO CUYOACO</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>PLIMB004143</t>
+          <t>PLIMB000626</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -76409,27 +76469,27 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Puebla (1)</t>
+          <t>Puebla (2)</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>Célula 5</t>
+          <t>Célula 7</t>
         </is>
       </c>
       <c r="E373" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>HOSPITAL COMUNITARIO TLACOTEPEC DE PORFIRÍO DÍAZ</t>
+          <t>HOSPITAL GENERAL CIUDAD SERDÁN</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>PLIMB004172</t>
+          <t>PLIMB001121</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -76439,27 +76499,27 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Puebla (1)</t>
+          <t>Puebla (2)</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>Célula 5</t>
+          <t>Célula 7</t>
         </is>
       </c>
       <c r="E374" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>UNIDAD DE ONCOLOGÍA</t>
+          <t>HOSPITAL COMUNITARIO HUEHUETLA</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>PLIMB004242</t>
+          <t>PLIMB001285</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -76478,18 +76538,18 @@
         </is>
       </c>
       <c r="E375" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>HOSPITAL INTEGRAL GUADALUPE VICTORIA</t>
+          <t>HOSPITAL COMUNITARIO  IXTACAMAXTITLAN</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>PLIMB004720</t>
+          <t>PLIMB001536</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -76499,27 +76559,27 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Puebla (1)</t>
+          <t>Puebla (2)</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>Célula 5</t>
+          <t>Célula 7</t>
         </is>
       </c>
       <c r="E376" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LA MUJER Y NEONATOLOGÍA</t>
+          <t>HOSPITAL GENERAL DE LIBRES</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>PLIMB004732</t>
+          <t>PLIMB001710</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -76538,18 +76598,18 @@
         </is>
       </c>
       <c r="E377" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>HOSPITAL INTEGRAL ZACAPOAXTLA</t>
+          <t>HOSPITAL COMUNITARIO CUACNOPALAN</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>PLIMB004925</t>
+          <t>PLIMB003571</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -76568,18 +76628,18 @@
         </is>
       </c>
       <c r="E378" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>HOSPITAL GENERAL DE TEZIUTLÁN</t>
+          <t>HOSPITAL INTEGRAL ZAPOTITLAN DE MENDEZ</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>PLIMB004954</t>
+          <t>PLIMB004020</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -76598,18 +76658,18 @@
         </is>
       </c>
       <c r="E379" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>HOSPITAL INTEGRAL SAN JOSÉ CHIAPA</t>
+          <t>HOSPITAL COMUNITARIO TLAOLA</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>PLIMB005012</t>
+          <t>PLIMB004056</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -76619,27 +76679,27 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Puebla (1)</t>
+          <t>Puebla (2)</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>Célula 5</t>
+          <t>Célula 7</t>
         </is>
       </c>
       <c r="E380" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>HOSPITAL GENERAL DE ACATLÁN DE OSORIO</t>
+          <t>HOSPITAL COMUNITARIO ACATZINGO</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>PLIMB005070</t>
+          <t>PLIMB004102</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -76658,18 +76718,18 @@
         </is>
       </c>
       <c r="E381" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>HOSPITAL GENERAL TLATLAUQUITEPEC</t>
+          <t>HOSPITAL COMUNITARIO MECAPALAPA</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>PLIMB005263</t>
+          <t>PLIMB004242</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -76688,18 +76748,18 @@
         </is>
       </c>
       <c r="E382" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>HOSPITAL INTEGRAL ACAJETE-TEPETZALA</t>
+          <t>HOSPITAL INTEGRAL GUADALUPE VICTORIA</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>PLIMB005321</t>
+          <t>PLIMB004732</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -76709,27 +76769,27 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Puebla (1)</t>
+          <t>Puebla (2)</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>Célula 5</t>
+          <t>Célula 7</t>
         </is>
       </c>
       <c r="E383" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>HOSPITAL GENERAL DE HUEJOTZINGO</t>
+          <t>HOSPITAL INTEGRAL ZACAPOAXTLA</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>PLIMB005555</t>
+          <t>PLIMB004925</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -76748,18 +76808,18 @@
         </is>
       </c>
       <c r="E384" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>HOSPITAL INTEGRAL PALMAR DE BRAVO</t>
+          <t>HOSPITAL GENERAL DE TEZIUTLÁN</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>PLIMB005601</t>
+          <t>PLIMB004954</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -76778,18 +76838,18 @@
         </is>
       </c>
       <c r="E385" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>HOSPITAL INTEGRAL DE XICOTEPEC</t>
+          <t>HOSPITAL INTEGRAL SAN JOSÉ CHIAPA</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>PLIMB005613</t>
+          <t>PLIMB005070</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -76799,27 +76859,27 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Puebla (1)</t>
+          <t>Puebla (2)</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>Célula 5</t>
+          <t>Célula 7</t>
         </is>
       </c>
       <c r="E386" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>HOSPITAL GENERAL DE ATLIXCO GONZALO RÍO ARRONTE</t>
+          <t>HOSPITAL GENERAL TLATLAUQUITEPEC</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>PLIMB005700</t>
+          <t>PLIMB005263</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -76829,27 +76889,27 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Puebla (1)</t>
+          <t>Puebla (2)</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>Célula 5</t>
+          <t>Célula 7</t>
         </is>
       </c>
       <c r="E387" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>HOSPITAL DE TRAUMATOLOGÍA Y ORTOPEDIA DOCTOR Y GENERAL RAFAEL MORENO VALLE</t>
+          <t>HOSPITAL INTEGRAL ACAJETE-TEPETZALA</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>PLIMB005794</t>
+          <t>PLIMB005555</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -76868,18 +76928,18 @@
         </is>
       </c>
       <c r="E388" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>HOSPITAL COMUNITARIO QUIMIXTLAN</t>
+          <t>HOSPITAL INTEGRAL PALMAR DE BRAVO</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>PLIMB006016</t>
+          <t>PLIMB005601</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -76898,18 +76958,18 @@
         </is>
       </c>
       <c r="E389" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>HOSPITAL GENERAL DE TEPEACA</t>
+          <t>HOSPITAL INTEGRAL DE XICOTEPEC</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>PLIMB006103</t>
+          <t>PLIMB005794</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -76928,18 +76988,18 @@
         </is>
       </c>
       <c r="E390" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>HOSPITAL GENERAL DE ZACATLÁN</t>
+          <t>HOSPITAL COMUNITARIO QUIMIXTLAN</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>PLIMB006885</t>
+          <t>PLIMB006016</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -76958,18 +77018,18 @@
         </is>
       </c>
       <c r="E391" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>HOSPITAL GENERAL HUAUCHINANGO</t>
+          <t>HOSPITAL GENERAL DE TEPEACA</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>PLIMB007083</t>
+          <t>PLIMB006103</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -76979,27 +77039,27 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Puebla (1)</t>
+          <t>Puebla (2)</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>Célula 5</t>
+          <t>Célula 7</t>
         </is>
       </c>
       <c r="E392" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>HOSPITAL GENERAL DE IZUCAR DE MATAMOROS</t>
+          <t>HOSPITAL GENERAL DE ZACATLÁN</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>PLIMB007095</t>
+          <t>PLIMB006885</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -77009,20 +77069,20 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Puebla (1)</t>
+          <t>Puebla (2)</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>Célula 5</t>
+          <t>Célula 7</t>
         </is>
       </c>
       <c r="E393" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>HOSPITAL COMUNITARIO ZACAPALA</t>
+          <t>HOSPITAL GENERAL HUAUCHINANGO</t>
         </is>
       </c>
     </row>
@@ -77048,7 +77108,7 @@
         </is>
       </c>
       <c r="E394" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -77078,7 +77138,7 @@
         </is>
       </c>
       <c r="E395" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -77108,7 +77168,7 @@
         </is>
       </c>
       <c r="E396" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -77138,7 +77198,7 @@
         </is>
       </c>
       <c r="E397" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -77168,7 +77228,7 @@
         </is>
       </c>
       <c r="E398" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -77588,7 +77648,7 @@
         </is>
       </c>
       <c r="E412" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -77618,7 +77678,7 @@
         </is>
       </c>
       <c r="E413" t="n">
-        <v>18.52</v>
+        <v>24.07</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -77648,7 +77708,7 @@
         </is>
       </c>
       <c r="E414" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -77678,7 +77738,7 @@
         </is>
       </c>
       <c r="E415" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -77708,7 +77768,7 @@
         </is>
       </c>
       <c r="E416" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -77738,7 +77798,7 @@
         </is>
       </c>
       <c r="E417" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -77768,7 +77828,7 @@
         </is>
       </c>
       <c r="E418" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -77798,7 +77858,7 @@
         </is>
       </c>
       <c r="E419" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -77828,7 +77888,7 @@
         </is>
       </c>
       <c r="E420" t="n">
-        <v>18.52</v>
+        <v>24.07</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -77858,7 +77918,7 @@
         </is>
       </c>
       <c r="E421" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -77888,7 +77948,7 @@
         </is>
       </c>
       <c r="E422" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -77918,7 +77978,7 @@
         </is>
       </c>
       <c r="E423" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -77948,7 +78008,7 @@
         </is>
       </c>
       <c r="E424" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -77978,7 +78038,7 @@
         </is>
       </c>
       <c r="E425" t="n">
-        <v>18.52</v>
+        <v>24.07</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -78008,7 +78068,7 @@
         </is>
       </c>
       <c r="E426" t="n">
-        <v>18.52</v>
+        <v>31.48</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -78038,7 +78098,7 @@
         </is>
       </c>
       <c r="E427" t="n">
-        <v>25.93</v>
+        <v>44.44</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -78278,7 +78338,7 @@
         </is>
       </c>
       <c r="E435" t="n">
-        <v>25.93</v>
+        <v>33.33</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -78409,7 +78469,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>SLIMB002230</t>
+          <t>SLIMB002242</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -78428,18 +78488,18 @@
         </is>
       </c>
       <c r="E440" t="n">
-        <v>18.52</v>
+        <v>55.56</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>HOSPITAL PEDIÁTRICO DE SINALOA</t>
+          <t>HOSPITAL INTEGRAL VALLE DEL CARRIZO</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>SLIMB002242</t>
+          <t>SLIMB002254</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -78458,18 +78518,18 @@
         </is>
       </c>
       <c r="E441" t="n">
-        <v>55.56</v>
+        <v>18.52</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>HOSPITAL INTEGRAL VALLE DEL CARRIZO</t>
+          <t>HOSPITAL GENERAL DE MAZATLÁN</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>SLIMB002254</t>
+          <t>SLIMB002464</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -78492,14 +78552,14 @@
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>HOSPITAL GENERAL DE MAZATLÁN</t>
+          <t>HOSPITAL INTEGRAL SAN IGNACIO</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>SLIMB002464</t>
+          <t>SLIMB002230</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -78518,11 +78578,11 @@
         </is>
       </c>
       <c r="E443" t="n">
-        <v>18.52</v>
+        <v>25.93</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>HOSPITAL INTEGRAL SAN IGNACIO</t>
+          <t>HOSPITAL PEDIÁTRICO DE SINALOA</t>
         </is>
       </c>
     </row>
@@ -78698,7 +78758,7 @@
         </is>
       </c>
       <c r="E449" t="n">
-        <v>25.93</v>
+        <v>50</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -79388,7 +79448,7 @@
         </is>
       </c>
       <c r="E472" t="n">
-        <v>18.52</v>
+        <v>25.93</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -79418,7 +79478,7 @@
         </is>
       </c>
       <c r="E473" t="n">
-        <v>18.52</v>
+        <v>25.93</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -79448,7 +79508,7 @@
         </is>
       </c>
       <c r="E474" t="n">
-        <v>18.52</v>
+        <v>25.93</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -79478,7 +79538,7 @@
         </is>
       </c>
       <c r="E475" t="n">
-        <v>18.52</v>
+        <v>25.93</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -79508,7 +79568,7 @@
         </is>
       </c>
       <c r="E476" t="n">
-        <v>18.52</v>
+        <v>25.93</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -79628,7 +79688,7 @@
         </is>
       </c>
       <c r="E480" t="n">
-        <v>18.52</v>
+        <v>25.93</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -79658,7 +79718,7 @@
         </is>
       </c>
       <c r="E481" t="n">
-        <v>18.52</v>
+        <v>25.93</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -79688,7 +79748,7 @@
         </is>
       </c>
       <c r="E482" t="n">
-        <v>18.52</v>
+        <v>25.93</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -79718,7 +79778,7 @@
         </is>
       </c>
       <c r="E483" t="n">
-        <v>18.52</v>
+        <v>25.93</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -79808,7 +79868,7 @@
         </is>
       </c>
       <c r="E486" t="n">
-        <v>18.52</v>
+        <v>25.93</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -79838,7 +79898,7 @@
         </is>
       </c>
       <c r="E487" t="n">
-        <v>18.52</v>
+        <v>25.93</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -79868,7 +79928,7 @@
         </is>
       </c>
       <c r="E488" t="n">
-        <v>18.52</v>
+        <v>25.93</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -79898,7 +79958,7 @@
         </is>
       </c>
       <c r="E489" t="n">
-        <v>18.52</v>
+        <v>25.93</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -79928,7 +79988,7 @@
         </is>
       </c>
       <c r="E490" t="n">
-        <v>18.52</v>
+        <v>25.93</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -79958,7 +80018,7 @@
         </is>
       </c>
       <c r="E491" t="n">
-        <v>18.52</v>
+        <v>25.93</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -81338,7 +81398,7 @@
         </is>
       </c>
       <c r="E537" t="n">
-        <v>31.48</v>
+        <v>61.11</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -81878,7 +81938,7 @@
         </is>
       </c>
       <c r="E555" t="n">
-        <v>31.48</v>
+        <v>61.11</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -82358,7 +82418,7 @@
         </is>
       </c>
       <c r="E571" t="n">
-        <v>31.48</v>
+        <v>50</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -83348,7 +83408,7 @@
         </is>
       </c>
       <c r="E604" t="n">
-        <v>66.67</v>
+        <v>72.22</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -83618,7 +83678,7 @@
         </is>
       </c>
       <c r="E613" t="n">
-        <v>66.67</v>
+        <v>77.78</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -83630,7 +83690,11 @@
       <c r="A614" t="inlineStr"/>
       <c r="B614" t="inlineStr"/>
       <c r="C614" t="inlineStr"/>
-      <c r="D614" t="inlineStr"/>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>Célula 42</t>
+        </is>
+      </c>
       <c r="E614" t="n">
         <v>100</v>
       </c>

--- a/data/diagnostico_coincidencias.xlsx
+++ b/data/diagnostico_coincidencias.xlsx
@@ -685,7 +685,7 @@
         <v>8</v>
       </c>
       <c r="H5" t="n">
-        <v>73.61</v>
+        <v>76.39</v>
       </c>
     </row>
     <row r="6">
@@ -781,7 +781,7 @@
         <v>9</v>
       </c>
       <c r="H8" t="n">
-        <v>74.28</v>
+        <v>75.31</v>
       </c>
     </row>
     <row r="9">
@@ -909,7 +909,7 @@
         <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>68.52</v>
+        <v>75.93000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1133,7 +1133,7 @@
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>72.53</v>
+        <v>77.78</v>
       </c>
     </row>
     <row r="20">
@@ -1293,7 +1293,7 @@
         <v>23</v>
       </c>
       <c r="H24" t="n">
-        <v>27.62</v>
+        <v>30.36</v>
       </c>
     </row>
     <row r="25">
@@ -1389,7 +1389,7 @@
         <v>9</v>
       </c>
       <c r="H27" t="n">
-        <v>88.27</v>
+        <v>93.83</v>
       </c>
     </row>
     <row r="28">
@@ -1485,7 +1485,7 @@
         <v>9</v>
       </c>
       <c r="H30" t="n">
-        <v>83.33</v>
+        <v>87.65000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1549,7 +1549,7 @@
         <v>12</v>
       </c>
       <c r="H32" t="n">
-        <v>71.3</v>
+        <v>76.39</v>
       </c>
     </row>
     <row r="33">
@@ -1581,7 +1581,7 @@
         <v>13</v>
       </c>
       <c r="H33" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
     </row>
     <row r="34">
@@ -1677,7 +1677,7 @@
         <v>13</v>
       </c>
       <c r="H36" t="n">
-        <v>24.07</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="37">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -2263,14 +2263,14 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P5" t="n">
         <v>100</v>
       </c>
       <c r="Q5" t="n">
-        <v>73.61</v>
+        <v>76.39</v>
       </c>
       <c r="R5" t="n">
         <v>8</v>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -2879,14 +2879,14 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P13" t="n">
         <v>100</v>
       </c>
       <c r="Q13" t="n">
-        <v>73.61</v>
+        <v>76.39</v>
       </c>
       <c r="R13" t="n">
         <v>8</v>
@@ -3483,13 +3483,13 @@
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="Q21" t="n">
-        <v>73.61</v>
+        <v>76.39</v>
       </c>
       <c r="R21" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S21" t="n">
         <v>8</v>
@@ -4083,13 +4083,13 @@
       </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="Q29" t="n">
-        <v>73.61</v>
+        <v>76.39</v>
       </c>
       <c r="R29" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S29" t="n">
         <v>8</v>
@@ -4525,7 +4525,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P35" t="n">
@@ -4687,14 +4687,14 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P37" t="n">
         <v>100</v>
       </c>
       <c r="Q37" t="n">
-        <v>73.61</v>
+        <v>76.39</v>
       </c>
       <c r="R37" t="n">
         <v>8</v>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P43" t="n">
@@ -5295,14 +5295,14 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P45" t="n">
         <v>100</v>
       </c>
       <c r="Q45" t="n">
-        <v>73.61</v>
+        <v>76.39</v>
       </c>
       <c r="R45" t="n">
         <v>8</v>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P51" t="n">
@@ -5903,14 +5903,14 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P53" t="n">
         <v>100</v>
       </c>
       <c r="Q53" t="n">
-        <v>73.61</v>
+        <v>76.39</v>
       </c>
       <c r="R53" t="n">
         <v>8</v>
@@ -6349,7 +6349,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P59" t="n">
@@ -6511,14 +6511,14 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P61" t="n">
         <v>100</v>
       </c>
       <c r="Q61" t="n">
-        <v>73.61</v>
+        <v>76.39</v>
       </c>
       <c r="R61" t="n">
         <v>8</v>
@@ -6957,7 +6957,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P67" t="n">
@@ -7119,14 +7119,14 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P69" t="n">
         <v>100</v>
       </c>
       <c r="Q69" t="n">
-        <v>73.61</v>
+        <v>76.39</v>
       </c>
       <c r="R69" t="n">
         <v>8</v>
@@ -7565,7 +7565,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P75" t="n">
@@ -7727,14 +7727,14 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P77" t="n">
         <v>100</v>
       </c>
       <c r="Q77" t="n">
-        <v>73.61</v>
+        <v>76.39</v>
       </c>
       <c r="R77" t="n">
         <v>8</v>
@@ -8173,7 +8173,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P83" t="n">
@@ -8335,14 +8335,14 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P85" t="n">
         <v>100</v>
       </c>
       <c r="Q85" t="n">
-        <v>73.61</v>
+        <v>76.39</v>
       </c>
       <c r="R85" t="n">
         <v>8</v>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P91" t="n">
@@ -8943,14 +8943,14 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P93" t="n">
         <v>100</v>
       </c>
       <c r="Q93" t="n">
-        <v>73.61</v>
+        <v>76.39</v>
       </c>
       <c r="R93" t="n">
         <v>8</v>
@@ -9550,7 +9550,7 @@
         <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>73.61</v>
+        <v>76.39</v>
       </c>
       <c r="R101" t="n">
         <v>0</v>
@@ -10150,7 +10150,7 @@
         <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>73.61</v>
+        <v>76.39</v>
       </c>
       <c r="R109" t="n">
         <v>0</v>
@@ -10750,7 +10750,7 @@
         <v>0</v>
       </c>
       <c r="Q117" t="n">
-        <v>73.61</v>
+        <v>76.39</v>
       </c>
       <c r="R117" t="n">
         <v>0</v>
@@ -11350,7 +11350,7 @@
         <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>73.61</v>
+        <v>76.39</v>
       </c>
       <c r="R125" t="n">
         <v>0</v>
@@ -11947,10 +11947,10 @@
       </c>
       <c r="O133" t="inlineStr"/>
       <c r="P133" t="n">
-        <v>73.59999999999999</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="Q133" t="n">
-        <v>73.61</v>
+        <v>76.39</v>
       </c>
       <c r="R133" t="n">
         <v>0</v>
@@ -12310,14 +12310,14 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P138" t="n">
         <v>100</v>
       </c>
       <c r="Q138" t="n">
-        <v>74.28</v>
+        <v>75.31</v>
       </c>
       <c r="R138" t="n">
         <v>9</v>
@@ -12393,7 +12393,7 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P139" t="n">
@@ -12480,7 +12480,7 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P140" t="n">
@@ -12567,7 +12567,7 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P141" t="n">
@@ -12650,14 +12650,14 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P142" t="n">
         <v>100</v>
       </c>
       <c r="Q142" t="n">
-        <v>74.28</v>
+        <v>75.31</v>
       </c>
       <c r="R142" t="n">
         <v>9</v>
@@ -12733,7 +12733,7 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P143" t="n">
@@ -12816,7 +12816,7 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P144" t="n">
@@ -12899,7 +12899,7 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P145" t="n">
@@ -12980,15 +12980,19 @@
           <t>programada</t>
         </is>
       </c>
-      <c r="O146" t="inlineStr"/>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
       <c r="P146" t="n">
-        <v>88.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="Q146" t="n">
-        <v>74.28</v>
+        <v>75.31</v>
       </c>
       <c r="R146" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S146" t="n">
         <v>9</v>
@@ -13296,15 +13300,19 @@
           <t>programada</t>
         </is>
       </c>
-      <c r="O150" t="inlineStr"/>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
       <c r="P150" t="n">
-        <v>88.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="Q150" t="n">
-        <v>74.28</v>
+        <v>75.31</v>
       </c>
       <c r="R150" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S150" t="n">
         <v>9</v>
@@ -13620,15 +13628,19 @@
           <t>programada</t>
         </is>
       </c>
-      <c r="O154" t="inlineStr"/>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
       <c r="P154" t="n">
-        <v>88.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="Q154" t="n">
-        <v>74.28</v>
+        <v>75.31</v>
       </c>
       <c r="R154" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S154" t="n">
         <v>9</v>
@@ -13938,14 +13950,14 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P158" t="n">
         <v>100</v>
       </c>
       <c r="Q158" t="n">
-        <v>74.28</v>
+        <v>75.31</v>
       </c>
       <c r="R158" t="n">
         <v>9</v>
@@ -14261,7 +14273,7 @@
         <v>88.90000000000001</v>
       </c>
       <c r="Q162" t="n">
-        <v>74.28</v>
+        <v>75.31</v>
       </c>
       <c r="R162" t="n">
         <v>8</v>
@@ -14577,7 +14589,7 @@
         <v>88.90000000000001</v>
       </c>
       <c r="Q166" t="n">
-        <v>74.28</v>
+        <v>75.31</v>
       </c>
       <c r="R166" t="n">
         <v>8</v>
@@ -14893,7 +14905,7 @@
         <v>88.90000000000001</v>
       </c>
       <c r="Q170" t="n">
-        <v>74.28</v>
+        <v>75.31</v>
       </c>
       <c r="R170" t="n">
         <v>8</v>
@@ -15209,7 +15221,7 @@
         <v>88.90000000000001</v>
       </c>
       <c r="Q174" t="n">
-        <v>74.28</v>
+        <v>75.31</v>
       </c>
       <c r="R174" t="n">
         <v>8</v>
@@ -15525,7 +15537,7 @@
         <v>88.90000000000001</v>
       </c>
       <c r="Q178" t="n">
-        <v>74.28</v>
+        <v>75.31</v>
       </c>
       <c r="R178" t="n">
         <v>8</v>
@@ -15841,7 +15853,7 @@
         <v>88.90000000000001</v>
       </c>
       <c r="Q182" t="n">
-        <v>74.28</v>
+        <v>75.31</v>
       </c>
       <c r="R182" t="n">
         <v>8</v>
@@ -16157,7 +16169,7 @@
         <v>0</v>
       </c>
       <c r="Q186" t="n">
-        <v>74.28</v>
+        <v>75.31</v>
       </c>
       <c r="R186" t="n">
         <v>0</v>
@@ -16473,7 +16485,7 @@
         <v>11.1</v>
       </c>
       <c r="Q190" t="n">
-        <v>74.28</v>
+        <v>75.31</v>
       </c>
       <c r="R190" t="n">
         <v>1</v>
@@ -16789,7 +16801,7 @@
         <v>11.1</v>
       </c>
       <c r="Q194" t="n">
-        <v>74.28</v>
+        <v>75.31</v>
       </c>
       <c r="R194" t="n">
         <v>1</v>
@@ -17105,7 +17117,7 @@
         <v>11.1</v>
       </c>
       <c r="Q198" t="n">
-        <v>74.28</v>
+        <v>75.31</v>
       </c>
       <c r="R198" t="n">
         <v>1</v>
@@ -17418,10 +17430,10 @@
       </c>
       <c r="O202" t="inlineStr"/>
       <c r="P202" t="n">
-        <v>74.3</v>
+        <v>75.3</v>
       </c>
       <c r="Q202" t="n">
-        <v>74.28</v>
+        <v>75.31</v>
       </c>
       <c r="R202" t="n">
         <v>0</v>
@@ -17734,14 +17746,14 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P206" t="n">
         <v>100</v>
       </c>
       <c r="Q206" t="n">
-        <v>68.52</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="R206" t="n">
         <v>3</v>
@@ -17817,7 +17829,7 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P207" t="n">
@@ -17900,7 +17912,7 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P208" t="n">
@@ -17983,7 +17995,7 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P209" t="n">
@@ -18066,7 +18078,7 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P210" t="n">
@@ -18149,14 +18161,14 @@
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P211" t="n">
         <v>100</v>
       </c>
       <c r="Q211" t="n">
-        <v>68.52</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="R211" t="n">
         <v>3</v>
@@ -18311,7 +18323,7 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P213" t="n">
@@ -18394,7 +18406,7 @@
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P214" t="n">
@@ -18559,7 +18571,7 @@
         <v>66.7</v>
       </c>
       <c r="Q216" t="n">
-        <v>68.52</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="R216" t="n">
         <v>2</v>
@@ -18954,7 +18966,7 @@
         <v>66.7</v>
       </c>
       <c r="Q221" t="n">
-        <v>68.52</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="R221" t="n">
         <v>2</v>
@@ -19346,14 +19358,14 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P226" t="n">
         <v>100</v>
       </c>
       <c r="Q226" t="n">
-        <v>68.52</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="R226" t="n">
         <v>3</v>
@@ -19587,7 +19599,7 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P229" t="n">
@@ -19749,14 +19761,14 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P231" t="n">
         <v>100</v>
       </c>
       <c r="Q231" t="n">
-        <v>68.52</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="R231" t="n">
         <v>3</v>
@@ -19990,7 +20002,7 @@
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P234" t="n">
@@ -20155,7 +20167,7 @@
         <v>66.7</v>
       </c>
       <c r="Q236" t="n">
-        <v>68.52</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="R236" t="n">
         <v>2</v>
@@ -20389,7 +20401,7 @@
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P239" t="n">
@@ -20551,14 +20563,14 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P241" t="n">
         <v>100</v>
       </c>
       <c r="Q241" t="n">
-        <v>68.52</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="R241" t="n">
         <v>3</v>
@@ -20792,7 +20804,7 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P244" t="n">
@@ -20957,7 +20969,7 @@
         <v>66.7</v>
       </c>
       <c r="Q246" t="n">
-        <v>68.52</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="R246" t="n">
         <v>2</v>
@@ -21191,7 +21203,7 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P249" t="n">
@@ -21356,7 +21368,7 @@
         <v>66.7</v>
       </c>
       <c r="Q251" t="n">
-        <v>68.52</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="R251" t="n">
         <v>2</v>
@@ -21590,7 +21602,7 @@
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P254" t="n">
@@ -21755,7 +21767,7 @@
         <v>66.7</v>
       </c>
       <c r="Q256" t="n">
-        <v>68.52</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="R256" t="n">
         <v>2</v>
@@ -21989,7 +22001,7 @@
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P259" t="n">
@@ -22154,7 +22166,7 @@
         <v>66.7</v>
       </c>
       <c r="Q261" t="n">
-        <v>68.52</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="R261" t="n">
         <v>2</v>
@@ -22388,7 +22400,7 @@
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P264" t="n">
@@ -22550,13 +22562,13 @@
       </c>
       <c r="O266" t="inlineStr"/>
       <c r="P266" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="Q266" t="n">
-        <v>68.52</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="R266" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S266" t="n">
         <v>3</v>
@@ -22945,13 +22957,13 @@
       </c>
       <c r="O271" t="inlineStr"/>
       <c r="P271" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="Q271" t="n">
-        <v>68.52</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="R271" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S271" t="n">
         <v>3</v>
@@ -23340,13 +23352,13 @@
       </c>
       <c r="O276" t="inlineStr"/>
       <c r="P276" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="Q276" t="n">
-        <v>68.52</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="R276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S276" t="n">
         <v>3</v>
@@ -23735,13 +23747,13 @@
       </c>
       <c r="O281" t="inlineStr"/>
       <c r="P281" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="Q281" t="n">
-        <v>68.52</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="R281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S281" t="n">
         <v>3</v>
@@ -24130,13 +24142,13 @@
       </c>
       <c r="O286" t="inlineStr"/>
       <c r="P286" t="n">
-        <v>68.5</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="Q286" t="n">
-        <v>68.52</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="R286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S286" t="n">
         <v>3</v>
@@ -24525,7 +24537,7 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P291" t="n">
@@ -24608,7 +24620,7 @@
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P292" t="n">
@@ -24691,14 +24703,14 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P293" t="n">
         <v>100</v>
       </c>
       <c r="Q293" t="n">
-        <v>72.53</v>
+        <v>77.78</v>
       </c>
       <c r="R293" t="n">
         <v>18</v>
@@ -24774,7 +24786,7 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P294" t="n">
@@ -24857,7 +24869,7 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P295" t="n">
@@ -24940,14 +24952,14 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P296" t="n">
         <v>100</v>
       </c>
       <c r="Q296" t="n">
-        <v>72.53</v>
+        <v>77.78</v>
       </c>
       <c r="R296" t="n">
         <v>18</v>
@@ -25102,7 +25114,7 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P298" t="n">
@@ -25185,14 +25197,14 @@
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P299" t="n">
         <v>100</v>
       </c>
       <c r="Q299" t="n">
-        <v>72.53</v>
+        <v>77.78</v>
       </c>
       <c r="R299" t="n">
         <v>18</v>
@@ -25347,7 +25359,7 @@
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P301" t="n">
@@ -25430,14 +25442,14 @@
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P302" t="n">
         <v>100</v>
       </c>
       <c r="Q302" t="n">
-        <v>72.53</v>
+        <v>77.78</v>
       </c>
       <c r="R302" t="n">
         <v>18</v>
@@ -25513,14 +25525,14 @@
       </c>
       <c r="O303" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P303" t="n">
         <v>100</v>
       </c>
       <c r="Q303" t="n">
-        <v>72.53</v>
+        <v>77.78</v>
       </c>
       <c r="R303" t="n">
         <v>18</v>
@@ -25675,7 +25687,7 @@
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P305" t="n">
@@ -25758,14 +25770,14 @@
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P306" t="n">
         <v>100</v>
       </c>
       <c r="Q306" t="n">
-        <v>72.53</v>
+        <v>77.78</v>
       </c>
       <c r="R306" t="n">
         <v>18</v>
@@ -25841,14 +25853,14 @@
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P307" t="n">
         <v>100</v>
       </c>
       <c r="Q307" t="n">
-        <v>72.53</v>
+        <v>77.78</v>
       </c>
       <c r="R307" t="n">
         <v>18</v>
@@ -26003,7 +26015,7 @@
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P309" t="n">
@@ -26086,14 +26098,14 @@
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P310" t="n">
         <v>100</v>
       </c>
       <c r="Q310" t="n">
-        <v>72.53</v>
+        <v>77.78</v>
       </c>
       <c r="R310" t="n">
         <v>18</v>
@@ -26169,14 +26181,14 @@
       </c>
       <c r="O311" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P311" t="n">
         <v>100</v>
       </c>
       <c r="Q311" t="n">
-        <v>72.53</v>
+        <v>77.78</v>
       </c>
       <c r="R311" t="n">
         <v>18</v>
@@ -26331,7 +26343,7 @@
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P313" t="n">
@@ -26414,14 +26426,14 @@
       </c>
       <c r="O314" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P314" t="n">
         <v>100</v>
       </c>
       <c r="Q314" t="n">
-        <v>72.53</v>
+        <v>77.78</v>
       </c>
       <c r="R314" t="n">
         <v>18</v>
@@ -26497,14 +26509,14 @@
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P315" t="n">
         <v>100</v>
       </c>
       <c r="Q315" t="n">
-        <v>72.53</v>
+        <v>77.78</v>
       </c>
       <c r="R315" t="n">
         <v>18</v>
@@ -26659,7 +26671,7 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P317" t="n">
@@ -26742,14 +26754,14 @@
       </c>
       <c r="O318" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P318" t="n">
         <v>100</v>
       </c>
       <c r="Q318" t="n">
-        <v>72.53</v>
+        <v>77.78</v>
       </c>
       <c r="R318" t="n">
         <v>18</v>
@@ -26825,14 +26837,14 @@
       </c>
       <c r="O319" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P319" t="n">
         <v>100</v>
       </c>
       <c r="Q319" t="n">
-        <v>72.53</v>
+        <v>77.78</v>
       </c>
       <c r="R319" t="n">
         <v>18</v>
@@ -26987,7 +26999,7 @@
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P321" t="n">
@@ -27068,15 +27080,19 @@
           <t>programada</t>
         </is>
       </c>
-      <c r="O322" t="inlineStr"/>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
       <c r="P322" t="n">
-        <v>5.6</v>
+        <v>100</v>
       </c>
       <c r="Q322" t="n">
-        <v>72.53</v>
+        <v>77.78</v>
       </c>
       <c r="R322" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="S322" t="n">
         <v>18</v>
@@ -27147,15 +27163,19 @@
           <t>programada</t>
         </is>
       </c>
-      <c r="O323" t="inlineStr"/>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
       <c r="P323" t="n">
-        <v>5.6</v>
+        <v>100</v>
       </c>
       <c r="Q323" t="n">
-        <v>72.53</v>
+        <v>77.78</v>
       </c>
       <c r="R323" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="S323" t="n">
         <v>18</v>
@@ -27307,7 +27327,7 @@
       </c>
       <c r="O325" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P325" t="n">
@@ -27388,15 +27408,19 @@
           <t>programada</t>
         </is>
       </c>
-      <c r="O326" t="inlineStr"/>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
       <c r="P326" t="n">
-        <v>5.6</v>
+        <v>100</v>
       </c>
       <c r="Q326" t="n">
-        <v>72.53</v>
+        <v>77.78</v>
       </c>
       <c r="R326" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="S326" t="n">
         <v>18</v>
@@ -27467,15 +27491,19 @@
           <t>programada</t>
         </is>
       </c>
-      <c r="O327" t="inlineStr"/>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
       <c r="P327" t="n">
-        <v>5.6</v>
+        <v>100</v>
       </c>
       <c r="Q327" t="n">
-        <v>72.53</v>
+        <v>77.78</v>
       </c>
       <c r="R327" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="S327" t="n">
         <v>18</v>
@@ -27627,7 +27655,7 @@
       </c>
       <c r="O329" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P329" t="n">
@@ -27708,15 +27736,19 @@
           <t>programada</t>
         </is>
       </c>
-      <c r="O330" t="inlineStr"/>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
       <c r="P330" t="n">
-        <v>5.6</v>
+        <v>100</v>
       </c>
       <c r="Q330" t="n">
-        <v>72.53</v>
+        <v>77.78</v>
       </c>
       <c r="R330" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="S330" t="n">
         <v>18</v>
@@ -27787,15 +27819,19 @@
           <t>programada</t>
         </is>
       </c>
-      <c r="O331" t="inlineStr"/>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
       <c r="P331" t="n">
-        <v>5.6</v>
+        <v>100</v>
       </c>
       <c r="Q331" t="n">
-        <v>72.53</v>
+        <v>77.78</v>
       </c>
       <c r="R331" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="S331" t="n">
         <v>18</v>
@@ -27947,7 +27983,7 @@
       </c>
       <c r="O333" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P333" t="n">
@@ -28028,15 +28064,19 @@
           <t>programada</t>
         </is>
       </c>
-      <c r="O334" t="inlineStr"/>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
       <c r="P334" t="n">
-        <v>5.6</v>
+        <v>100</v>
       </c>
       <c r="Q334" t="n">
-        <v>72.53</v>
+        <v>77.78</v>
       </c>
       <c r="R334" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="S334" t="n">
         <v>18</v>
@@ -28107,15 +28147,19 @@
           <t>programada</t>
         </is>
       </c>
-      <c r="O335" t="inlineStr"/>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
       <c r="P335" t="n">
-        <v>5.6</v>
+        <v>100</v>
       </c>
       <c r="Q335" t="n">
-        <v>72.53</v>
+        <v>77.78</v>
       </c>
       <c r="R335" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="S335" t="n">
         <v>18</v>
@@ -28349,7 +28393,7 @@
         <v>0</v>
       </c>
       <c r="Q338" t="n">
-        <v>72.53</v>
+        <v>77.78</v>
       </c>
       <c r="R338" t="n">
         <v>0</v>
@@ -28428,7 +28472,7 @@
         <v>0</v>
       </c>
       <c r="Q339" t="n">
-        <v>72.53</v>
+        <v>77.78</v>
       </c>
       <c r="R339" t="n">
         <v>0</v>
@@ -28665,7 +28709,7 @@
         <v>0</v>
       </c>
       <c r="Q342" t="n">
-        <v>72.53</v>
+        <v>77.78</v>
       </c>
       <c r="R342" t="n">
         <v>0</v>
@@ -28744,7 +28788,7 @@
         <v>0</v>
       </c>
       <c r="Q343" t="n">
-        <v>72.53</v>
+        <v>77.78</v>
       </c>
       <c r="R343" t="n">
         <v>0</v>
@@ -28981,7 +29025,7 @@
         <v>0</v>
       </c>
       <c r="Q346" t="n">
-        <v>72.53</v>
+        <v>77.78</v>
       </c>
       <c r="R346" t="n">
         <v>0</v>
@@ -29060,7 +29104,7 @@
         <v>0</v>
       </c>
       <c r="Q347" t="n">
-        <v>72.53</v>
+        <v>77.78</v>
       </c>
       <c r="R347" t="n">
         <v>0</v>
@@ -29297,7 +29341,7 @@
         <v>0</v>
       </c>
       <c r="Q350" t="n">
-        <v>72.53</v>
+        <v>77.78</v>
       </c>
       <c r="R350" t="n">
         <v>0</v>
@@ -29376,7 +29420,7 @@
         <v>0</v>
       </c>
       <c r="Q351" t="n">
-        <v>72.53</v>
+        <v>77.78</v>
       </c>
       <c r="R351" t="n">
         <v>0</v>
@@ -29610,10 +29654,10 @@
       </c>
       <c r="O354" t="inlineStr"/>
       <c r="P354" t="n">
-        <v>72.5</v>
+        <v>77.8</v>
       </c>
       <c r="Q354" t="n">
-        <v>72.53</v>
+        <v>77.78</v>
       </c>
       <c r="R354" t="n">
         <v>0</v>
@@ -29689,10 +29733,10 @@
       </c>
       <c r="O355" t="inlineStr"/>
       <c r="P355" t="n">
-        <v>72.5</v>
+        <v>77.8</v>
       </c>
       <c r="Q355" t="n">
-        <v>72.53</v>
+        <v>77.78</v>
       </c>
       <c r="R355" t="n">
         <v>0</v>
@@ -29768,7 +29812,7 @@
       </c>
       <c r="O356" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P356" t="n">
@@ -29851,7 +29895,7 @@
       </c>
       <c r="O357" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P357" t="n">
@@ -29934,7 +29978,7 @@
       </c>
       <c r="O358" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P358" t="n">
@@ -30017,7 +30061,7 @@
       </c>
       <c r="O359" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P359" t="n">
@@ -30100,7 +30144,7 @@
       </c>
       <c r="O360" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P360" t="n">
@@ -30183,7 +30227,7 @@
       </c>
       <c r="O361" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P361" t="n">
@@ -30266,7 +30310,7 @@
       </c>
       <c r="O362" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P362" t="n">
@@ -30349,7 +30393,7 @@
       </c>
       <c r="O363" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P363" t="n">
@@ -30432,7 +30476,7 @@
       </c>
       <c r="O364" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P364" t="n">
@@ -30515,7 +30559,7 @@
       </c>
       <c r="O365" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P365" t="n">
@@ -30598,7 +30642,7 @@
       </c>
       <c r="O366" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P366" t="n">
@@ -30681,7 +30725,7 @@
       </c>
       <c r="O367" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P367" t="n">
@@ -30922,7 +30966,7 @@
       </c>
       <c r="O370" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P370" t="n">
@@ -31163,7 +31207,7 @@
       </c>
       <c r="O373" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P373" t="n">
@@ -31404,7 +31448,7 @@
       </c>
       <c r="O376" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P376" t="n">
@@ -31645,7 +31689,7 @@
       </c>
       <c r="O379" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P379" t="n">
@@ -31886,7 +31930,7 @@
       </c>
       <c r="O382" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P382" t="n">
@@ -32127,7 +32171,7 @@
       </c>
       <c r="O385" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P385" t="n">
@@ -32368,7 +32412,7 @@
       </c>
       <c r="O388" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P388" t="n">
@@ -32609,7 +32653,7 @@
       </c>
       <c r="O391" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P391" t="n">
@@ -33798,7 +33842,7 @@
       </c>
       <c r="O406" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P406" t="n">
@@ -34039,7 +34083,7 @@
       </c>
       <c r="O409" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P409" t="n">
@@ -34280,7 +34324,7 @@
       </c>
       <c r="O412" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P412" t="n">
@@ -34521,7 +34565,7 @@
       </c>
       <c r="O415" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P415" t="n">
@@ -34762,7 +34806,7 @@
       </c>
       <c r="O418" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P418" t="n">
@@ -35003,7 +35047,7 @@
       </c>
       <c r="O421" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P421" t="n">
@@ -35244,7 +35288,7 @@
       </c>
       <c r="O424" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P424" t="n">
@@ -35485,7 +35529,7 @@
       </c>
       <c r="O427" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P427" t="n">
@@ -38341,7 +38385,7 @@
       </c>
       <c r="O463" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P463" t="n">
@@ -38424,14 +38468,14 @@
       </c>
       <c r="O464" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P464" t="n">
         <v>100</v>
       </c>
       <c r="Q464" t="n">
-        <v>27.62</v>
+        <v>30.36</v>
       </c>
       <c r="R464" t="n">
         <v>23</v>
@@ -38586,7 +38630,7 @@
       </c>
       <c r="O466" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P466" t="n">
@@ -38669,14 +38713,14 @@
       </c>
       <c r="O467" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P467" t="n">
         <v>100</v>
       </c>
       <c r="Q467" t="n">
-        <v>27.62</v>
+        <v>30.36</v>
       </c>
       <c r="R467" t="n">
         <v>23</v>
@@ -38752,7 +38796,7 @@
       </c>
       <c r="O468" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P468" t="n">
@@ -38835,14 +38879,14 @@
       </c>
       <c r="O469" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P469" t="n">
         <v>100</v>
       </c>
       <c r="Q469" t="n">
-        <v>27.62</v>
+        <v>30.36</v>
       </c>
       <c r="R469" t="n">
         <v>23</v>
@@ -38997,7 +39041,7 @@
       </c>
       <c r="O471" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P471" t="n">
@@ -39080,14 +39124,14 @@
       </c>
       <c r="O472" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P472" t="n">
         <v>100</v>
       </c>
       <c r="Q472" t="n">
-        <v>27.62</v>
+        <v>30.36</v>
       </c>
       <c r="R472" t="n">
         <v>23</v>
@@ -39245,7 +39289,7 @@
         <v>0</v>
       </c>
       <c r="Q474" t="n">
-        <v>27.62</v>
+        <v>30.36</v>
       </c>
       <c r="R474" t="n">
         <v>0</v>
@@ -39482,7 +39526,7 @@
         <v>0</v>
       </c>
       <c r="Q477" t="n">
-        <v>27.62</v>
+        <v>30.36</v>
       </c>
       <c r="R477" t="n">
         <v>0</v>
@@ -39640,7 +39684,7 @@
         <v>0</v>
       </c>
       <c r="Q479" t="n">
-        <v>27.62</v>
+        <v>30.36</v>
       </c>
       <c r="R479" t="n">
         <v>0</v>
@@ -39877,7 +39921,7 @@
         <v>0</v>
       </c>
       <c r="Q482" t="n">
-        <v>27.62</v>
+        <v>30.36</v>
       </c>
       <c r="R482" t="n">
         <v>0</v>
@@ -40032,13 +40076,13 @@
       </c>
       <c r="O484" t="inlineStr"/>
       <c r="P484" t="n">
-        <v>26.1</v>
+        <v>30.4</v>
       </c>
       <c r="Q484" t="n">
-        <v>27.62</v>
+        <v>30.36</v>
       </c>
       <c r="R484" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S484" t="n">
         <v>23</v>
@@ -40269,13 +40313,13 @@
       </c>
       <c r="O487" t="inlineStr"/>
       <c r="P487" t="n">
-        <v>26.1</v>
+        <v>30.4</v>
       </c>
       <c r="Q487" t="n">
-        <v>27.62</v>
+        <v>30.36</v>
       </c>
       <c r="R487" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S487" t="n">
         <v>23</v>
@@ -40427,13 +40471,13 @@
       </c>
       <c r="O489" t="inlineStr"/>
       <c r="P489" t="n">
-        <v>26.1</v>
+        <v>34.8</v>
       </c>
       <c r="Q489" t="n">
-        <v>27.62</v>
+        <v>30.36</v>
       </c>
       <c r="R489" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S489" t="n">
         <v>23</v>
@@ -40664,13 +40708,13 @@
       </c>
       <c r="O492" t="inlineStr"/>
       <c r="P492" t="n">
-        <v>26.1</v>
+        <v>34.8</v>
       </c>
       <c r="Q492" t="n">
-        <v>27.62</v>
+        <v>30.36</v>
       </c>
       <c r="R492" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S492" t="n">
         <v>23</v>
@@ -40822,13 +40866,13 @@
       </c>
       <c r="O494" t="inlineStr"/>
       <c r="P494" t="n">
-        <v>8.699999999999999</v>
+        <v>13</v>
       </c>
       <c r="Q494" t="n">
-        <v>27.62</v>
+        <v>30.36</v>
       </c>
       <c r="R494" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S494" t="n">
         <v>23</v>
@@ -41059,13 +41103,13 @@
       </c>
       <c r="O497" t="inlineStr"/>
       <c r="P497" t="n">
-        <v>8.699999999999999</v>
+        <v>13</v>
       </c>
       <c r="Q497" t="n">
-        <v>27.62</v>
+        <v>30.36</v>
       </c>
       <c r="R497" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S497" t="n">
         <v>23</v>
@@ -41217,13 +41261,13 @@
       </c>
       <c r="O499" t="inlineStr"/>
       <c r="P499" t="n">
-        <v>13</v>
+        <v>17.4</v>
       </c>
       <c r="Q499" t="n">
-        <v>27.62</v>
+        <v>30.36</v>
       </c>
       <c r="R499" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S499" t="n">
         <v>23</v>
@@ -41454,13 +41498,13 @@
       </c>
       <c r="O502" t="inlineStr"/>
       <c r="P502" t="n">
-        <v>13</v>
+        <v>17.4</v>
       </c>
       <c r="Q502" t="n">
-        <v>27.62</v>
+        <v>30.36</v>
       </c>
       <c r="R502" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S502" t="n">
         <v>23</v>
@@ -41615,7 +41659,7 @@
         <v>0</v>
       </c>
       <c r="Q504" t="n">
-        <v>27.62</v>
+        <v>30.36</v>
       </c>
       <c r="R504" t="n">
         <v>0</v>
@@ -41852,7 +41896,7 @@
         <v>0</v>
       </c>
       <c r="Q507" t="n">
-        <v>27.62</v>
+        <v>30.36</v>
       </c>
       <c r="R507" t="n">
         <v>0</v>
@@ -42010,7 +42054,7 @@
         <v>0</v>
       </c>
       <c r="Q509" t="n">
-        <v>27.62</v>
+        <v>30.36</v>
       </c>
       <c r="R509" t="n">
         <v>0</v>
@@ -42247,7 +42291,7 @@
         <v>0</v>
       </c>
       <c r="Q512" t="n">
-        <v>27.62</v>
+        <v>30.36</v>
       </c>
       <c r="R512" t="n">
         <v>0</v>
@@ -42405,7 +42449,7 @@
         <v>0</v>
       </c>
       <c r="Q514" t="n">
-        <v>27.62</v>
+        <v>30.36</v>
       </c>
       <c r="R514" t="n">
         <v>0</v>
@@ -42642,7 +42686,7 @@
         <v>0</v>
       </c>
       <c r="Q517" t="n">
-        <v>27.62</v>
+        <v>30.36</v>
       </c>
       <c r="R517" t="n">
         <v>0</v>
@@ -42800,7 +42844,7 @@
         <v>0</v>
       </c>
       <c r="Q519" t="n">
-        <v>27.62</v>
+        <v>30.36</v>
       </c>
       <c r="R519" t="n">
         <v>0</v>
@@ -43037,7 +43081,7 @@
         <v>0</v>
       </c>
       <c r="Q522" t="n">
-        <v>27.62</v>
+        <v>30.36</v>
       </c>
       <c r="R522" t="n">
         <v>0</v>
@@ -43195,7 +43239,7 @@
         <v>0</v>
       </c>
       <c r="Q524" t="n">
-        <v>27.62</v>
+        <v>30.36</v>
       </c>
       <c r="R524" t="n">
         <v>0</v>
@@ -43432,7 +43476,7 @@
         <v>0</v>
       </c>
       <c r="Q527" t="n">
-        <v>27.62</v>
+        <v>30.36</v>
       </c>
       <c r="R527" t="n">
         <v>0</v>
@@ -43590,7 +43634,7 @@
         <v>0</v>
       </c>
       <c r="Q529" t="n">
-        <v>27.62</v>
+        <v>30.36</v>
       </c>
       <c r="R529" t="n">
         <v>0</v>
@@ -43827,7 +43871,7 @@
         <v>0</v>
       </c>
       <c r="Q532" t="n">
-        <v>27.62</v>
+        <v>30.36</v>
       </c>
       <c r="R532" t="n">
         <v>0</v>
@@ -43985,7 +44029,7 @@
         <v>0</v>
       </c>
       <c r="Q534" t="n">
-        <v>27.62</v>
+        <v>30.36</v>
       </c>
       <c r="R534" t="n">
         <v>0</v>
@@ -44222,7 +44266,7 @@
         <v>0</v>
       </c>
       <c r="Q537" t="n">
-        <v>27.62</v>
+        <v>30.36</v>
       </c>
       <c r="R537" t="n">
         <v>0</v>
@@ -44380,7 +44424,7 @@
         <v>0</v>
       </c>
       <c r="Q539" t="n">
-        <v>27.62</v>
+        <v>30.36</v>
       </c>
       <c r="R539" t="n">
         <v>0</v>
@@ -44617,7 +44661,7 @@
         <v>0</v>
       </c>
       <c r="Q542" t="n">
-        <v>27.62</v>
+        <v>30.36</v>
       </c>
       <c r="R542" t="n">
         <v>0</v>
@@ -44772,10 +44816,10 @@
       </c>
       <c r="O544" t="inlineStr"/>
       <c r="P544" t="n">
-        <v>27.6</v>
+        <v>30.4</v>
       </c>
       <c r="Q544" t="n">
-        <v>27.62</v>
+        <v>30.36</v>
       </c>
       <c r="R544" t="n">
         <v>0</v>
@@ -45009,10 +45053,10 @@
       </c>
       <c r="O547" t="inlineStr"/>
       <c r="P547" t="n">
-        <v>27.6</v>
+        <v>30.4</v>
       </c>
       <c r="Q547" t="n">
-        <v>27.62</v>
+        <v>30.36</v>
       </c>
       <c r="R547" t="n">
         <v>0</v>
@@ -45088,7 +45132,7 @@
       </c>
       <c r="O548" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P548" t="n">
@@ -45171,14 +45215,14 @@
       </c>
       <c r="O549" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P549" t="n">
         <v>100</v>
       </c>
       <c r="Q549" t="n">
-        <v>88.27</v>
+        <v>93.83</v>
       </c>
       <c r="R549" t="n">
         <v>9</v>
@@ -45254,7 +45298,7 @@
       </c>
       <c r="O550" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P550" t="n">
@@ -45416,14 +45460,14 @@
       </c>
       <c r="O552" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P552" t="n">
         <v>100</v>
       </c>
       <c r="Q552" t="n">
-        <v>88.27</v>
+        <v>93.83</v>
       </c>
       <c r="R552" t="n">
         <v>9</v>
@@ -45499,7 +45543,7 @@
       </c>
       <c r="O553" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P553" t="n">
@@ -45664,7 +45708,7 @@
         <v>55.6</v>
       </c>
       <c r="Q555" t="n">
-        <v>88.27</v>
+        <v>93.83</v>
       </c>
       <c r="R555" t="n">
         <v>5</v>
@@ -45901,7 +45945,7 @@
         <v>55.6</v>
       </c>
       <c r="Q558" t="n">
-        <v>88.27</v>
+        <v>93.83</v>
       </c>
       <c r="R558" t="n">
         <v>5</v>
@@ -46135,14 +46179,14 @@
       </c>
       <c r="O561" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P561" t="n">
         <v>100</v>
       </c>
       <c r="Q561" t="n">
-        <v>88.27</v>
+        <v>93.83</v>
       </c>
       <c r="R561" t="n">
         <v>9</v>
@@ -46376,14 +46420,14 @@
       </c>
       <c r="O564" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P564" t="n">
         <v>100</v>
       </c>
       <c r="Q564" t="n">
-        <v>88.27</v>
+        <v>93.83</v>
       </c>
       <c r="R564" t="n">
         <v>9</v>
@@ -46617,14 +46661,14 @@
       </c>
       <c r="O567" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P567" t="n">
         <v>100</v>
       </c>
       <c r="Q567" t="n">
-        <v>88.27</v>
+        <v>93.83</v>
       </c>
       <c r="R567" t="n">
         <v>9</v>
@@ -46856,15 +46900,19 @@
           <t>programada</t>
         </is>
       </c>
-      <c r="O570" t="inlineStr"/>
+      <c r="O570" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
       <c r="P570" t="n">
-        <v>88.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="Q570" t="n">
-        <v>88.27</v>
+        <v>93.83</v>
       </c>
       <c r="R570" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S570" t="n">
         <v>9</v>
@@ -47095,14 +47143,14 @@
       </c>
       <c r="O573" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P573" t="n">
         <v>100</v>
       </c>
       <c r="Q573" t="n">
-        <v>88.27</v>
+        <v>93.83</v>
       </c>
       <c r="R573" t="n">
         <v>9</v>
@@ -47336,14 +47384,14 @@
       </c>
       <c r="O576" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P576" t="n">
         <v>100</v>
       </c>
       <c r="Q576" t="n">
-        <v>88.27</v>
+        <v>93.83</v>
       </c>
       <c r="R576" t="n">
         <v>9</v>
@@ -47577,14 +47625,14 @@
       </c>
       <c r="O579" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P579" t="n">
         <v>100</v>
       </c>
       <c r="Q579" t="n">
-        <v>88.27</v>
+        <v>93.83</v>
       </c>
       <c r="R579" t="n">
         <v>9</v>
@@ -47818,14 +47866,14 @@
       </c>
       <c r="O582" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P582" t="n">
         <v>100</v>
       </c>
       <c r="Q582" t="n">
-        <v>88.27</v>
+        <v>93.83</v>
       </c>
       <c r="R582" t="n">
         <v>9</v>
@@ -48057,15 +48105,19 @@
           <t>programada</t>
         </is>
       </c>
-      <c r="O585" t="inlineStr"/>
+      <c r="O585" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
       <c r="P585" t="n">
-        <v>77.8</v>
+        <v>100</v>
       </c>
       <c r="Q585" t="n">
-        <v>88.27</v>
+        <v>93.83</v>
       </c>
       <c r="R585" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="S585" t="n">
         <v>9</v>
@@ -48296,13 +48348,13 @@
       </c>
       <c r="O588" t="inlineStr"/>
       <c r="P588" t="n">
-        <v>44.4</v>
+        <v>66.7</v>
       </c>
       <c r="Q588" t="n">
-        <v>88.27</v>
+        <v>93.83</v>
       </c>
       <c r="R588" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S588" t="n">
         <v>9</v>
@@ -48533,13 +48585,13 @@
       </c>
       <c r="O591" t="inlineStr"/>
       <c r="P591" t="n">
-        <v>44.4</v>
+        <v>66.7</v>
       </c>
       <c r="Q591" t="n">
-        <v>88.27</v>
+        <v>93.83</v>
       </c>
       <c r="R591" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S591" t="n">
         <v>9</v>
@@ -48770,13 +48822,13 @@
       </c>
       <c r="O594" t="inlineStr"/>
       <c r="P594" t="n">
-        <v>44.4</v>
+        <v>66.7</v>
       </c>
       <c r="Q594" t="n">
-        <v>88.27</v>
+        <v>93.83</v>
       </c>
       <c r="R594" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S594" t="n">
         <v>9</v>
@@ -49007,13 +49059,13 @@
       </c>
       <c r="O597" t="inlineStr"/>
       <c r="P597" t="n">
-        <v>88.3</v>
+        <v>93.8</v>
       </c>
       <c r="Q597" t="n">
-        <v>88.27</v>
+        <v>93.83</v>
       </c>
       <c r="R597" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S597" t="n">
         <v>9</v>
@@ -49165,7 +49217,7 @@
       </c>
       <c r="O599" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P599" t="n">
@@ -49248,14 +49300,14 @@
       </c>
       <c r="O600" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P600" t="n">
         <v>100</v>
       </c>
       <c r="Q600" t="n">
-        <v>83.33</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="R600" t="n">
         <v>9</v>
@@ -49331,7 +49383,7 @@
       </c>
       <c r="O601" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P601" t="n">
@@ -49414,7 +49466,7 @@
       </c>
       <c r="O602" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P602" t="n">
@@ -49576,14 +49628,14 @@
       </c>
       <c r="O604" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P604" t="n">
         <v>100</v>
       </c>
       <c r="Q604" t="n">
-        <v>83.33</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="R604" t="n">
         <v>9</v>
@@ -49659,7 +49711,7 @@
       </c>
       <c r="O605" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P605" t="n">
@@ -49742,7 +49794,7 @@
       </c>
       <c r="O606" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P606" t="n">
@@ -49904,13 +49956,13 @@
       </c>
       <c r="O608" t="inlineStr"/>
       <c r="P608" t="n">
-        <v>44.4</v>
+        <v>33.3</v>
       </c>
       <c r="Q608" t="n">
-        <v>83.33</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="R608" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S608" t="n">
         <v>9</v>
@@ -50220,13 +50272,13 @@
       </c>
       <c r="O612" t="inlineStr"/>
       <c r="P612" t="n">
-        <v>44.4</v>
+        <v>33.3</v>
       </c>
       <c r="Q612" t="n">
-        <v>83.33</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="R612" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S612" t="n">
         <v>9</v>
@@ -50536,14 +50588,14 @@
       </c>
       <c r="O616" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P616" t="n">
         <v>100</v>
       </c>
       <c r="Q616" t="n">
-        <v>83.33</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="R616" t="n">
         <v>9</v>
@@ -50856,14 +50908,14 @@
       </c>
       <c r="O620" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P620" t="n">
         <v>100</v>
       </c>
       <c r="Q620" t="n">
-        <v>83.33</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="R620" t="n">
         <v>9</v>
@@ -51176,14 +51228,14 @@
       </c>
       <c r="O624" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P624" t="n">
         <v>100</v>
       </c>
       <c r="Q624" t="n">
-        <v>83.33</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="R624" t="n">
         <v>9</v>
@@ -51496,14 +51548,14 @@
       </c>
       <c r="O628" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P628" t="n">
         <v>100</v>
       </c>
       <c r="Q628" t="n">
-        <v>83.33</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="R628" t="n">
         <v>9</v>
@@ -51816,14 +51868,14 @@
       </c>
       <c r="O632" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P632" t="n">
         <v>100</v>
       </c>
       <c r="Q632" t="n">
-        <v>83.33</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="R632" t="n">
         <v>9</v>
@@ -52136,14 +52188,14 @@
       </c>
       <c r="O636" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P636" t="n">
         <v>100</v>
       </c>
       <c r="Q636" t="n">
-        <v>83.33</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="R636" t="n">
         <v>9</v>
@@ -52456,14 +52508,14 @@
       </c>
       <c r="O640" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P640" t="n">
         <v>100</v>
       </c>
       <c r="Q640" t="n">
-        <v>83.33</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="R640" t="n">
         <v>9</v>
@@ -52776,14 +52828,14 @@
       </c>
       <c r="O644" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P644" t="n">
         <v>100</v>
       </c>
       <c r="Q644" t="n">
-        <v>83.33</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="R644" t="n">
         <v>9</v>
@@ -53096,13 +53148,13 @@
       </c>
       <c r="O648" t="inlineStr"/>
       <c r="P648" t="n">
-        <v>55.6</v>
+        <v>66.7</v>
       </c>
       <c r="Q648" t="n">
-        <v>83.33</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="R648" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S648" t="n">
         <v>9</v>
@@ -53412,13 +53464,13 @@
       </c>
       <c r="O652" t="inlineStr"/>
       <c r="P652" t="n">
-        <v>22.2</v>
+        <v>55.6</v>
       </c>
       <c r="Q652" t="n">
-        <v>83.33</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="R652" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S652" t="n">
         <v>9</v>
@@ -53728,13 +53780,13 @@
       </c>
       <c r="O656" t="inlineStr"/>
       <c r="P656" t="n">
-        <v>22.2</v>
+        <v>55.6</v>
       </c>
       <c r="Q656" t="n">
-        <v>83.33</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="R656" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S656" t="n">
         <v>9</v>
@@ -54044,13 +54096,13 @@
       </c>
       <c r="O660" t="inlineStr"/>
       <c r="P660" t="n">
-        <v>22.2</v>
+        <v>55.6</v>
       </c>
       <c r="Q660" t="n">
-        <v>83.33</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="R660" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S660" t="n">
         <v>9</v>
@@ -54360,13 +54412,13 @@
       </c>
       <c r="O664" t="inlineStr"/>
       <c r="P664" t="n">
-        <v>83.3</v>
+        <v>87.7</v>
       </c>
       <c r="Q664" t="n">
-        <v>83.33</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="R664" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S664" t="n">
         <v>9</v>
@@ -54597,14 +54649,14 @@
       </c>
       <c r="O667" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P667" t="n">
         <v>100</v>
       </c>
       <c r="Q667" t="n">
-        <v>71.3</v>
+        <v>76.39</v>
       </c>
       <c r="R667" t="n">
         <v>12</v>
@@ -54680,14 +54732,14 @@
       </c>
       <c r="O668" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P668" t="n">
         <v>100</v>
       </c>
       <c r="Q668" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="R668" t="n">
         <v>13</v>
@@ -54763,7 +54815,7 @@
       </c>
       <c r="O669" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P669" t="n">
@@ -54846,7 +54898,7 @@
       </c>
       <c r="O670" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P670" t="n">
@@ -54929,7 +54981,7 @@
       </c>
       <c r="O671" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P671" t="n">
@@ -55012,7 +55064,7 @@
       </c>
       <c r="O672" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P672" t="n">
@@ -55095,14 +55147,14 @@
       </c>
       <c r="O673" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P673" t="n">
         <v>100</v>
       </c>
       <c r="Q673" t="n">
-        <v>71.3</v>
+        <v>76.39</v>
       </c>
       <c r="R673" t="n">
         <v>12</v>
@@ -55178,14 +55230,14 @@
       </c>
       <c r="O674" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P674" t="n">
         <v>100</v>
       </c>
       <c r="Q674" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="R674" t="n">
         <v>13</v>
@@ -55261,7 +55313,7 @@
       </c>
       <c r="O675" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P675" t="n">
@@ -55423,7 +55475,7 @@
       </c>
       <c r="O677" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P677" t="n">
@@ -55588,7 +55640,7 @@
         <v>41.7</v>
       </c>
       <c r="Q679" t="n">
-        <v>71.3</v>
+        <v>76.39</v>
       </c>
       <c r="R679" t="n">
         <v>5</v>
@@ -55667,7 +55719,7 @@
         <v>0</v>
       </c>
       <c r="Q680" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="R680" t="n">
         <v>0</v>
@@ -56082,7 +56134,7 @@
         <v>41.7</v>
       </c>
       <c r="Q685" t="n">
-        <v>71.3</v>
+        <v>76.39</v>
       </c>
       <c r="R685" t="n">
         <v>5</v>
@@ -56161,7 +56213,7 @@
         <v>0</v>
       </c>
       <c r="Q686" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="R686" t="n">
         <v>0</v>
@@ -56565,14 +56617,14 @@
       </c>
       <c r="O691" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P691" t="n">
         <v>100</v>
       </c>
       <c r="Q691" t="n">
-        <v>71.3</v>
+        <v>76.39</v>
       </c>
       <c r="R691" t="n">
         <v>12</v>
@@ -56651,7 +56703,7 @@
         <v>0</v>
       </c>
       <c r="Q692" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="R692" t="n">
         <v>0</v>
@@ -57043,14 +57095,14 @@
       </c>
       <c r="O697" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P697" t="n">
         <v>100</v>
       </c>
       <c r="Q697" t="n">
-        <v>71.3</v>
+        <v>76.39</v>
       </c>
       <c r="R697" t="n">
         <v>12</v>
@@ -57129,7 +57181,7 @@
         <v>0</v>
       </c>
       <c r="Q698" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="R698" t="n">
         <v>0</v>
@@ -57521,14 +57573,14 @@
       </c>
       <c r="O703" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P703" t="n">
         <v>100</v>
       </c>
       <c r="Q703" t="n">
-        <v>71.3</v>
+        <v>76.39</v>
       </c>
       <c r="R703" t="n">
         <v>12</v>
@@ -57607,7 +57659,7 @@
         <v>0</v>
       </c>
       <c r="Q704" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="R704" t="n">
         <v>0</v>
@@ -57999,14 +58051,14 @@
       </c>
       <c r="O709" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P709" t="n">
         <v>100</v>
       </c>
       <c r="Q709" t="n">
-        <v>71.3</v>
+        <v>76.39</v>
       </c>
       <c r="R709" t="n">
         <v>12</v>
@@ -58089,7 +58141,7 @@
         <v>0</v>
       </c>
       <c r="Q710" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="R710" t="n">
         <v>0</v>
@@ -58479,15 +58531,19 @@
           <t>programada</t>
         </is>
       </c>
-      <c r="O715" t="inlineStr"/>
+      <c r="O715" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
       <c r="P715" t="n">
-        <v>8.300000000000001</v>
+        <v>100</v>
       </c>
       <c r="Q715" t="n">
-        <v>71.3</v>
+        <v>76.39</v>
       </c>
       <c r="R715" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="S715" t="n">
         <v>12</v>
@@ -58563,7 +58619,7 @@
         <v>0</v>
       </c>
       <c r="Q716" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="R716" t="n">
         <v>0</v>
@@ -58953,15 +59009,19 @@
           <t>programada</t>
         </is>
       </c>
-      <c r="O721" t="inlineStr"/>
+      <c r="O721" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
       <c r="P721" t="n">
-        <v>8.300000000000001</v>
+        <v>100</v>
       </c>
       <c r="Q721" t="n">
-        <v>71.3</v>
+        <v>76.39</v>
       </c>
       <c r="R721" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="S721" t="n">
         <v>12</v>
@@ -59037,7 +59097,7 @@
         <v>0</v>
       </c>
       <c r="Q722" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="R722" t="n">
         <v>0</v>
@@ -59427,15 +59487,19 @@
           <t>programada</t>
         </is>
       </c>
-      <c r="O727" t="inlineStr"/>
+      <c r="O727" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
       <c r="P727" t="n">
-        <v>8.300000000000001</v>
+        <v>100</v>
       </c>
       <c r="Q727" t="n">
-        <v>71.3</v>
+        <v>76.39</v>
       </c>
       <c r="R727" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="S727" t="n">
         <v>12</v>
@@ -59511,7 +59575,7 @@
         <v>0</v>
       </c>
       <c r="Q728" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="R728" t="n">
         <v>0</v>
@@ -59901,15 +59965,19 @@
           <t>programada</t>
         </is>
       </c>
-      <c r="O733" t="inlineStr"/>
+      <c r="O733" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
       <c r="P733" t="n">
-        <v>8.300000000000001</v>
+        <v>100</v>
       </c>
       <c r="Q733" t="n">
-        <v>71.3</v>
+        <v>76.39</v>
       </c>
       <c r="R733" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="S733" t="n">
         <v>12</v>
@@ -59985,7 +60053,7 @@
         <v>0</v>
       </c>
       <c r="Q734" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="R734" t="n">
         <v>0</v>
@@ -60380,7 +60448,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="Q739" t="n">
-        <v>71.3</v>
+        <v>76.39</v>
       </c>
       <c r="R739" t="n">
         <v>1</v>
@@ -60459,7 +60527,7 @@
         <v>0</v>
       </c>
       <c r="Q740" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="R740" t="n">
         <v>0</v>
@@ -60862,7 +60930,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="Q745" t="n">
-        <v>71.3</v>
+        <v>76.39</v>
       </c>
       <c r="R745" t="n">
         <v>1</v>
@@ -60941,7 +61009,7 @@
         <v>0</v>
       </c>
       <c r="Q746" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="R746" t="n">
         <v>0</v>
@@ -61336,7 +61404,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="Q751" t="n">
-        <v>71.3</v>
+        <v>76.39</v>
       </c>
       <c r="R751" t="n">
         <v>1</v>
@@ -61415,7 +61483,7 @@
         <v>0</v>
       </c>
       <c r="Q752" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="R752" t="n">
         <v>0</v>
@@ -61810,7 +61878,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="Q757" t="n">
-        <v>71.3</v>
+        <v>76.39</v>
       </c>
       <c r="R757" t="n">
         <v>1</v>
@@ -61889,7 +61957,7 @@
         <v>0</v>
       </c>
       <c r="Q758" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="R758" t="n">
         <v>0</v>
@@ -62281,10 +62349,10 @@
       </c>
       <c r="O763" t="inlineStr"/>
       <c r="P763" t="n">
-        <v>71.3</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="Q763" t="n">
-        <v>71.3</v>
+        <v>76.39</v>
       </c>
       <c r="R763" t="n">
         <v>1</v>
@@ -62360,10 +62428,10 @@
       </c>
       <c r="O764" t="inlineStr"/>
       <c r="P764" t="n">
-        <v>24.1</v>
+        <v>31.5</v>
       </c>
       <c r="Q764" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="R764" t="n">
         <v>0</v>
@@ -62755,14 +62823,14 @@
       </c>
       <c r="O769" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P769" t="n">
         <v>100</v>
       </c>
       <c r="Q769" t="n">
-        <v>24.07</v>
+        <v>24.5</v>
       </c>
       <c r="R769" t="n">
         <v>13</v>
@@ -62838,7 +62906,7 @@
       </c>
       <c r="O770" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P770" t="n">
@@ -62921,14 +62989,14 @@
       </c>
       <c r="O771" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P771" t="n">
         <v>100</v>
       </c>
       <c r="Q771" t="n">
-        <v>24.07</v>
+        <v>24.5</v>
       </c>
       <c r="R771" t="n">
         <v>13</v>
@@ -63004,7 +63072,7 @@
       </c>
       <c r="O772" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P772" t="n">
@@ -63090,7 +63158,7 @@
         <v>0</v>
       </c>
       <c r="Q773" t="n">
-        <v>24.07</v>
+        <v>24.5</v>
       </c>
       <c r="R773" t="n">
         <v>0</v>
@@ -63166,7 +63234,7 @@
       </c>
       <c r="O774" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P774" t="n">
@@ -63252,7 +63320,7 @@
         <v>0</v>
       </c>
       <c r="Q775" t="n">
-        <v>24.07</v>
+        <v>24.5</v>
       </c>
       <c r="R775" t="n">
         <v>0</v>
@@ -63328,7 +63396,7 @@
       </c>
       <c r="O776" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P776" t="n">
@@ -63414,7 +63482,7 @@
         <v>0</v>
       </c>
       <c r="Q777" t="n">
-        <v>24.07</v>
+        <v>24.5</v>
       </c>
       <c r="R777" t="n">
         <v>0</v>
@@ -63490,7 +63558,7 @@
       </c>
       <c r="O778" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P778" t="n">
@@ -63576,7 +63644,7 @@
         <v>0</v>
       </c>
       <c r="Q779" t="n">
-        <v>24.07</v>
+        <v>24.5</v>
       </c>
       <c r="R779" t="n">
         <v>0</v>
@@ -63652,7 +63720,7 @@
       </c>
       <c r="O780" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P780" t="n">
@@ -63738,7 +63806,7 @@
         <v>0</v>
       </c>
       <c r="Q781" t="n">
-        <v>24.07</v>
+        <v>24.5</v>
       </c>
       <c r="R781" t="n">
         <v>0</v>
@@ -63814,7 +63882,7 @@
       </c>
       <c r="O782" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P782" t="n">
@@ -63900,7 +63968,7 @@
         <v>0</v>
       </c>
       <c r="Q783" t="n">
-        <v>24.07</v>
+        <v>24.5</v>
       </c>
       <c r="R783" t="n">
         <v>0</v>
@@ -63976,7 +64044,7 @@
       </c>
       <c r="O784" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P784" t="n">
@@ -64062,7 +64130,7 @@
         <v>0</v>
       </c>
       <c r="Q785" t="n">
-        <v>24.07</v>
+        <v>24.5</v>
       </c>
       <c r="R785" t="n">
         <v>0</v>
@@ -64138,7 +64206,7 @@
       </c>
       <c r="O786" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P786" t="n">
@@ -64224,7 +64292,7 @@
         <v>0</v>
       </c>
       <c r="Q787" t="n">
-        <v>24.07</v>
+        <v>24.5</v>
       </c>
       <c r="R787" t="n">
         <v>0</v>
@@ -64300,7 +64368,7 @@
       </c>
       <c r="O788" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P788" t="n">
@@ -64386,7 +64454,7 @@
         <v>0</v>
       </c>
       <c r="Q789" t="n">
-        <v>24.07</v>
+        <v>24.5</v>
       </c>
       <c r="R789" t="n">
         <v>0</v>
@@ -64462,7 +64530,7 @@
       </c>
       <c r="O790" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P790" t="n">
@@ -64548,7 +64616,7 @@
         <v>0</v>
       </c>
       <c r="Q791" t="n">
-        <v>24.07</v>
+        <v>24.5</v>
       </c>
       <c r="R791" t="n">
         <v>0</v>
@@ -64624,7 +64692,7 @@
       </c>
       <c r="O792" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="P792" t="n">
@@ -64710,7 +64778,7 @@
         <v>0</v>
       </c>
       <c r="Q793" t="n">
-        <v>24.07</v>
+        <v>24.5</v>
       </c>
       <c r="R793" t="n">
         <v>0</v>
@@ -64872,7 +64940,7 @@
         <v>0</v>
       </c>
       <c r="Q795" t="n">
-        <v>24.07</v>
+        <v>24.5</v>
       </c>
       <c r="R795" t="n">
         <v>0</v>
@@ -65034,7 +65102,7 @@
         <v>0</v>
       </c>
       <c r="Q797" t="n">
-        <v>24.07</v>
+        <v>24.5</v>
       </c>
       <c r="R797" t="n">
         <v>0</v>
@@ -65196,7 +65264,7 @@
         <v>0</v>
       </c>
       <c r="Q799" t="n">
-        <v>24.07</v>
+        <v>24.5</v>
       </c>
       <c r="R799" t="n">
         <v>0</v>
@@ -65355,10 +65423,10 @@
       </c>
       <c r="O801" t="inlineStr"/>
       <c r="P801" t="n">
-        <v>24.1</v>
+        <v>24.5</v>
       </c>
       <c r="Q801" t="n">
-        <v>24.07</v>
+        <v>24.5</v>
       </c>
       <c r="R801" t="n">
         <v>0</v>
@@ -65884,7 +65952,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>72.22</v>
+        <v>77.78</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -65944,7 +66012,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>51.85</v>
+        <v>55.56</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -66154,7 +66222,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>24.07</v>
+        <v>29.63</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -67704,7 +67772,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>88.89</v>
+        <v>100</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -67794,7 +67862,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>83.33</v>
+        <v>94.44</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -67824,7 +67892,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>77.78</v>
+        <v>100</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -67944,7 +68012,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>72.22</v>
+        <v>83.33</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -67974,7 +68042,7 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>88.89</v>
+        <v>94.44</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -68064,7 +68132,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>66.67</v>
+        <v>94.44</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -70898,7 +70966,7 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>72.22</v>
+        <v>77.78</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -70988,7 +71056,7 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>72.22</v>
+        <v>77.78</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -71018,7 +71086,7 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>72.22</v>
+        <v>77.78</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -71228,7 +71296,7 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>72.22</v>
+        <v>77.78</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -73658,7 +73726,7 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>66.67</v>
+        <v>72.22</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -73688,7 +73756,7 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>66.67</v>
+        <v>72.22</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -73718,7 +73786,7 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>66.67</v>
+        <v>72.22</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -73748,7 +73816,7 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>66.67</v>
+        <v>72.22</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -73778,7 +73846,7 @@
         </is>
       </c>
       <c r="E283" t="n">
-        <v>72.22</v>
+        <v>77.78</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -73808,7 +73876,7 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>72.22</v>
+        <v>77.78</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -73838,7 +73906,7 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>66.67</v>
+        <v>72.22</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -73868,7 +73936,7 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>72.22</v>
+        <v>77.78</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -73898,7 +73966,7 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>72.22</v>
+        <v>77.78</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -73928,7 +73996,7 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>66.67</v>
+        <v>72.22</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -73958,7 +74026,7 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>66.67</v>
+        <v>72.22</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -74498,7 +74566,7 @@
         </is>
       </c>
       <c r="E307" t="n">
-        <v>77.78</v>
+        <v>100</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -77258,7 +77326,7 @@
         </is>
       </c>
       <c r="E399" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -77288,7 +77356,7 @@
         </is>
       </c>
       <c r="E400" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -77318,7 +77386,7 @@
         </is>
       </c>
       <c r="E401" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -77348,7 +77416,7 @@
         </is>
       </c>
       <c r="E402" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -77378,7 +77446,7 @@
         </is>
       </c>
       <c r="E403" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -77408,7 +77476,7 @@
         </is>
       </c>
       <c r="E404" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -77438,7 +77506,7 @@
         </is>
       </c>
       <c r="E405" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -77468,7 +77536,7 @@
         </is>
       </c>
       <c r="E406" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -77498,7 +77566,7 @@
         </is>
       </c>
       <c r="E407" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -77528,7 +77596,7 @@
         </is>
       </c>
       <c r="E408" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -77558,7 +77626,7 @@
         </is>
       </c>
       <c r="E409" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -77588,7 +77656,7 @@
         </is>
       </c>
       <c r="E410" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -77618,7 +77686,7 @@
         </is>
       </c>
       <c r="E411" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -78128,7 +78196,7 @@
         </is>
       </c>
       <c r="E428" t="n">
-        <v>44.44</v>
+        <v>55.56</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -78218,7 +78286,7 @@
         </is>
       </c>
       <c r="E431" t="n">
-        <v>25.93</v>
+        <v>33.33</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -78278,7 +78346,7 @@
         </is>
       </c>
       <c r="E433" t="n">
-        <v>18.52</v>
+        <v>33.33</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -78368,7 +78436,7 @@
         </is>
       </c>
       <c r="E436" t="n">
-        <v>18.52</v>
+        <v>25.93</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -78458,7 +78526,7 @@
         </is>
       </c>
       <c r="E439" t="n">
-        <v>18.52</v>
+        <v>25.93</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -78668,7 +78736,7 @@
         </is>
       </c>
       <c r="E446" t="n">
-        <v>18.52</v>
+        <v>25.93</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -78728,7 +78796,7 @@
         </is>
       </c>
       <c r="E448" t="n">
-        <v>18.52</v>
+        <v>25.93</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -80138,7 +80206,7 @@
         </is>
       </c>
       <c r="E495" t="n">
-        <v>37.04</v>
+        <v>51.85</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -83168,7 +83236,7 @@
         </is>
       </c>
       <c r="E596" t="n">
-        <v>72.22</v>
+        <v>77.78</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -83198,7 +83266,7 @@
         </is>
       </c>
       <c r="E597" t="n">
-        <v>72.22</v>
+        <v>77.78</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -83228,7 +83296,7 @@
         </is>
       </c>
       <c r="E598" t="n">
-        <v>72.22</v>
+        <v>77.78</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -83258,7 +83326,7 @@
         </is>
       </c>
       <c r="E599" t="n">
-        <v>72.22</v>
+        <v>77.78</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -83288,7 +83356,7 @@
         </is>
       </c>
       <c r="E600" t="n">
-        <v>72.22</v>
+        <v>77.78</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -83318,7 +83386,7 @@
         </is>
       </c>
       <c r="E601" t="n">
-        <v>72.22</v>
+        <v>77.78</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -83348,7 +83416,7 @@
         </is>
       </c>
       <c r="E602" t="n">
-        <v>72.22</v>
+        <v>77.78</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -83378,7 +83446,7 @@
         </is>
       </c>
       <c r="E603" t="n">
-        <v>72.22</v>
+        <v>77.78</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -83408,7 +83476,7 @@
         </is>
       </c>
       <c r="E604" t="n">
-        <v>72.22</v>
+        <v>77.78</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -83438,7 +83506,7 @@
         </is>
       </c>
       <c r="E605" t="n">
-        <v>72.22</v>
+        <v>77.78</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -83468,7 +83536,7 @@
         </is>
       </c>
       <c r="E606" t="n">
-        <v>72.22</v>
+        <v>77.78</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -83498,7 +83566,7 @@
         </is>
       </c>
       <c r="E607" t="n">
-        <v>72.22</v>
+        <v>77.78</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -83528,7 +83596,7 @@
         </is>
       </c>
       <c r="E608" t="n">
-        <v>72.22</v>
+        <v>77.78</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -83558,7 +83626,7 @@
         </is>
       </c>
       <c r="E609" t="n">
-        <v>72.22</v>
+        <v>77.78</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -83588,7 +83656,7 @@
         </is>
       </c>
       <c r="E610" t="n">
-        <v>72.22</v>
+        <v>77.78</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -83618,7 +83686,7 @@
         </is>
       </c>
       <c r="E611" t="n">
-        <v>72.22</v>
+        <v>77.78</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -83648,7 +83716,7 @@
         </is>
       </c>
       <c r="E612" t="n">
-        <v>72.22</v>
+        <v>77.78</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -83692,7 +83760,7 @@
       <c r="C614" t="inlineStr"/>
       <c r="D614" t="inlineStr">
         <is>
-          <t>Célula 42</t>
+          <t>Célula 43</t>
         </is>
       </c>
       <c r="E614" t="n">

--- a/data/diagnostico_coincidencias.xlsx
+++ b/data/diagnostico_coincidencias.xlsx
@@ -877,7 +877,7 @@
         <v>8</v>
       </c>
       <c r="H11" t="n">
-        <v>69.91</v>
+        <v>72.69</v>
       </c>
     </row>
     <row r="12">
@@ -1261,7 +1261,7 @@
         <v>17</v>
       </c>
       <c r="H23" t="n">
-        <v>27.45</v>
+        <v>27.02</v>
       </c>
     </row>
     <row r="24">
@@ -1293,7 +1293,7 @@
         <v>23</v>
       </c>
       <c r="H24" t="n">
-        <v>30.36</v>
+        <v>31.56</v>
       </c>
     </row>
     <row r="25">
@@ -1389,7 +1389,7 @@
         <v>9</v>
       </c>
       <c r="H27" t="n">
-        <v>93.83</v>
+        <v>91.36</v>
       </c>
     </row>
     <row r="28">
@@ -1485,7 +1485,7 @@
         <v>9</v>
       </c>
       <c r="H30" t="n">
-        <v>87.65000000000001</v>
+        <v>88.89</v>
       </c>
     </row>
     <row r="31">
@@ -1517,7 +1517,7 @@
         <v>23</v>
       </c>
       <c r="H31" t="n">
-        <v>23.35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32">
@@ -1677,7 +1677,7 @@
         <v>13</v>
       </c>
       <c r="H36" t="n">
-        <v>24.5</v>
+        <v>24.78</v>
       </c>
     </row>
     <row r="37">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P35" t="n">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P37" t="n">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P43" t="n">
@@ -5295,7 +5295,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P51" t="n">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P53" t="n">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P59" t="n">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P61" t="n">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P67" t="n">
@@ -7119,7 +7119,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P69" t="n">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P75" t="n">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P77" t="n">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P83" t="n">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P85" t="n">
@@ -8781,7 +8781,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P91" t="n">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P93" t="n">
@@ -12310,7 +12310,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P138" t="n">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P139" t="n">
@@ -12480,7 +12480,7 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P140" t="n">
@@ -12567,14 +12567,14 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P141" t="n">
         <v>100</v>
       </c>
       <c r="Q141" t="n">
-        <v>69.91</v>
+        <v>72.69</v>
       </c>
       <c r="R141" t="n">
         <v>8</v>
@@ -12650,7 +12650,7 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P142" t="n">
@@ -12733,7 +12733,7 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P143" t="n">
@@ -12816,7 +12816,7 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P144" t="n">
@@ -12899,14 +12899,14 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P145" t="n">
         <v>100</v>
       </c>
       <c r="Q145" t="n">
-        <v>69.91</v>
+        <v>72.69</v>
       </c>
       <c r="R145" t="n">
         <v>8</v>
@@ -12982,7 +12982,7 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P146" t="n">
@@ -13226,7 +13226,7 @@
         <v>50</v>
       </c>
       <c r="Q149" t="n">
-        <v>69.91</v>
+        <v>72.69</v>
       </c>
       <c r="R149" t="n">
         <v>4</v>
@@ -13302,7 +13302,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P150" t="n">
@@ -13554,7 +13554,7 @@
         <v>50</v>
       </c>
       <c r="Q153" t="n">
-        <v>69.91</v>
+        <v>72.69</v>
       </c>
       <c r="R153" t="n">
         <v>4</v>
@@ -13630,7 +13630,7 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P154" t="n">
@@ -13874,7 +13874,7 @@
         <v>87.5</v>
       </c>
       <c r="Q157" t="n">
-        <v>69.91</v>
+        <v>72.69</v>
       </c>
       <c r="R157" t="n">
         <v>7</v>
@@ -13950,7 +13950,7 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P158" t="n">
@@ -14194,7 +14194,7 @@
         <v>87.5</v>
       </c>
       <c r="Q161" t="n">
-        <v>69.91</v>
+        <v>72.69</v>
       </c>
       <c r="R161" t="n">
         <v>7</v>
@@ -14510,7 +14510,7 @@
         <v>87.5</v>
       </c>
       <c r="Q165" t="n">
-        <v>69.91</v>
+        <v>72.69</v>
       </c>
       <c r="R165" t="n">
         <v>7</v>
@@ -14826,7 +14826,7 @@
         <v>87.5</v>
       </c>
       <c r="Q169" t="n">
-        <v>69.91</v>
+        <v>72.69</v>
       </c>
       <c r="R169" t="n">
         <v>7</v>
@@ -15142,7 +15142,7 @@
         <v>50</v>
       </c>
       <c r="Q173" t="n">
-        <v>69.91</v>
+        <v>72.69</v>
       </c>
       <c r="R173" t="n">
         <v>4</v>
@@ -15458,7 +15458,7 @@
         <v>50</v>
       </c>
       <c r="Q177" t="n">
-        <v>69.91</v>
+        <v>72.69</v>
       </c>
       <c r="R177" t="n">
         <v>4</v>
@@ -15774,7 +15774,7 @@
         <v>50</v>
       </c>
       <c r="Q181" t="n">
-        <v>69.91</v>
+        <v>72.69</v>
       </c>
       <c r="R181" t="n">
         <v>4</v>
@@ -16090,7 +16090,7 @@
         <v>50</v>
       </c>
       <c r="Q185" t="n">
-        <v>69.91</v>
+        <v>72.69</v>
       </c>
       <c r="R185" t="n">
         <v>4</v>
@@ -16403,13 +16403,13 @@
       </c>
       <c r="O189" t="inlineStr"/>
       <c r="P189" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Q189" t="n">
-        <v>69.91</v>
+        <v>72.69</v>
       </c>
       <c r="R189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S189" t="n">
         <v>8</v>
@@ -16719,13 +16719,13 @@
       </c>
       <c r="O193" t="inlineStr"/>
       <c r="P193" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Q193" t="n">
-        <v>69.91</v>
+        <v>72.69</v>
       </c>
       <c r="R193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S193" t="n">
         <v>8</v>
@@ -17035,13 +17035,13 @@
       </c>
       <c r="O197" t="inlineStr"/>
       <c r="P197" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Q197" t="n">
-        <v>69.91</v>
+        <v>72.69</v>
       </c>
       <c r="R197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S197" t="n">
         <v>8</v>
@@ -17351,13 +17351,13 @@
       </c>
       <c r="O201" t="inlineStr"/>
       <c r="P201" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Q201" t="n">
-        <v>69.91</v>
+        <v>72.69</v>
       </c>
       <c r="R201" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S201" t="n">
         <v>8</v>
@@ -17667,13 +17667,13 @@
       </c>
       <c r="O205" t="inlineStr"/>
       <c r="P205" t="n">
-        <v>69.90000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="Q205" t="n">
-        <v>69.91</v>
+        <v>72.69</v>
       </c>
       <c r="R205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S205" t="n">
         <v>8</v>
@@ -17746,7 +17746,7 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P206" t="n">
@@ -17829,7 +17829,7 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P207" t="n">
@@ -17912,7 +17912,7 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P208" t="n">
@@ -17995,7 +17995,7 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P209" t="n">
@@ -18078,7 +18078,7 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P210" t="n">
@@ -18161,7 +18161,7 @@
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P211" t="n">
@@ -18323,7 +18323,7 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P213" t="n">
@@ -18406,7 +18406,7 @@
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P214" t="n">
@@ -19358,7 +19358,7 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P226" t="n">
@@ -19599,7 +19599,7 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P229" t="n">
@@ -19761,7 +19761,7 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P231" t="n">
@@ -20002,7 +20002,7 @@
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P234" t="n">
@@ -20401,7 +20401,7 @@
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P239" t="n">
@@ -20563,7 +20563,7 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P241" t="n">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P244" t="n">
@@ -21203,7 +21203,7 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P249" t="n">
@@ -21602,7 +21602,7 @@
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P254" t="n">
@@ -22001,7 +22001,7 @@
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P259" t="n">
@@ -22400,7 +22400,7 @@
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P264" t="n">
@@ -24537,7 +24537,7 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P291" t="n">
@@ -24620,7 +24620,7 @@
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P292" t="n">
@@ -24703,7 +24703,7 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P293" t="n">
@@ -24786,7 +24786,7 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P294" t="n">
@@ -24869,7 +24869,7 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P295" t="n">
@@ -24952,7 +24952,7 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P296" t="n">
@@ -25114,7 +25114,7 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P298" t="n">
@@ -25197,7 +25197,7 @@
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P299" t="n">
@@ -25359,7 +25359,7 @@
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P301" t="n">
@@ -25442,7 +25442,7 @@
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P302" t="n">
@@ -25525,7 +25525,7 @@
       </c>
       <c r="O303" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P303" t="n">
@@ -25687,7 +25687,7 @@
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P305" t="n">
@@ -25770,7 +25770,7 @@
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P306" t="n">
@@ -25853,7 +25853,7 @@
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P307" t="n">
@@ -26015,7 +26015,7 @@
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P309" t="n">
@@ -26098,7 +26098,7 @@
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P310" t="n">
@@ -26181,7 +26181,7 @@
       </c>
       <c r="O311" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P311" t="n">
@@ -26343,7 +26343,7 @@
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P313" t="n">
@@ -26426,7 +26426,7 @@
       </c>
       <c r="O314" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P314" t="n">
@@ -26509,7 +26509,7 @@
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P315" t="n">
@@ -26671,7 +26671,7 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P317" t="n">
@@ -26754,7 +26754,7 @@
       </c>
       <c r="O318" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P318" t="n">
@@ -26837,7 +26837,7 @@
       </c>
       <c r="O319" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P319" t="n">
@@ -26999,7 +26999,7 @@
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P321" t="n">
@@ -27082,7 +27082,7 @@
       </c>
       <c r="O322" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P322" t="n">
@@ -27165,7 +27165,7 @@
       </c>
       <c r="O323" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P323" t="n">
@@ -27327,7 +27327,7 @@
       </c>
       <c r="O325" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P325" t="n">
@@ -27410,7 +27410,7 @@
       </c>
       <c r="O326" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P326" t="n">
@@ -27493,7 +27493,7 @@
       </c>
       <c r="O327" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P327" t="n">
@@ -27655,7 +27655,7 @@
       </c>
       <c r="O329" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P329" t="n">
@@ -27738,7 +27738,7 @@
       </c>
       <c r="O330" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P330" t="n">
@@ -27821,7 +27821,7 @@
       </c>
       <c r="O331" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P331" t="n">
@@ -27983,7 +27983,7 @@
       </c>
       <c r="O333" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P333" t="n">
@@ -28066,7 +28066,7 @@
       </c>
       <c r="O334" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P334" t="n">
@@ -28149,7 +28149,7 @@
       </c>
       <c r="O335" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P335" t="n">
@@ -29812,7 +29812,7 @@
       </c>
       <c r="O356" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P356" t="n">
@@ -29895,7 +29895,7 @@
       </c>
       <c r="O357" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P357" t="n">
@@ -29978,7 +29978,7 @@
       </c>
       <c r="O358" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P358" t="n">
@@ -30061,7 +30061,7 @@
       </c>
       <c r="O359" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P359" t="n">
@@ -30144,7 +30144,7 @@
       </c>
       <c r="O360" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P360" t="n">
@@ -30227,7 +30227,7 @@
       </c>
       <c r="O361" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P361" t="n">
@@ -30310,7 +30310,7 @@
       </c>
       <c r="O362" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P362" t="n">
@@ -30393,7 +30393,7 @@
       </c>
       <c r="O363" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P363" t="n">
@@ -30476,7 +30476,7 @@
       </c>
       <c r="O364" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P364" t="n">
@@ -30559,7 +30559,7 @@
       </c>
       <c r="O365" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P365" t="n">
@@ -30642,7 +30642,7 @@
       </c>
       <c r="O366" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P366" t="n">
@@ -30725,7 +30725,7 @@
       </c>
       <c r="O367" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P367" t="n">
@@ -30966,7 +30966,7 @@
       </c>
       <c r="O370" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P370" t="n">
@@ -31207,7 +31207,7 @@
       </c>
       <c r="O373" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P373" t="n">
@@ -31448,7 +31448,7 @@
       </c>
       <c r="O376" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P376" t="n">
@@ -31689,7 +31689,7 @@
       </c>
       <c r="O379" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P379" t="n">
@@ -31930,7 +31930,7 @@
       </c>
       <c r="O382" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P382" t="n">
@@ -32171,7 +32171,7 @@
       </c>
       <c r="O385" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P385" t="n">
@@ -32412,7 +32412,7 @@
       </c>
       <c r="O388" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P388" t="n">
@@ -32653,7 +32653,7 @@
       </c>
       <c r="O391" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P391" t="n">
@@ -33842,7 +33842,7 @@
       </c>
       <c r="O406" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P406" t="n">
@@ -34083,7 +34083,7 @@
       </c>
       <c r="O409" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P409" t="n">
@@ -34324,7 +34324,7 @@
       </c>
       <c r="O412" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P412" t="n">
@@ -34565,7 +34565,7 @@
       </c>
       <c r="O415" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P415" t="n">
@@ -34806,7 +34806,7 @@
       </c>
       <c r="O418" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P418" t="n">
@@ -35047,7 +35047,7 @@
       </c>
       <c r="O421" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P421" t="n">
@@ -35288,7 +35288,7 @@
       </c>
       <c r="O424" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P424" t="n">
@@ -35529,7 +35529,7 @@
       </c>
       <c r="O427" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P427" t="n">
@@ -38385,14 +38385,14 @@
       </c>
       <c r="O463" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P463" t="n">
         <v>100</v>
       </c>
       <c r="Q463" t="n">
-        <v>27.45</v>
+        <v>27.02</v>
       </c>
       <c r="R463" t="n">
         <v>17</v>
@@ -38468,14 +38468,14 @@
       </c>
       <c r="O464" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P464" t="n">
         <v>100</v>
       </c>
       <c r="Q464" t="n">
-        <v>30.36</v>
+        <v>31.56</v>
       </c>
       <c r="R464" t="n">
         <v>23</v>
@@ -38630,14 +38630,14 @@
       </c>
       <c r="O466" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P466" t="n">
         <v>100</v>
       </c>
       <c r="Q466" t="n">
-        <v>27.45</v>
+        <v>27.02</v>
       </c>
       <c r="R466" t="n">
         <v>17</v>
@@ -38713,14 +38713,14 @@
       </c>
       <c r="O467" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P467" t="n">
         <v>100</v>
       </c>
       <c r="Q467" t="n">
-        <v>30.36</v>
+        <v>31.56</v>
       </c>
       <c r="R467" t="n">
         <v>23</v>
@@ -38796,14 +38796,14 @@
       </c>
       <c r="O468" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P468" t="n">
         <v>100</v>
       </c>
       <c r="Q468" t="n">
-        <v>27.45</v>
+        <v>27.02</v>
       </c>
       <c r="R468" t="n">
         <v>17</v>
@@ -38879,14 +38879,14 @@
       </c>
       <c r="O469" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P469" t="n">
         <v>100</v>
       </c>
       <c r="Q469" t="n">
-        <v>30.36</v>
+        <v>31.56</v>
       </c>
       <c r="R469" t="n">
         <v>23</v>
@@ -39041,14 +39041,14 @@
       </c>
       <c r="O471" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P471" t="n">
         <v>100</v>
       </c>
       <c r="Q471" t="n">
-        <v>27.45</v>
+        <v>27.02</v>
       </c>
       <c r="R471" t="n">
         <v>17</v>
@@ -39124,14 +39124,14 @@
       </c>
       <c r="O472" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P472" t="n">
         <v>100</v>
       </c>
       <c r="Q472" t="n">
-        <v>30.36</v>
+        <v>31.56</v>
       </c>
       <c r="R472" t="n">
         <v>23</v>
@@ -39210,7 +39210,7 @@
         <v>0</v>
       </c>
       <c r="Q473" t="n">
-        <v>27.45</v>
+        <v>27.02</v>
       </c>
       <c r="R473" t="n">
         <v>0</v>
@@ -39289,7 +39289,7 @@
         <v>0</v>
       </c>
       <c r="Q474" t="n">
-        <v>30.36</v>
+        <v>31.56</v>
       </c>
       <c r="R474" t="n">
         <v>0</v>
@@ -39447,7 +39447,7 @@
         <v>0</v>
       </c>
       <c r="Q476" t="n">
-        <v>27.45</v>
+        <v>27.02</v>
       </c>
       <c r="R476" t="n">
         <v>0</v>
@@ -39526,7 +39526,7 @@
         <v>0</v>
       </c>
       <c r="Q477" t="n">
-        <v>30.36</v>
+        <v>31.56</v>
       </c>
       <c r="R477" t="n">
         <v>0</v>
@@ -39605,7 +39605,7 @@
         <v>0</v>
       </c>
       <c r="Q478" t="n">
-        <v>27.45</v>
+        <v>27.02</v>
       </c>
       <c r="R478" t="n">
         <v>0</v>
@@ -39684,7 +39684,7 @@
         <v>0</v>
       </c>
       <c r="Q479" t="n">
-        <v>30.36</v>
+        <v>31.56</v>
       </c>
       <c r="R479" t="n">
         <v>0</v>
@@ -39842,7 +39842,7 @@
         <v>0</v>
       </c>
       <c r="Q481" t="n">
-        <v>27.45</v>
+        <v>27.02</v>
       </c>
       <c r="R481" t="n">
         <v>0</v>
@@ -39921,7 +39921,7 @@
         <v>0</v>
       </c>
       <c r="Q482" t="n">
-        <v>30.36</v>
+        <v>31.56</v>
       </c>
       <c r="R482" t="n">
         <v>0</v>
@@ -40000,7 +40000,7 @@
         <v>5.9</v>
       </c>
       <c r="Q483" t="n">
-        <v>27.45</v>
+        <v>27.02</v>
       </c>
       <c r="R483" t="n">
         <v>1</v>
@@ -40076,13 +40076,13 @@
       </c>
       <c r="O484" t="inlineStr"/>
       <c r="P484" t="n">
-        <v>30.4</v>
+        <v>39.1</v>
       </c>
       <c r="Q484" t="n">
-        <v>30.36</v>
+        <v>31.56</v>
       </c>
       <c r="R484" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="S484" t="n">
         <v>23</v>
@@ -40237,7 +40237,7 @@
         <v>5.9</v>
       </c>
       <c r="Q486" t="n">
-        <v>27.45</v>
+        <v>27.02</v>
       </c>
       <c r="R486" t="n">
         <v>1</v>
@@ -40313,13 +40313,13 @@
       </c>
       <c r="O487" t="inlineStr"/>
       <c r="P487" t="n">
-        <v>30.4</v>
+        <v>39.1</v>
       </c>
       <c r="Q487" t="n">
-        <v>30.36</v>
+        <v>31.56</v>
       </c>
       <c r="R487" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="S487" t="n">
         <v>23</v>
@@ -40392,13 +40392,13 @@
       </c>
       <c r="O488" t="inlineStr"/>
       <c r="P488" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="Q488" t="n">
-        <v>27.45</v>
+        <v>27.02</v>
       </c>
       <c r="R488" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S488" t="n">
         <v>17</v>
@@ -40471,13 +40471,13 @@
       </c>
       <c r="O489" t="inlineStr"/>
       <c r="P489" t="n">
-        <v>34.8</v>
+        <v>43.5</v>
       </c>
       <c r="Q489" t="n">
-        <v>30.36</v>
+        <v>31.56</v>
       </c>
       <c r="R489" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S489" t="n">
         <v>23</v>
@@ -40629,13 +40629,13 @@
       </c>
       <c r="O491" t="inlineStr"/>
       <c r="P491" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="Q491" t="n">
-        <v>27.45</v>
+        <v>27.02</v>
       </c>
       <c r="R491" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S491" t="n">
         <v>17</v>
@@ -40708,13 +40708,13 @@
       </c>
       <c r="O492" t="inlineStr"/>
       <c r="P492" t="n">
-        <v>34.8</v>
+        <v>43.5</v>
       </c>
       <c r="Q492" t="n">
-        <v>30.36</v>
+        <v>31.56</v>
       </c>
       <c r="R492" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S492" t="n">
         <v>23</v>
@@ -40787,13 +40787,13 @@
       </c>
       <c r="O493" t="inlineStr"/>
       <c r="P493" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="Q493" t="n">
-        <v>27.45</v>
+        <v>27.02</v>
       </c>
       <c r="R493" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S493" t="n">
         <v>17</v>
@@ -40866,13 +40866,13 @@
       </c>
       <c r="O494" t="inlineStr"/>
       <c r="P494" t="n">
-        <v>13</v>
+        <v>17.4</v>
       </c>
       <c r="Q494" t="n">
-        <v>30.36</v>
+        <v>31.56</v>
       </c>
       <c r="R494" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S494" t="n">
         <v>23</v>
@@ -41024,13 +41024,13 @@
       </c>
       <c r="O496" t="inlineStr"/>
       <c r="P496" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="Q496" t="n">
-        <v>27.45</v>
+        <v>27.02</v>
       </c>
       <c r="R496" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S496" t="n">
         <v>17</v>
@@ -41103,13 +41103,13 @@
       </c>
       <c r="O497" t="inlineStr"/>
       <c r="P497" t="n">
-        <v>13</v>
+        <v>17.4</v>
       </c>
       <c r="Q497" t="n">
-        <v>30.36</v>
+        <v>31.56</v>
       </c>
       <c r="R497" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S497" t="n">
         <v>23</v>
@@ -41185,7 +41185,7 @@
         <v>0</v>
       </c>
       <c r="Q498" t="n">
-        <v>27.45</v>
+        <v>27.02</v>
       </c>
       <c r="R498" t="n">
         <v>0</v>
@@ -41264,7 +41264,7 @@
         <v>17.4</v>
       </c>
       <c r="Q499" t="n">
-        <v>30.36</v>
+        <v>31.56</v>
       </c>
       <c r="R499" t="n">
         <v>4</v>
@@ -41422,7 +41422,7 @@
         <v>0</v>
       </c>
       <c r="Q501" t="n">
-        <v>27.45</v>
+        <v>27.02</v>
       </c>
       <c r="R501" t="n">
         <v>0</v>
@@ -41501,7 +41501,7 @@
         <v>17.4</v>
       </c>
       <c r="Q502" t="n">
-        <v>30.36</v>
+        <v>31.56</v>
       </c>
       <c r="R502" t="n">
         <v>4</v>
@@ -41580,7 +41580,7 @@
         <v>0</v>
       </c>
       <c r="Q503" t="n">
-        <v>27.45</v>
+        <v>27.02</v>
       </c>
       <c r="R503" t="n">
         <v>0</v>
@@ -41659,7 +41659,7 @@
         <v>0</v>
       </c>
       <c r="Q504" t="n">
-        <v>30.36</v>
+        <v>31.56</v>
       </c>
       <c r="R504" t="n">
         <v>0</v>
@@ -41817,7 +41817,7 @@
         <v>0</v>
       </c>
       <c r="Q506" t="n">
-        <v>27.45</v>
+        <v>27.02</v>
       </c>
       <c r="R506" t="n">
         <v>0</v>
@@ -41896,7 +41896,7 @@
         <v>0</v>
       </c>
       <c r="Q507" t="n">
-        <v>30.36</v>
+        <v>31.56</v>
       </c>
       <c r="R507" t="n">
         <v>0</v>
@@ -41975,7 +41975,7 @@
         <v>0</v>
       </c>
       <c r="Q508" t="n">
-        <v>27.45</v>
+        <v>27.02</v>
       </c>
       <c r="R508" t="n">
         <v>0</v>
@@ -42054,7 +42054,7 @@
         <v>0</v>
       </c>
       <c r="Q509" t="n">
-        <v>30.36</v>
+        <v>31.56</v>
       </c>
       <c r="R509" t="n">
         <v>0</v>
@@ -42212,7 +42212,7 @@
         <v>0</v>
       </c>
       <c r="Q511" t="n">
-        <v>27.45</v>
+        <v>27.02</v>
       </c>
       <c r="R511" t="n">
         <v>0</v>
@@ -42291,7 +42291,7 @@
         <v>0</v>
       </c>
       <c r="Q512" t="n">
-        <v>30.36</v>
+        <v>31.56</v>
       </c>
       <c r="R512" t="n">
         <v>0</v>
@@ -42370,7 +42370,7 @@
         <v>0</v>
       </c>
       <c r="Q513" t="n">
-        <v>27.45</v>
+        <v>27.02</v>
       </c>
       <c r="R513" t="n">
         <v>0</v>
@@ -42449,7 +42449,7 @@
         <v>0</v>
       </c>
       <c r="Q514" t="n">
-        <v>30.36</v>
+        <v>31.56</v>
       </c>
       <c r="R514" t="n">
         <v>0</v>
@@ -42607,7 +42607,7 @@
         <v>0</v>
       </c>
       <c r="Q516" t="n">
-        <v>27.45</v>
+        <v>27.02</v>
       </c>
       <c r="R516" t="n">
         <v>0</v>
@@ -42686,7 +42686,7 @@
         <v>0</v>
       </c>
       <c r="Q517" t="n">
-        <v>30.36</v>
+        <v>31.56</v>
       </c>
       <c r="R517" t="n">
         <v>0</v>
@@ -42765,7 +42765,7 @@
         <v>0</v>
       </c>
       <c r="Q518" t="n">
-        <v>27.45</v>
+        <v>27.02</v>
       </c>
       <c r="R518" t="n">
         <v>0</v>
@@ -42844,7 +42844,7 @@
         <v>0</v>
       </c>
       <c r="Q519" t="n">
-        <v>30.36</v>
+        <v>31.56</v>
       </c>
       <c r="R519" t="n">
         <v>0</v>
@@ -43002,7 +43002,7 @@
         <v>0</v>
       </c>
       <c r="Q521" t="n">
-        <v>27.45</v>
+        <v>27.02</v>
       </c>
       <c r="R521" t="n">
         <v>0</v>
@@ -43081,7 +43081,7 @@
         <v>0</v>
       </c>
       <c r="Q522" t="n">
-        <v>30.36</v>
+        <v>31.56</v>
       </c>
       <c r="R522" t="n">
         <v>0</v>
@@ -43160,7 +43160,7 @@
         <v>0</v>
       </c>
       <c r="Q523" t="n">
-        <v>27.45</v>
+        <v>27.02</v>
       </c>
       <c r="R523" t="n">
         <v>0</v>
@@ -43239,7 +43239,7 @@
         <v>0</v>
       </c>
       <c r="Q524" t="n">
-        <v>30.36</v>
+        <v>31.56</v>
       </c>
       <c r="R524" t="n">
         <v>0</v>
@@ -43397,7 +43397,7 @@
         <v>0</v>
       </c>
       <c r="Q526" t="n">
-        <v>27.45</v>
+        <v>27.02</v>
       </c>
       <c r="R526" t="n">
         <v>0</v>
@@ -43476,7 +43476,7 @@
         <v>0</v>
       </c>
       <c r="Q527" t="n">
-        <v>30.36</v>
+        <v>31.56</v>
       </c>
       <c r="R527" t="n">
         <v>0</v>
@@ -43555,7 +43555,7 @@
         <v>5.9</v>
       </c>
       <c r="Q528" t="n">
-        <v>27.45</v>
+        <v>27.02</v>
       </c>
       <c r="R528" t="n">
         <v>1</v>
@@ -43634,7 +43634,7 @@
         <v>0</v>
       </c>
       <c r="Q529" t="n">
-        <v>30.36</v>
+        <v>31.56</v>
       </c>
       <c r="R529" t="n">
         <v>0</v>
@@ -43792,7 +43792,7 @@
         <v>5.9</v>
       </c>
       <c r="Q531" t="n">
-        <v>27.45</v>
+        <v>27.02</v>
       </c>
       <c r="R531" t="n">
         <v>1</v>
@@ -43871,7 +43871,7 @@
         <v>0</v>
       </c>
       <c r="Q532" t="n">
-        <v>30.36</v>
+        <v>31.56</v>
       </c>
       <c r="R532" t="n">
         <v>0</v>
@@ -43950,7 +43950,7 @@
         <v>5.9</v>
       </c>
       <c r="Q533" t="n">
-        <v>27.45</v>
+        <v>27.02</v>
       </c>
       <c r="R533" t="n">
         <v>1</v>
@@ -44029,7 +44029,7 @@
         <v>0</v>
       </c>
       <c r="Q534" t="n">
-        <v>30.36</v>
+        <v>31.56</v>
       </c>
       <c r="R534" t="n">
         <v>0</v>
@@ -44187,7 +44187,7 @@
         <v>5.9</v>
       </c>
       <c r="Q536" t="n">
-        <v>27.45</v>
+        <v>27.02</v>
       </c>
       <c r="R536" t="n">
         <v>1</v>
@@ -44266,7 +44266,7 @@
         <v>0</v>
       </c>
       <c r="Q537" t="n">
-        <v>30.36</v>
+        <v>31.56</v>
       </c>
       <c r="R537" t="n">
         <v>0</v>
@@ -44345,7 +44345,7 @@
         <v>5.9</v>
       </c>
       <c r="Q538" t="n">
-        <v>27.45</v>
+        <v>27.02</v>
       </c>
       <c r="R538" t="n">
         <v>1</v>
@@ -44424,7 +44424,7 @@
         <v>0</v>
       </c>
       <c r="Q539" t="n">
-        <v>30.36</v>
+        <v>31.56</v>
       </c>
       <c r="R539" t="n">
         <v>0</v>
@@ -44582,7 +44582,7 @@
         <v>5.9</v>
       </c>
       <c r="Q541" t="n">
-        <v>27.45</v>
+        <v>27.02</v>
       </c>
       <c r="R541" t="n">
         <v>1</v>
@@ -44661,7 +44661,7 @@
         <v>0</v>
       </c>
       <c r="Q542" t="n">
-        <v>30.36</v>
+        <v>31.56</v>
       </c>
       <c r="R542" t="n">
         <v>0</v>
@@ -44737,10 +44737,10 @@
       </c>
       <c r="O543" t="inlineStr"/>
       <c r="P543" t="n">
-        <v>27.5</v>
+        <v>27</v>
       </c>
       <c r="Q543" t="n">
-        <v>27.45</v>
+        <v>27.02</v>
       </c>
       <c r="R543" t="n">
         <v>0</v>
@@ -44816,10 +44816,10 @@
       </c>
       <c r="O544" t="inlineStr"/>
       <c r="P544" t="n">
-        <v>30.4</v>
+        <v>31.6</v>
       </c>
       <c r="Q544" t="n">
-        <v>30.36</v>
+        <v>31.56</v>
       </c>
       <c r="R544" t="n">
         <v>0</v>
@@ -44974,10 +44974,10 @@
       </c>
       <c r="O546" t="inlineStr"/>
       <c r="P546" t="n">
-        <v>27.5</v>
+        <v>27</v>
       </c>
       <c r="Q546" t="n">
-        <v>27.45</v>
+        <v>27.02</v>
       </c>
       <c r="R546" t="n">
         <v>0</v>
@@ -45053,10 +45053,10 @@
       </c>
       <c r="O547" t="inlineStr"/>
       <c r="P547" t="n">
-        <v>30.4</v>
+        <v>31.6</v>
       </c>
       <c r="Q547" t="n">
-        <v>30.36</v>
+        <v>31.56</v>
       </c>
       <c r="R547" t="n">
         <v>0</v>
@@ -45132,7 +45132,7 @@
       </c>
       <c r="O548" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P548" t="n">
@@ -45215,14 +45215,14 @@
       </c>
       <c r="O549" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P549" t="n">
         <v>100</v>
       </c>
       <c r="Q549" t="n">
-        <v>93.83</v>
+        <v>91.36</v>
       </c>
       <c r="R549" t="n">
         <v>9</v>
@@ -45298,7 +45298,7 @@
       </c>
       <c r="O550" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P550" t="n">
@@ -45460,14 +45460,14 @@
       </c>
       <c r="O552" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P552" t="n">
         <v>100</v>
       </c>
       <c r="Q552" t="n">
-        <v>93.83</v>
+        <v>91.36</v>
       </c>
       <c r="R552" t="n">
         <v>9</v>
@@ -45543,7 +45543,7 @@
       </c>
       <c r="O553" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P553" t="n">
@@ -45708,7 +45708,7 @@
         <v>55.6</v>
       </c>
       <c r="Q555" t="n">
-        <v>93.83</v>
+        <v>91.36</v>
       </c>
       <c r="R555" t="n">
         <v>5</v>
@@ -45945,7 +45945,7 @@
         <v>55.6</v>
       </c>
       <c r="Q558" t="n">
-        <v>93.83</v>
+        <v>91.36</v>
       </c>
       <c r="R558" t="n">
         <v>5</v>
@@ -46179,14 +46179,14 @@
       </c>
       <c r="O561" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P561" t="n">
         <v>100</v>
       </c>
       <c r="Q561" t="n">
-        <v>93.83</v>
+        <v>91.36</v>
       </c>
       <c r="R561" t="n">
         <v>9</v>
@@ -46420,14 +46420,14 @@
       </c>
       <c r="O564" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P564" t="n">
         <v>100</v>
       </c>
       <c r="Q564" t="n">
-        <v>93.83</v>
+        <v>91.36</v>
       </c>
       <c r="R564" t="n">
         <v>9</v>
@@ -46661,14 +46661,14 @@
       </c>
       <c r="O567" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P567" t="n">
         <v>100</v>
       </c>
       <c r="Q567" t="n">
-        <v>93.83</v>
+        <v>91.36</v>
       </c>
       <c r="R567" t="n">
         <v>9</v>
@@ -46902,14 +46902,14 @@
       </c>
       <c r="O570" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P570" t="n">
         <v>100</v>
       </c>
       <c r="Q570" t="n">
-        <v>93.83</v>
+        <v>91.36</v>
       </c>
       <c r="R570" t="n">
         <v>9</v>
@@ -47143,14 +47143,14 @@
       </c>
       <c r="O573" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P573" t="n">
         <v>100</v>
       </c>
       <c r="Q573" t="n">
-        <v>93.83</v>
+        <v>91.36</v>
       </c>
       <c r="R573" t="n">
         <v>9</v>
@@ -47384,14 +47384,14 @@
       </c>
       <c r="O576" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P576" t="n">
         <v>100</v>
       </c>
       <c r="Q576" t="n">
-        <v>93.83</v>
+        <v>91.36</v>
       </c>
       <c r="R576" t="n">
         <v>9</v>
@@ -47625,14 +47625,14 @@
       </c>
       <c r="O579" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P579" t="n">
         <v>100</v>
       </c>
       <c r="Q579" t="n">
-        <v>93.83</v>
+        <v>91.36</v>
       </c>
       <c r="R579" t="n">
         <v>9</v>
@@ -47866,14 +47866,14 @@
       </c>
       <c r="O582" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P582" t="n">
         <v>100</v>
       </c>
       <c r="Q582" t="n">
-        <v>93.83</v>
+        <v>91.36</v>
       </c>
       <c r="R582" t="n">
         <v>9</v>
@@ -48105,19 +48105,15 @@
           <t>programada</t>
         </is>
       </c>
-      <c r="O585" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
+      <c r="O585" t="inlineStr"/>
       <c r="P585" t="n">
-        <v>100</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="Q585" t="n">
-        <v>93.83</v>
+        <v>91.36</v>
       </c>
       <c r="R585" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S585" t="n">
         <v>9</v>
@@ -48348,13 +48344,13 @@
       </c>
       <c r="O588" t="inlineStr"/>
       <c r="P588" t="n">
-        <v>66.7</v>
+        <v>55.6</v>
       </c>
       <c r="Q588" t="n">
-        <v>93.83</v>
+        <v>91.36</v>
       </c>
       <c r="R588" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S588" t="n">
         <v>9</v>
@@ -48585,13 +48581,13 @@
       </c>
       <c r="O591" t="inlineStr"/>
       <c r="P591" t="n">
-        <v>66.7</v>
+        <v>55.6</v>
       </c>
       <c r="Q591" t="n">
-        <v>93.83</v>
+        <v>91.36</v>
       </c>
       <c r="R591" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S591" t="n">
         <v>9</v>
@@ -48822,13 +48818,13 @@
       </c>
       <c r="O594" t="inlineStr"/>
       <c r="P594" t="n">
-        <v>66.7</v>
+        <v>55.6</v>
       </c>
       <c r="Q594" t="n">
-        <v>93.83</v>
+        <v>91.36</v>
       </c>
       <c r="R594" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S594" t="n">
         <v>9</v>
@@ -49059,13 +49055,13 @@
       </c>
       <c r="O597" t="inlineStr"/>
       <c r="P597" t="n">
-        <v>93.8</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="Q597" t="n">
-        <v>93.83</v>
+        <v>91.36</v>
       </c>
       <c r="R597" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S597" t="n">
         <v>9</v>
@@ -49217,7 +49213,7 @@
       </c>
       <c r="O599" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P599" t="n">
@@ -49300,14 +49296,14 @@
       </c>
       <c r="O600" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P600" t="n">
         <v>100</v>
       </c>
       <c r="Q600" t="n">
-        <v>87.65000000000001</v>
+        <v>88.89</v>
       </c>
       <c r="R600" t="n">
         <v>9</v>
@@ -49383,14 +49379,14 @@
       </c>
       <c r="O601" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P601" t="n">
         <v>100</v>
       </c>
       <c r="Q601" t="n">
-        <v>23.35</v>
+        <v>24</v>
       </c>
       <c r="R601" t="n">
         <v>23</v>
@@ -49466,14 +49462,14 @@
       </c>
       <c r="O602" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P602" t="n">
         <v>100</v>
       </c>
       <c r="Q602" t="n">
-        <v>23.35</v>
+        <v>24</v>
       </c>
       <c r="R602" t="n">
         <v>23</v>
@@ -49628,14 +49624,14 @@
       </c>
       <c r="O604" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P604" t="n">
         <v>100</v>
       </c>
       <c r="Q604" t="n">
-        <v>87.65000000000001</v>
+        <v>88.89</v>
       </c>
       <c r="R604" t="n">
         <v>9</v>
@@ -49711,14 +49707,14 @@
       </c>
       <c r="O605" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P605" t="n">
         <v>100</v>
       </c>
       <c r="Q605" t="n">
-        <v>23.35</v>
+        <v>24</v>
       </c>
       <c r="R605" t="n">
         <v>23</v>
@@ -49794,14 +49790,14 @@
       </c>
       <c r="O606" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P606" t="n">
         <v>100</v>
       </c>
       <c r="Q606" t="n">
-        <v>23.35</v>
+        <v>24</v>
       </c>
       <c r="R606" t="n">
         <v>23</v>
@@ -49959,7 +49955,7 @@
         <v>33.3</v>
       </c>
       <c r="Q608" t="n">
-        <v>87.65000000000001</v>
+        <v>88.89</v>
       </c>
       <c r="R608" t="n">
         <v>3</v>
@@ -50038,7 +50034,7 @@
         <v>0</v>
       </c>
       <c r="Q609" t="n">
-        <v>23.35</v>
+        <v>24</v>
       </c>
       <c r="R609" t="n">
         <v>0</v>
@@ -50117,7 +50113,7 @@
         <v>0</v>
       </c>
       <c r="Q610" t="n">
-        <v>23.35</v>
+        <v>24</v>
       </c>
       <c r="R610" t="n">
         <v>0</v>
@@ -50275,7 +50271,7 @@
         <v>33.3</v>
       </c>
       <c r="Q612" t="n">
-        <v>87.65000000000001</v>
+        <v>88.89</v>
       </c>
       <c r="R612" t="n">
         <v>3</v>
@@ -50354,7 +50350,7 @@
         <v>0</v>
       </c>
       <c r="Q613" t="n">
-        <v>23.35</v>
+        <v>24</v>
       </c>
       <c r="R613" t="n">
         <v>0</v>
@@ -50433,7 +50429,7 @@
         <v>0</v>
       </c>
       <c r="Q614" t="n">
-        <v>23.35</v>
+        <v>24</v>
       </c>
       <c r="R614" t="n">
         <v>0</v>
@@ -50588,14 +50584,14 @@
       </c>
       <c r="O616" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P616" t="n">
         <v>100</v>
       </c>
       <c r="Q616" t="n">
-        <v>87.65000000000001</v>
+        <v>88.89</v>
       </c>
       <c r="R616" t="n">
         <v>9</v>
@@ -50671,13 +50667,13 @@
       </c>
       <c r="O617" t="inlineStr"/>
       <c r="P617" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q617" t="n">
-        <v>23.35</v>
+        <v>24</v>
       </c>
       <c r="R617" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S617" t="n">
         <v>23</v>
@@ -50750,13 +50746,13 @@
       </c>
       <c r="O618" t="inlineStr"/>
       <c r="P618" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q618" t="n">
-        <v>23.35</v>
+        <v>24</v>
       </c>
       <c r="R618" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S618" t="n">
         <v>23</v>
@@ -50908,14 +50904,14 @@
       </c>
       <c r="O620" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P620" t="n">
         <v>100</v>
       </c>
       <c r="Q620" t="n">
-        <v>87.65000000000001</v>
+        <v>88.89</v>
       </c>
       <c r="R620" t="n">
         <v>9</v>
@@ -50991,13 +50987,13 @@
       </c>
       <c r="O621" t="inlineStr"/>
       <c r="P621" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q621" t="n">
-        <v>23.35</v>
+        <v>24</v>
       </c>
       <c r="R621" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S621" t="n">
         <v>23</v>
@@ -51070,13 +51066,13 @@
       </c>
       <c r="O622" t="inlineStr"/>
       <c r="P622" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q622" t="n">
-        <v>23.35</v>
+        <v>24</v>
       </c>
       <c r="R622" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S622" t="n">
         <v>23</v>
@@ -51228,14 +51224,14 @@
       </c>
       <c r="O624" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P624" t="n">
         <v>100</v>
       </c>
       <c r="Q624" t="n">
-        <v>87.65000000000001</v>
+        <v>88.89</v>
       </c>
       <c r="R624" t="n">
         <v>9</v>
@@ -51314,7 +51310,7 @@
         <v>0</v>
       </c>
       <c r="Q625" t="n">
-        <v>23.35</v>
+        <v>24</v>
       </c>
       <c r="R625" t="n">
         <v>0</v>
@@ -51393,7 +51389,7 @@
         <v>0</v>
       </c>
       <c r="Q626" t="n">
-        <v>23.35</v>
+        <v>24</v>
       </c>
       <c r="R626" t="n">
         <v>0</v>
@@ -51548,14 +51544,14 @@
       </c>
       <c r="O628" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P628" t="n">
         <v>100</v>
       </c>
       <c r="Q628" t="n">
-        <v>87.65000000000001</v>
+        <v>88.89</v>
       </c>
       <c r="R628" t="n">
         <v>9</v>
@@ -51634,7 +51630,7 @@
         <v>0</v>
       </c>
       <c r="Q629" t="n">
-        <v>23.35</v>
+        <v>24</v>
       </c>
       <c r="R629" t="n">
         <v>0</v>
@@ -51713,7 +51709,7 @@
         <v>0</v>
       </c>
       <c r="Q630" t="n">
-        <v>23.35</v>
+        <v>24</v>
       </c>
       <c r="R630" t="n">
         <v>0</v>
@@ -51868,14 +51864,14 @@
       </c>
       <c r="O632" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P632" t="n">
         <v>100</v>
       </c>
       <c r="Q632" t="n">
-        <v>87.65000000000001</v>
+        <v>88.89</v>
       </c>
       <c r="R632" t="n">
         <v>9</v>
@@ -51954,7 +51950,7 @@
         <v>0</v>
       </c>
       <c r="Q633" t="n">
-        <v>23.35</v>
+        <v>24</v>
       </c>
       <c r="R633" t="n">
         <v>0</v>
@@ -52033,7 +52029,7 @@
         <v>0</v>
       </c>
       <c r="Q634" t="n">
-        <v>23.35</v>
+        <v>24</v>
       </c>
       <c r="R634" t="n">
         <v>0</v>
@@ -52188,14 +52184,14 @@
       </c>
       <c r="O636" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P636" t="n">
         <v>100</v>
       </c>
       <c r="Q636" t="n">
-        <v>87.65000000000001</v>
+        <v>88.89</v>
       </c>
       <c r="R636" t="n">
         <v>9</v>
@@ -52274,7 +52270,7 @@
         <v>0</v>
       </c>
       <c r="Q637" t="n">
-        <v>23.35</v>
+        <v>24</v>
       </c>
       <c r="R637" t="n">
         <v>0</v>
@@ -52353,7 +52349,7 @@
         <v>0</v>
       </c>
       <c r="Q638" t="n">
-        <v>23.35</v>
+        <v>24</v>
       </c>
       <c r="R638" t="n">
         <v>0</v>
@@ -52508,14 +52504,14 @@
       </c>
       <c r="O640" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P640" t="n">
         <v>100</v>
       </c>
       <c r="Q640" t="n">
-        <v>87.65000000000001</v>
+        <v>88.89</v>
       </c>
       <c r="R640" t="n">
         <v>9</v>
@@ -52594,7 +52590,7 @@
         <v>0</v>
       </c>
       <c r="Q641" t="n">
-        <v>23.35</v>
+        <v>24</v>
       </c>
       <c r="R641" t="n">
         <v>0</v>
@@ -52673,7 +52669,7 @@
         <v>0</v>
       </c>
       <c r="Q642" t="n">
-        <v>23.35</v>
+        <v>24</v>
       </c>
       <c r="R642" t="n">
         <v>0</v>
@@ -52828,14 +52824,14 @@
       </c>
       <c r="O644" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P644" t="n">
         <v>100</v>
       </c>
       <c r="Q644" t="n">
-        <v>87.65000000000001</v>
+        <v>88.89</v>
       </c>
       <c r="R644" t="n">
         <v>9</v>
@@ -52914,7 +52910,7 @@
         <v>0</v>
       </c>
       <c r="Q645" t="n">
-        <v>23.35</v>
+        <v>24</v>
       </c>
       <c r="R645" t="n">
         <v>0</v>
@@ -52993,7 +52989,7 @@
         <v>0</v>
       </c>
       <c r="Q646" t="n">
-        <v>23.35</v>
+        <v>24</v>
       </c>
       <c r="R646" t="n">
         <v>0</v>
@@ -53148,13 +53144,13 @@
       </c>
       <c r="O648" t="inlineStr"/>
       <c r="P648" t="n">
-        <v>66.7</v>
+        <v>77.8</v>
       </c>
       <c r="Q648" t="n">
-        <v>87.65000000000001</v>
+        <v>88.89</v>
       </c>
       <c r="R648" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S648" t="n">
         <v>9</v>
@@ -53230,7 +53226,7 @@
         <v>0</v>
       </c>
       <c r="Q649" t="n">
-        <v>23.35</v>
+        <v>24</v>
       </c>
       <c r="R649" t="n">
         <v>0</v>
@@ -53309,7 +53305,7 @@
         <v>0</v>
       </c>
       <c r="Q650" t="n">
-        <v>23.35</v>
+        <v>24</v>
       </c>
       <c r="R650" t="n">
         <v>0</v>
@@ -53467,7 +53463,7 @@
         <v>55.6</v>
       </c>
       <c r="Q652" t="n">
-        <v>87.65000000000001</v>
+        <v>88.89</v>
       </c>
       <c r="R652" t="n">
         <v>5</v>
@@ -53546,7 +53542,7 @@
         <v>0</v>
       </c>
       <c r="Q653" t="n">
-        <v>23.35</v>
+        <v>24</v>
       </c>
       <c r="R653" t="n">
         <v>0</v>
@@ -53625,7 +53621,7 @@
         <v>0</v>
       </c>
       <c r="Q654" t="n">
-        <v>23.35</v>
+        <v>24</v>
       </c>
       <c r="R654" t="n">
         <v>0</v>
@@ -53783,7 +53779,7 @@
         <v>55.6</v>
       </c>
       <c r="Q656" t="n">
-        <v>87.65000000000001</v>
+        <v>88.89</v>
       </c>
       <c r="R656" t="n">
         <v>5</v>
@@ -53862,7 +53858,7 @@
         <v>0</v>
       </c>
       <c r="Q657" t="n">
-        <v>23.35</v>
+        <v>24</v>
       </c>
       <c r="R657" t="n">
         <v>0</v>
@@ -53941,7 +53937,7 @@
         <v>0</v>
       </c>
       <c r="Q658" t="n">
-        <v>23.35</v>
+        <v>24</v>
       </c>
       <c r="R658" t="n">
         <v>0</v>
@@ -54099,7 +54095,7 @@
         <v>55.6</v>
       </c>
       <c r="Q660" t="n">
-        <v>87.65000000000001</v>
+        <v>88.89</v>
       </c>
       <c r="R660" t="n">
         <v>5</v>
@@ -54178,7 +54174,7 @@
         <v>0</v>
       </c>
       <c r="Q661" t="n">
-        <v>23.35</v>
+        <v>24</v>
       </c>
       <c r="R661" t="n">
         <v>0</v>
@@ -54257,7 +54253,7 @@
         <v>0</v>
       </c>
       <c r="Q662" t="n">
-        <v>23.35</v>
+        <v>24</v>
       </c>
       <c r="R662" t="n">
         <v>0</v>
@@ -54412,10 +54408,10 @@
       </c>
       <c r="O664" t="inlineStr"/>
       <c r="P664" t="n">
-        <v>87.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="Q664" t="n">
-        <v>87.65000000000001</v>
+        <v>88.89</v>
       </c>
       <c r="R664" t="n">
         <v>2</v>
@@ -54491,10 +54487,10 @@
       </c>
       <c r="O665" t="inlineStr"/>
       <c r="P665" t="n">
-        <v>23.4</v>
+        <v>24</v>
       </c>
       <c r="Q665" t="n">
-        <v>23.35</v>
+        <v>24</v>
       </c>
       <c r="R665" t="n">
         <v>0</v>
@@ -54570,10 +54566,10 @@
       </c>
       <c r="O666" t="inlineStr"/>
       <c r="P666" t="n">
-        <v>23.4</v>
+        <v>24</v>
       </c>
       <c r="Q666" t="n">
-        <v>23.35</v>
+        <v>24</v>
       </c>
       <c r="R666" t="n">
         <v>0</v>
@@ -54649,7 +54645,7 @@
       </c>
       <c r="O667" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P667" t="n">
@@ -54732,7 +54728,7 @@
       </c>
       <c r="O668" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P668" t="n">
@@ -54815,7 +54811,7 @@
       </c>
       <c r="O669" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P669" t="n">
@@ -54898,7 +54894,7 @@
       </c>
       <c r="O670" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P670" t="n">
@@ -54981,7 +54977,7 @@
       </c>
       <c r="O671" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P671" t="n">
@@ -55064,7 +55060,7 @@
       </c>
       <c r="O672" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P672" t="n">
@@ -55147,7 +55143,7 @@
       </c>
       <c r="O673" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P673" t="n">
@@ -55230,7 +55226,7 @@
       </c>
       <c r="O674" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P674" t="n">
@@ -55313,7 +55309,7 @@
       </c>
       <c r="O675" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P675" t="n">
@@ -55475,7 +55471,7 @@
       </c>
       <c r="O677" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P677" t="n">
@@ -56617,7 +56613,7 @@
       </c>
       <c r="O691" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P691" t="n">
@@ -57095,7 +57091,7 @@
       </c>
       <c r="O697" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P697" t="n">
@@ -57573,7 +57569,7 @@
       </c>
       <c r="O703" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P703" t="n">
@@ -58051,7 +58047,7 @@
       </c>
       <c r="O709" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P709" t="n">
@@ -58533,7 +58529,7 @@
       </c>
       <c r="O715" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P715" t="n">
@@ -59011,7 +59007,7 @@
       </c>
       <c r="O721" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P721" t="n">
@@ -59489,7 +59485,7 @@
       </c>
       <c r="O727" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P727" t="n">
@@ -59967,7 +59963,7 @@
       </c>
       <c r="O733" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P733" t="n">
@@ -62823,14 +62819,14 @@
       </c>
       <c r="O769" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P769" t="n">
         <v>100</v>
       </c>
       <c r="Q769" t="n">
-        <v>24.5</v>
+        <v>24.78</v>
       </c>
       <c r="R769" t="n">
         <v>13</v>
@@ -62906,7 +62902,7 @@
       </c>
       <c r="O770" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P770" t="n">
@@ -62989,14 +62985,14 @@
       </c>
       <c r="O771" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P771" t="n">
         <v>100</v>
       </c>
       <c r="Q771" t="n">
-        <v>24.5</v>
+        <v>24.78</v>
       </c>
       <c r="R771" t="n">
         <v>13</v>
@@ -63072,7 +63068,7 @@
       </c>
       <c r="O772" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P772" t="n">
@@ -63158,7 +63154,7 @@
         <v>0</v>
       </c>
       <c r="Q773" t="n">
-        <v>24.5</v>
+        <v>24.78</v>
       </c>
       <c r="R773" t="n">
         <v>0</v>
@@ -63234,7 +63230,7 @@
       </c>
       <c r="O774" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P774" t="n">
@@ -63320,7 +63316,7 @@
         <v>0</v>
       </c>
       <c r="Q775" t="n">
-        <v>24.5</v>
+        <v>24.78</v>
       </c>
       <c r="R775" t="n">
         <v>0</v>
@@ -63396,7 +63392,7 @@
       </c>
       <c r="O776" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P776" t="n">
@@ -63482,7 +63478,7 @@
         <v>0</v>
       </c>
       <c r="Q777" t="n">
-        <v>24.5</v>
+        <v>24.78</v>
       </c>
       <c r="R777" t="n">
         <v>0</v>
@@ -63558,7 +63554,7 @@
       </c>
       <c r="O778" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P778" t="n">
@@ -63644,7 +63640,7 @@
         <v>0</v>
       </c>
       <c r="Q779" t="n">
-        <v>24.5</v>
+        <v>24.78</v>
       </c>
       <c r="R779" t="n">
         <v>0</v>
@@ -63720,7 +63716,7 @@
       </c>
       <c r="O780" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P780" t="n">
@@ -63806,7 +63802,7 @@
         <v>0</v>
       </c>
       <c r="Q781" t="n">
-        <v>24.5</v>
+        <v>24.78</v>
       </c>
       <c r="R781" t="n">
         <v>0</v>
@@ -63882,7 +63878,7 @@
       </c>
       <c r="O782" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P782" t="n">
@@ -63968,7 +63964,7 @@
         <v>0</v>
       </c>
       <c r="Q783" t="n">
-        <v>24.5</v>
+        <v>24.78</v>
       </c>
       <c r="R783" t="n">
         <v>0</v>
@@ -64044,7 +64040,7 @@
       </c>
       <c r="O784" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P784" t="n">
@@ -64130,7 +64126,7 @@
         <v>0</v>
       </c>
       <c r="Q785" t="n">
-        <v>24.5</v>
+        <v>24.78</v>
       </c>
       <c r="R785" t="n">
         <v>0</v>
@@ -64206,7 +64202,7 @@
       </c>
       <c r="O786" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P786" t="n">
@@ -64292,7 +64288,7 @@
         <v>0</v>
       </c>
       <c r="Q787" t="n">
-        <v>24.5</v>
+        <v>24.78</v>
       </c>
       <c r="R787" t="n">
         <v>0</v>
@@ -64368,7 +64364,7 @@
       </c>
       <c r="O788" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P788" t="n">
@@ -64454,7 +64450,7 @@
         <v>0</v>
       </c>
       <c r="Q789" t="n">
-        <v>24.5</v>
+        <v>24.78</v>
       </c>
       <c r="R789" t="n">
         <v>0</v>
@@ -64530,7 +64526,7 @@
       </c>
       <c r="O790" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P790" t="n">
@@ -64616,7 +64612,7 @@
         <v>0</v>
       </c>
       <c r="Q791" t="n">
-        <v>24.5</v>
+        <v>24.78</v>
       </c>
       <c r="R791" t="n">
         <v>0</v>
@@ -64692,7 +64688,7 @@
       </c>
       <c r="O792" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P792" t="n">
@@ -64778,7 +64774,7 @@
         <v>0</v>
       </c>
       <c r="Q793" t="n">
-        <v>24.5</v>
+        <v>24.78</v>
       </c>
       <c r="R793" t="n">
         <v>0</v>
@@ -64940,7 +64936,7 @@
         <v>0</v>
       </c>
       <c r="Q795" t="n">
-        <v>24.5</v>
+        <v>24.78</v>
       </c>
       <c r="R795" t="n">
         <v>0</v>
@@ -65102,7 +65098,7 @@
         <v>0</v>
       </c>
       <c r="Q797" t="n">
-        <v>24.5</v>
+        <v>24.78</v>
       </c>
       <c r="R797" t="n">
         <v>0</v>
@@ -65264,7 +65260,7 @@
         <v>0</v>
       </c>
       <c r="Q799" t="n">
-        <v>24.5</v>
+        <v>24.78</v>
       </c>
       <c r="R799" t="n">
         <v>0</v>
@@ -65423,10 +65419,10 @@
       </c>
       <c r="O801" t="inlineStr"/>
       <c r="P801" t="n">
-        <v>24.5</v>
+        <v>24.8</v>
       </c>
       <c r="Q801" t="n">
-        <v>24.5</v>
+        <v>24.78</v>
       </c>
       <c r="R801" t="n">
         <v>0</v>
@@ -66222,7 +66218,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>29.63</v>
+        <v>33.33</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -67892,7 +67888,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100</v>
+        <v>77.78</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -68072,7 +68068,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>72.22</v>
+        <v>83.33</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -71476,7 +71472,7 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>77.78</v>
+        <v>100</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -74056,7 +74052,7 @@
         </is>
       </c>
       <c r="E290" t="n">
-        <v>51.85</v>
+        <v>44.44</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -78226,7 +78222,7 @@
         </is>
       </c>
       <c r="E429" t="n">
-        <v>25.93</v>
+        <v>33.33</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -78706,7 +78702,7 @@
         </is>
       </c>
       <c r="E445" t="n">
-        <v>25.93</v>
+        <v>33.33</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -78766,7 +78762,7 @@
         </is>
       </c>
       <c r="E447" t="n">
-        <v>18.52</v>
+        <v>25.93</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -78826,7 +78822,7 @@
         </is>
       </c>
       <c r="E449" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -79816,7 +79812,7 @@
         </is>
       </c>
       <c r="E482" t="n">
-        <v>25.93</v>
+        <v>33.33</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -79846,7 +79842,7 @@
         </is>
       </c>
       <c r="E483" t="n">
-        <v>25.93</v>
+        <v>33.33</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -80206,7 +80202,7 @@
         </is>
       </c>
       <c r="E495" t="n">
-        <v>51.85</v>
+        <v>88.89</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>

--- a/data/diagnostico_coincidencias.xlsx
+++ b/data/diagnostico_coincidencias.xlsx
@@ -1069,7 +1069,7 @@
         <v>41</v>
       </c>
       <c r="H17" t="n">
-        <v>25.88</v>
+        <v>31.48</v>
       </c>
     </row>
     <row r="18">
@@ -1101,7 +1101,7 @@
         <v>18</v>
       </c>
       <c r="H18" t="n">
-        <v>97.53</v>
+        <v>98.77</v>
       </c>
     </row>
     <row r="19">
@@ -1229,7 +1229,7 @@
         <v>21</v>
       </c>
       <c r="H22" t="n">
-        <v>72.48999999999999</v>
+        <v>73.02</v>
       </c>
     </row>
     <row r="23">
@@ -1261,7 +1261,7 @@
         <v>17</v>
       </c>
       <c r="H23" t="n">
-        <v>27.02</v>
+        <v>27.45</v>
       </c>
     </row>
     <row r="24">
@@ -1293,7 +1293,7 @@
         <v>23</v>
       </c>
       <c r="H24" t="n">
-        <v>31.56</v>
+        <v>33.17</v>
       </c>
     </row>
     <row r="25">
@@ -1389,7 +1389,7 @@
         <v>9</v>
       </c>
       <c r="H27" t="n">
-        <v>91.36</v>
+        <v>93.83</v>
       </c>
     </row>
     <row r="28">
@@ -22562,13 +22562,13 @@
       </c>
       <c r="O266" t="inlineStr"/>
       <c r="P266" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="Q266" t="n">
         <v>75.93000000000001</v>
       </c>
       <c r="R266" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S266" t="n">
         <v>3</v>
@@ -22957,13 +22957,13 @@
       </c>
       <c r="O271" t="inlineStr"/>
       <c r="P271" t="n">
-        <v>33.3</v>
+        <v>66.7</v>
       </c>
       <c r="Q271" t="n">
         <v>75.93000000000001</v>
       </c>
       <c r="R271" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S271" t="n">
         <v>3</v>
@@ -23352,13 +23352,13 @@
       </c>
       <c r="O276" t="inlineStr"/>
       <c r="P276" t="n">
-        <v>33.3</v>
+        <v>66.7</v>
       </c>
       <c r="Q276" t="n">
         <v>75.93000000000001</v>
       </c>
       <c r="R276" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S276" t="n">
         <v>3</v>
@@ -23747,13 +23747,13 @@
       </c>
       <c r="O281" t="inlineStr"/>
       <c r="P281" t="n">
-        <v>33.3</v>
+        <v>66.7</v>
       </c>
       <c r="Q281" t="n">
         <v>75.93000000000001</v>
       </c>
       <c r="R281" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S281" t="n">
         <v>3</v>
@@ -24148,7 +24148,7 @@
         <v>75.93000000000001</v>
       </c>
       <c r="R286" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S286" t="n">
         <v>3</v>
@@ -24544,7 +24544,7 @@
         <v>100</v>
       </c>
       <c r="Q291" t="n">
-        <v>25.88</v>
+        <v>31.48</v>
       </c>
       <c r="R291" t="n">
         <v>41</v>
@@ -24627,7 +24627,7 @@
         <v>100</v>
       </c>
       <c r="Q292" t="n">
-        <v>97.53</v>
+        <v>98.77</v>
       </c>
       <c r="R292" t="n">
         <v>18</v>
@@ -24793,7 +24793,7 @@
         <v>100</v>
       </c>
       <c r="Q294" t="n">
-        <v>25.88</v>
+        <v>31.48</v>
       </c>
       <c r="R294" t="n">
         <v>41</v>
@@ -24876,7 +24876,7 @@
         <v>100</v>
       </c>
       <c r="Q295" t="n">
-        <v>97.53</v>
+        <v>98.77</v>
       </c>
       <c r="R295" t="n">
         <v>18</v>
@@ -25038,7 +25038,7 @@
         <v>0</v>
       </c>
       <c r="Q297" t="n">
-        <v>25.88</v>
+        <v>31.48</v>
       </c>
       <c r="R297" t="n">
         <v>0</v>
@@ -25121,7 +25121,7 @@
         <v>100</v>
       </c>
       <c r="Q298" t="n">
-        <v>97.53</v>
+        <v>98.77</v>
       </c>
       <c r="R298" t="n">
         <v>18</v>
@@ -25283,7 +25283,7 @@
         <v>0</v>
       </c>
       <c r="Q300" t="n">
-        <v>25.88</v>
+        <v>31.48</v>
       </c>
       <c r="R300" t="n">
         <v>0</v>
@@ -25366,7 +25366,7 @@
         <v>100</v>
       </c>
       <c r="Q301" t="n">
-        <v>97.53</v>
+        <v>98.77</v>
       </c>
       <c r="R301" t="n">
         <v>18</v>
@@ -25611,7 +25611,7 @@
         <v>0</v>
       </c>
       <c r="Q304" t="n">
-        <v>25.88</v>
+        <v>31.48</v>
       </c>
       <c r="R304" t="n">
         <v>0</v>
@@ -25694,7 +25694,7 @@
         <v>100</v>
       </c>
       <c r="Q305" t="n">
-        <v>97.53</v>
+        <v>98.77</v>
       </c>
       <c r="R305" t="n">
         <v>18</v>
@@ -25939,7 +25939,7 @@
         <v>0</v>
       </c>
       <c r="Q308" t="n">
-        <v>25.88</v>
+        <v>31.48</v>
       </c>
       <c r="R308" t="n">
         <v>0</v>
@@ -26022,7 +26022,7 @@
         <v>100</v>
       </c>
       <c r="Q309" t="n">
-        <v>97.53</v>
+        <v>98.77</v>
       </c>
       <c r="R309" t="n">
         <v>18</v>
@@ -26267,7 +26267,7 @@
         <v>0</v>
       </c>
       <c r="Q312" t="n">
-        <v>25.88</v>
+        <v>31.48</v>
       </c>
       <c r="R312" t="n">
         <v>0</v>
@@ -26350,7 +26350,7 @@
         <v>100</v>
       </c>
       <c r="Q313" t="n">
-        <v>97.53</v>
+        <v>98.77</v>
       </c>
       <c r="R313" t="n">
         <v>18</v>
@@ -26595,7 +26595,7 @@
         <v>0</v>
       </c>
       <c r="Q316" t="n">
-        <v>25.88</v>
+        <v>31.48</v>
       </c>
       <c r="R316" t="n">
         <v>0</v>
@@ -26678,7 +26678,7 @@
         <v>100</v>
       </c>
       <c r="Q317" t="n">
-        <v>97.53</v>
+        <v>98.77</v>
       </c>
       <c r="R317" t="n">
         <v>18</v>
@@ -26923,7 +26923,7 @@
         <v>0</v>
       </c>
       <c r="Q320" t="n">
-        <v>25.88</v>
+        <v>31.48</v>
       </c>
       <c r="R320" t="n">
         <v>0</v>
@@ -27006,7 +27006,7 @@
         <v>100</v>
       </c>
       <c r="Q321" t="n">
-        <v>97.53</v>
+        <v>98.77</v>
       </c>
       <c r="R321" t="n">
         <v>18</v>
@@ -27251,7 +27251,7 @@
         <v>0</v>
       </c>
       <c r="Q324" t="n">
-        <v>25.88</v>
+        <v>31.48</v>
       </c>
       <c r="R324" t="n">
         <v>0</v>
@@ -27334,7 +27334,7 @@
         <v>100</v>
       </c>
       <c r="Q325" t="n">
-        <v>97.53</v>
+        <v>98.77</v>
       </c>
       <c r="R325" t="n">
         <v>18</v>
@@ -27579,7 +27579,7 @@
         <v>0</v>
       </c>
       <c r="Q328" t="n">
-        <v>25.88</v>
+        <v>31.48</v>
       </c>
       <c r="R328" t="n">
         <v>0</v>
@@ -27662,7 +27662,7 @@
         <v>100</v>
       </c>
       <c r="Q329" t="n">
-        <v>97.53</v>
+        <v>98.77</v>
       </c>
       <c r="R329" t="n">
         <v>18</v>
@@ -27907,7 +27907,7 @@
         <v>0</v>
       </c>
       <c r="Q332" t="n">
-        <v>25.88</v>
+        <v>31.48</v>
       </c>
       <c r="R332" t="n">
         <v>0</v>
@@ -27990,7 +27990,7 @@
         <v>100</v>
       </c>
       <c r="Q333" t="n">
-        <v>97.53</v>
+        <v>98.77</v>
       </c>
       <c r="R333" t="n">
         <v>18</v>
@@ -28235,7 +28235,7 @@
         <v>0</v>
       </c>
       <c r="Q336" t="n">
-        <v>25.88</v>
+        <v>31.48</v>
       </c>
       <c r="R336" t="n">
         <v>0</v>
@@ -28311,13 +28311,13 @@
       </c>
       <c r="O337" t="inlineStr"/>
       <c r="P337" t="n">
-        <v>88.90000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="Q337" t="n">
-        <v>97.53</v>
+        <v>98.77</v>
       </c>
       <c r="R337" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S337" t="n">
         <v>18</v>
@@ -28551,7 +28551,7 @@
         <v>0</v>
       </c>
       <c r="Q340" t="n">
-        <v>25.88</v>
+        <v>31.48</v>
       </c>
       <c r="R340" t="n">
         <v>0</v>
@@ -28627,13 +28627,13 @@
       </c>
       <c r="O341" t="inlineStr"/>
       <c r="P341" t="n">
-        <v>88.90000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="Q341" t="n">
-        <v>97.53</v>
+        <v>98.77</v>
       </c>
       <c r="R341" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S341" t="n">
         <v>18</v>
@@ -28867,7 +28867,7 @@
         <v>0</v>
       </c>
       <c r="Q344" t="n">
-        <v>25.88</v>
+        <v>31.48</v>
       </c>
       <c r="R344" t="n">
         <v>0</v>
@@ -28943,13 +28943,13 @@
       </c>
       <c r="O345" t="inlineStr"/>
       <c r="P345" t="n">
-        <v>88.90000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="Q345" t="n">
-        <v>97.53</v>
+        <v>98.77</v>
       </c>
       <c r="R345" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S345" t="n">
         <v>18</v>
@@ -29183,7 +29183,7 @@
         <v>0</v>
       </c>
       <c r="Q348" t="n">
-        <v>25.88</v>
+        <v>31.48</v>
       </c>
       <c r="R348" t="n">
         <v>0</v>
@@ -29259,13 +29259,13 @@
       </c>
       <c r="O349" t="inlineStr"/>
       <c r="P349" t="n">
-        <v>88.90000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="Q349" t="n">
-        <v>97.53</v>
+        <v>98.77</v>
       </c>
       <c r="R349" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S349" t="n">
         <v>18</v>
@@ -29496,10 +29496,10 @@
       </c>
       <c r="O352" t="inlineStr"/>
       <c r="P352" t="n">
-        <v>25.9</v>
+        <v>31.5</v>
       </c>
       <c r="Q352" t="n">
-        <v>25.88</v>
+        <v>31.48</v>
       </c>
       <c r="R352" t="n">
         <v>0</v>
@@ -29575,13 +29575,13 @@
       </c>
       <c r="O353" t="inlineStr"/>
       <c r="P353" t="n">
-        <v>97.5</v>
+        <v>98.8</v>
       </c>
       <c r="Q353" t="n">
-        <v>97.53</v>
+        <v>98.77</v>
       </c>
       <c r="R353" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S353" t="n">
         <v>18</v>
@@ -29985,7 +29985,7 @@
         <v>100</v>
       </c>
       <c r="Q358" t="n">
-        <v>72.48999999999999</v>
+        <v>73.02</v>
       </c>
       <c r="R358" t="n">
         <v>21</v>
@@ -30234,7 +30234,7 @@
         <v>100</v>
       </c>
       <c r="Q361" t="n">
-        <v>72.48999999999999</v>
+        <v>73.02</v>
       </c>
       <c r="R361" t="n">
         <v>21</v>
@@ -30483,7 +30483,7 @@
         <v>100</v>
       </c>
       <c r="Q364" t="n">
-        <v>72.48999999999999</v>
+        <v>73.02</v>
       </c>
       <c r="R364" t="n">
         <v>21</v>
@@ -30732,7 +30732,7 @@
         <v>100</v>
       </c>
       <c r="Q367" t="n">
-        <v>72.48999999999999</v>
+        <v>73.02</v>
       </c>
       <c r="R367" t="n">
         <v>21</v>
@@ -30973,7 +30973,7 @@
         <v>100</v>
       </c>
       <c r="Q370" t="n">
-        <v>72.48999999999999</v>
+        <v>73.02</v>
       </c>
       <c r="R370" t="n">
         <v>21</v>
@@ -31214,7 +31214,7 @@
         <v>100</v>
       </c>
       <c r="Q373" t="n">
-        <v>72.48999999999999</v>
+        <v>73.02</v>
       </c>
       <c r="R373" t="n">
         <v>21</v>
@@ -31455,7 +31455,7 @@
         <v>100</v>
       </c>
       <c r="Q376" t="n">
-        <v>72.48999999999999</v>
+        <v>73.02</v>
       </c>
       <c r="R376" t="n">
         <v>21</v>
@@ -31696,7 +31696,7 @@
         <v>100</v>
       </c>
       <c r="Q379" t="n">
-        <v>72.48999999999999</v>
+        <v>73.02</v>
       </c>
       <c r="R379" t="n">
         <v>21</v>
@@ -31937,7 +31937,7 @@
         <v>100</v>
       </c>
       <c r="Q382" t="n">
-        <v>72.48999999999999</v>
+        <v>73.02</v>
       </c>
       <c r="R382" t="n">
         <v>21</v>
@@ -32178,7 +32178,7 @@
         <v>100</v>
       </c>
       <c r="Q385" t="n">
-        <v>72.48999999999999</v>
+        <v>73.02</v>
       </c>
       <c r="R385" t="n">
         <v>21</v>
@@ -32419,7 +32419,7 @@
         <v>100</v>
       </c>
       <c r="Q388" t="n">
-        <v>72.48999999999999</v>
+        <v>73.02</v>
       </c>
       <c r="R388" t="n">
         <v>21</v>
@@ -32660,7 +32660,7 @@
         <v>100</v>
       </c>
       <c r="Q391" t="n">
-        <v>72.48999999999999</v>
+        <v>73.02</v>
       </c>
       <c r="R391" t="n">
         <v>21</v>
@@ -32897,7 +32897,7 @@
         <v>42.9</v>
       </c>
       <c r="Q394" t="n">
-        <v>72.48999999999999</v>
+        <v>73.02</v>
       </c>
       <c r="R394" t="n">
         <v>9</v>
@@ -33134,7 +33134,7 @@
         <v>42.9</v>
       </c>
       <c r="Q397" t="n">
-        <v>72.48999999999999</v>
+        <v>73.02</v>
       </c>
       <c r="R397" t="n">
         <v>9</v>
@@ -33371,7 +33371,7 @@
         <v>42.9</v>
       </c>
       <c r="Q400" t="n">
-        <v>72.48999999999999</v>
+        <v>73.02</v>
       </c>
       <c r="R400" t="n">
         <v>9</v>
@@ -33608,7 +33608,7 @@
         <v>42.9</v>
       </c>
       <c r="Q403" t="n">
-        <v>72.48999999999999</v>
+        <v>73.02</v>
       </c>
       <c r="R403" t="n">
         <v>9</v>
@@ -33849,7 +33849,7 @@
         <v>100</v>
       </c>
       <c r="Q406" t="n">
-        <v>72.48999999999999</v>
+        <v>73.02</v>
       </c>
       <c r="R406" t="n">
         <v>21</v>
@@ -34090,7 +34090,7 @@
         <v>100</v>
       </c>
       <c r="Q409" t="n">
-        <v>72.48999999999999</v>
+        <v>73.02</v>
       </c>
       <c r="R409" t="n">
         <v>21</v>
@@ -34331,7 +34331,7 @@
         <v>100</v>
       </c>
       <c r="Q412" t="n">
-        <v>72.48999999999999</v>
+        <v>73.02</v>
       </c>
       <c r="R412" t="n">
         <v>21</v>
@@ -34572,7 +34572,7 @@
         <v>100</v>
       </c>
       <c r="Q415" t="n">
-        <v>72.48999999999999</v>
+        <v>73.02</v>
       </c>
       <c r="R415" t="n">
         <v>21</v>
@@ -34813,7 +34813,7 @@
         <v>100</v>
       </c>
       <c r="Q418" t="n">
-        <v>72.48999999999999</v>
+        <v>73.02</v>
       </c>
       <c r="R418" t="n">
         <v>21</v>
@@ -35054,7 +35054,7 @@
         <v>100</v>
       </c>
       <c r="Q421" t="n">
-        <v>72.48999999999999</v>
+        <v>73.02</v>
       </c>
       <c r="R421" t="n">
         <v>21</v>
@@ -35295,7 +35295,7 @@
         <v>100</v>
       </c>
       <c r="Q424" t="n">
-        <v>72.48999999999999</v>
+        <v>73.02</v>
       </c>
       <c r="R424" t="n">
         <v>21</v>
@@ -35536,7 +35536,7 @@
         <v>100</v>
       </c>
       <c r="Q427" t="n">
-        <v>72.48999999999999</v>
+        <v>73.02</v>
       </c>
       <c r="R427" t="n">
         <v>21</v>
@@ -35770,13 +35770,13 @@
       </c>
       <c r="O430" t="inlineStr"/>
       <c r="P430" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q430" t="n">
-        <v>72.48999999999999</v>
+        <v>73.02</v>
       </c>
       <c r="R430" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S430" t="n">
         <v>21</v>
@@ -36007,13 +36007,13 @@
       </c>
       <c r="O433" t="inlineStr"/>
       <c r="P433" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q433" t="n">
-        <v>72.48999999999999</v>
+        <v>73.02</v>
       </c>
       <c r="R433" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S433" t="n">
         <v>21</v>
@@ -36247,7 +36247,7 @@
         <v>9.5</v>
       </c>
       <c r="Q436" t="n">
-        <v>72.48999999999999</v>
+        <v>73.02</v>
       </c>
       <c r="R436" t="n">
         <v>2</v>
@@ -36484,7 +36484,7 @@
         <v>9.5</v>
       </c>
       <c r="Q439" t="n">
-        <v>72.48999999999999</v>
+        <v>73.02</v>
       </c>
       <c r="R439" t="n">
         <v>2</v>
@@ -36721,7 +36721,7 @@
         <v>9.5</v>
       </c>
       <c r="Q442" t="n">
-        <v>72.48999999999999</v>
+        <v>73.02</v>
       </c>
       <c r="R442" t="n">
         <v>2</v>
@@ -36958,7 +36958,7 @@
         <v>9.5</v>
       </c>
       <c r="Q445" t="n">
-        <v>72.48999999999999</v>
+        <v>73.02</v>
       </c>
       <c r="R445" t="n">
         <v>2</v>
@@ -37195,7 +37195,7 @@
         <v>9.5</v>
       </c>
       <c r="Q448" t="n">
-        <v>72.48999999999999</v>
+        <v>73.02</v>
       </c>
       <c r="R448" t="n">
         <v>2</v>
@@ -37432,7 +37432,7 @@
         <v>9.5</v>
       </c>
       <c r="Q451" t="n">
-        <v>72.48999999999999</v>
+        <v>73.02</v>
       </c>
       <c r="R451" t="n">
         <v>2</v>
@@ -37824,13 +37824,13 @@
       </c>
       <c r="O456" t="inlineStr"/>
       <c r="P456" t="n">
-        <v>72.5</v>
+        <v>73</v>
       </c>
       <c r="Q456" t="n">
-        <v>72.48999999999999</v>
+        <v>73.02</v>
       </c>
       <c r="R456" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S456" t="n">
         <v>21</v>
@@ -37907,13 +37907,13 @@
       </c>
       <c r="O457" t="inlineStr"/>
       <c r="P457" t="n">
-        <v>72.5</v>
+        <v>73</v>
       </c>
       <c r="Q457" t="n">
-        <v>72.48999999999999</v>
+        <v>73.02</v>
       </c>
       <c r="R457" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S457" t="n">
         <v>21</v>
@@ -38223,13 +38223,13 @@
       </c>
       <c r="O461" t="inlineStr"/>
       <c r="P461" t="n">
-        <v>72.5</v>
+        <v>73</v>
       </c>
       <c r="Q461" t="n">
-        <v>72.48999999999999</v>
+        <v>73.02</v>
       </c>
       <c r="R461" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S461" t="n">
         <v>21</v>
@@ -38306,13 +38306,13 @@
       </c>
       <c r="O462" t="inlineStr"/>
       <c r="P462" t="n">
-        <v>72.5</v>
+        <v>73</v>
       </c>
       <c r="Q462" t="n">
-        <v>72.48999999999999</v>
+        <v>73.02</v>
       </c>
       <c r="R462" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S462" t="n">
         <v>21</v>
@@ -38392,7 +38392,7 @@
         <v>100</v>
       </c>
       <c r="Q463" t="n">
-        <v>27.02</v>
+        <v>27.45</v>
       </c>
       <c r="R463" t="n">
         <v>17</v>
@@ -38475,7 +38475,7 @@
         <v>100</v>
       </c>
       <c r="Q464" t="n">
-        <v>31.56</v>
+        <v>33.17</v>
       </c>
       <c r="R464" t="n">
         <v>23</v>
@@ -38637,7 +38637,7 @@
         <v>100</v>
       </c>
       <c r="Q466" t="n">
-        <v>27.02</v>
+        <v>27.45</v>
       </c>
       <c r="R466" t="n">
         <v>17</v>
@@ -38720,7 +38720,7 @@
         <v>100</v>
       </c>
       <c r="Q467" t="n">
-        <v>31.56</v>
+        <v>33.17</v>
       </c>
       <c r="R467" t="n">
         <v>23</v>
@@ -38803,7 +38803,7 @@
         <v>100</v>
       </c>
       <c r="Q468" t="n">
-        <v>27.02</v>
+        <v>27.45</v>
       </c>
       <c r="R468" t="n">
         <v>17</v>
@@ -38886,7 +38886,7 @@
         <v>100</v>
       </c>
       <c r="Q469" t="n">
-        <v>31.56</v>
+        <v>33.17</v>
       </c>
       <c r="R469" t="n">
         <v>23</v>
@@ -39048,7 +39048,7 @@
         <v>100</v>
       </c>
       <c r="Q471" t="n">
-        <v>27.02</v>
+        <v>27.45</v>
       </c>
       <c r="R471" t="n">
         <v>17</v>
@@ -39131,7 +39131,7 @@
         <v>100</v>
       </c>
       <c r="Q472" t="n">
-        <v>31.56</v>
+        <v>33.17</v>
       </c>
       <c r="R472" t="n">
         <v>23</v>
@@ -39210,7 +39210,7 @@
         <v>0</v>
       </c>
       <c r="Q473" t="n">
-        <v>27.02</v>
+        <v>27.45</v>
       </c>
       <c r="R473" t="n">
         <v>0</v>
@@ -39289,7 +39289,7 @@
         <v>0</v>
       </c>
       <c r="Q474" t="n">
-        <v>31.56</v>
+        <v>33.17</v>
       </c>
       <c r="R474" t="n">
         <v>0</v>
@@ -39447,7 +39447,7 @@
         <v>0</v>
       </c>
       <c r="Q476" t="n">
-        <v>27.02</v>
+        <v>27.45</v>
       </c>
       <c r="R476" t="n">
         <v>0</v>
@@ -39526,7 +39526,7 @@
         <v>0</v>
       </c>
       <c r="Q477" t="n">
-        <v>31.56</v>
+        <v>33.17</v>
       </c>
       <c r="R477" t="n">
         <v>0</v>
@@ -39605,7 +39605,7 @@
         <v>0</v>
       </c>
       <c r="Q478" t="n">
-        <v>27.02</v>
+        <v>27.45</v>
       </c>
       <c r="R478" t="n">
         <v>0</v>
@@ -39684,7 +39684,7 @@
         <v>0</v>
       </c>
       <c r="Q479" t="n">
-        <v>31.56</v>
+        <v>33.17</v>
       </c>
       <c r="R479" t="n">
         <v>0</v>
@@ -39842,7 +39842,7 @@
         <v>0</v>
       </c>
       <c r="Q481" t="n">
-        <v>27.02</v>
+        <v>27.45</v>
       </c>
       <c r="R481" t="n">
         <v>0</v>
@@ -39921,7 +39921,7 @@
         <v>0</v>
       </c>
       <c r="Q482" t="n">
-        <v>31.56</v>
+        <v>33.17</v>
       </c>
       <c r="R482" t="n">
         <v>0</v>
@@ -39997,13 +39997,13 @@
       </c>
       <c r="O483" t="inlineStr"/>
       <c r="P483" t="n">
-        <v>5.9</v>
+        <v>11.8</v>
       </c>
       <c r="Q483" t="n">
-        <v>27.02</v>
+        <v>27.45</v>
       </c>
       <c r="R483" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S483" t="n">
         <v>17</v>
@@ -40076,13 +40076,13 @@
       </c>
       <c r="O484" t="inlineStr"/>
       <c r="P484" t="n">
-        <v>39.1</v>
+        <v>60.9</v>
       </c>
       <c r="Q484" t="n">
-        <v>31.56</v>
+        <v>33.17</v>
       </c>
       <c r="R484" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="S484" t="n">
         <v>23</v>
@@ -40234,13 +40234,13 @@
       </c>
       <c r="O486" t="inlineStr"/>
       <c r="P486" t="n">
-        <v>5.9</v>
+        <v>11.8</v>
       </c>
       <c r="Q486" t="n">
-        <v>27.02</v>
+        <v>27.45</v>
       </c>
       <c r="R486" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S486" t="n">
         <v>17</v>
@@ -40313,13 +40313,13 @@
       </c>
       <c r="O487" t="inlineStr"/>
       <c r="P487" t="n">
-        <v>39.1</v>
+        <v>60.9</v>
       </c>
       <c r="Q487" t="n">
-        <v>31.56</v>
+        <v>33.17</v>
       </c>
       <c r="R487" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="S487" t="n">
         <v>23</v>
@@ -40392,13 +40392,13 @@
       </c>
       <c r="O488" t="inlineStr"/>
       <c r="P488" t="n">
-        <v>5.9</v>
+        <v>11.8</v>
       </c>
       <c r="Q488" t="n">
-        <v>27.02</v>
+        <v>27.45</v>
       </c>
       <c r="R488" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S488" t="n">
         <v>17</v>
@@ -40471,13 +40471,13 @@
       </c>
       <c r="O489" t="inlineStr"/>
       <c r="P489" t="n">
-        <v>43.5</v>
+        <v>65.2</v>
       </c>
       <c r="Q489" t="n">
-        <v>31.56</v>
+        <v>33.17</v>
       </c>
       <c r="R489" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="S489" t="n">
         <v>23</v>
@@ -40629,13 +40629,13 @@
       </c>
       <c r="O491" t="inlineStr"/>
       <c r="P491" t="n">
-        <v>5.9</v>
+        <v>11.8</v>
       </c>
       <c r="Q491" t="n">
-        <v>27.02</v>
+        <v>27.45</v>
       </c>
       <c r="R491" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S491" t="n">
         <v>17</v>
@@ -40708,13 +40708,13 @@
       </c>
       <c r="O492" t="inlineStr"/>
       <c r="P492" t="n">
-        <v>43.5</v>
+        <v>65.2</v>
       </c>
       <c r="Q492" t="n">
-        <v>31.56</v>
+        <v>33.17</v>
       </c>
       <c r="R492" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="S492" t="n">
         <v>23</v>
@@ -40790,7 +40790,7 @@
         <v>0</v>
       </c>
       <c r="Q493" t="n">
-        <v>27.02</v>
+        <v>27.45</v>
       </c>
       <c r="R493" t="n">
         <v>0</v>
@@ -40869,7 +40869,7 @@
         <v>17.4</v>
       </c>
       <c r="Q494" t="n">
-        <v>31.56</v>
+        <v>33.17</v>
       </c>
       <c r="R494" t="n">
         <v>4</v>
@@ -41027,7 +41027,7 @@
         <v>0</v>
       </c>
       <c r="Q496" t="n">
-        <v>27.02</v>
+        <v>27.45</v>
       </c>
       <c r="R496" t="n">
         <v>0</v>
@@ -41106,7 +41106,7 @@
         <v>17.4</v>
       </c>
       <c r="Q497" t="n">
-        <v>31.56</v>
+        <v>33.17</v>
       </c>
       <c r="R497" t="n">
         <v>4</v>
@@ -41185,7 +41185,7 @@
         <v>0</v>
       </c>
       <c r="Q498" t="n">
-        <v>27.02</v>
+        <v>27.45</v>
       </c>
       <c r="R498" t="n">
         <v>0</v>
@@ -41264,7 +41264,7 @@
         <v>17.4</v>
       </c>
       <c r="Q499" t="n">
-        <v>31.56</v>
+        <v>33.17</v>
       </c>
       <c r="R499" t="n">
         <v>4</v>
@@ -41422,7 +41422,7 @@
         <v>0</v>
       </c>
       <c r="Q501" t="n">
-        <v>27.02</v>
+        <v>27.45</v>
       </c>
       <c r="R501" t="n">
         <v>0</v>
@@ -41501,7 +41501,7 @@
         <v>17.4</v>
       </c>
       <c r="Q502" t="n">
-        <v>31.56</v>
+        <v>33.17</v>
       </c>
       <c r="R502" t="n">
         <v>4</v>
@@ -41580,7 +41580,7 @@
         <v>0</v>
       </c>
       <c r="Q503" t="n">
-        <v>27.02</v>
+        <v>27.45</v>
       </c>
       <c r="R503" t="n">
         <v>0</v>
@@ -41659,7 +41659,7 @@
         <v>0</v>
       </c>
       <c r="Q504" t="n">
-        <v>31.56</v>
+        <v>33.17</v>
       </c>
       <c r="R504" t="n">
         <v>0</v>
@@ -41817,7 +41817,7 @@
         <v>0</v>
       </c>
       <c r="Q506" t="n">
-        <v>27.02</v>
+        <v>27.45</v>
       </c>
       <c r="R506" t="n">
         <v>0</v>
@@ -41896,7 +41896,7 @@
         <v>0</v>
       </c>
       <c r="Q507" t="n">
-        <v>31.56</v>
+        <v>33.17</v>
       </c>
       <c r="R507" t="n">
         <v>0</v>
@@ -41975,7 +41975,7 @@
         <v>0</v>
       </c>
       <c r="Q508" t="n">
-        <v>27.02</v>
+        <v>27.45</v>
       </c>
       <c r="R508" t="n">
         <v>0</v>
@@ -42054,7 +42054,7 @@
         <v>0</v>
       </c>
       <c r="Q509" t="n">
-        <v>31.56</v>
+        <v>33.17</v>
       </c>
       <c r="R509" t="n">
         <v>0</v>
@@ -42212,7 +42212,7 @@
         <v>0</v>
       </c>
       <c r="Q511" t="n">
-        <v>27.02</v>
+        <v>27.45</v>
       </c>
       <c r="R511" t="n">
         <v>0</v>
@@ -42291,7 +42291,7 @@
         <v>0</v>
       </c>
       <c r="Q512" t="n">
-        <v>31.56</v>
+        <v>33.17</v>
       </c>
       <c r="R512" t="n">
         <v>0</v>
@@ -42370,7 +42370,7 @@
         <v>0</v>
       </c>
       <c r="Q513" t="n">
-        <v>27.02</v>
+        <v>27.45</v>
       </c>
       <c r="R513" t="n">
         <v>0</v>
@@ -42449,7 +42449,7 @@
         <v>0</v>
       </c>
       <c r="Q514" t="n">
-        <v>31.56</v>
+        <v>33.17</v>
       </c>
       <c r="R514" t="n">
         <v>0</v>
@@ -42607,7 +42607,7 @@
         <v>0</v>
       </c>
       <c r="Q516" t="n">
-        <v>27.02</v>
+        <v>27.45</v>
       </c>
       <c r="R516" t="n">
         <v>0</v>
@@ -42686,7 +42686,7 @@
         <v>0</v>
       </c>
       <c r="Q517" t="n">
-        <v>31.56</v>
+        <v>33.17</v>
       </c>
       <c r="R517" t="n">
         <v>0</v>
@@ -42765,7 +42765,7 @@
         <v>0</v>
       </c>
       <c r="Q518" t="n">
-        <v>27.02</v>
+        <v>27.45</v>
       </c>
       <c r="R518" t="n">
         <v>0</v>
@@ -42844,7 +42844,7 @@
         <v>0</v>
       </c>
       <c r="Q519" t="n">
-        <v>31.56</v>
+        <v>33.17</v>
       </c>
       <c r="R519" t="n">
         <v>0</v>
@@ -43002,7 +43002,7 @@
         <v>0</v>
       </c>
       <c r="Q521" t="n">
-        <v>27.02</v>
+        <v>27.45</v>
       </c>
       <c r="R521" t="n">
         <v>0</v>
@@ -43081,7 +43081,7 @@
         <v>0</v>
       </c>
       <c r="Q522" t="n">
-        <v>31.56</v>
+        <v>33.17</v>
       </c>
       <c r="R522" t="n">
         <v>0</v>
@@ -43160,7 +43160,7 @@
         <v>0</v>
       </c>
       <c r="Q523" t="n">
-        <v>27.02</v>
+        <v>27.45</v>
       </c>
       <c r="R523" t="n">
         <v>0</v>
@@ -43239,7 +43239,7 @@
         <v>0</v>
       </c>
       <c r="Q524" t="n">
-        <v>31.56</v>
+        <v>33.17</v>
       </c>
       <c r="R524" t="n">
         <v>0</v>
@@ -43397,7 +43397,7 @@
         <v>0</v>
       </c>
       <c r="Q526" t="n">
-        <v>27.02</v>
+        <v>27.45</v>
       </c>
       <c r="R526" t="n">
         <v>0</v>
@@ -43476,7 +43476,7 @@
         <v>0</v>
       </c>
       <c r="Q527" t="n">
-        <v>31.56</v>
+        <v>33.17</v>
       </c>
       <c r="R527" t="n">
         <v>0</v>
@@ -43555,7 +43555,7 @@
         <v>5.9</v>
       </c>
       <c r="Q528" t="n">
-        <v>27.02</v>
+        <v>27.45</v>
       </c>
       <c r="R528" t="n">
         <v>1</v>
@@ -43634,7 +43634,7 @@
         <v>0</v>
       </c>
       <c r="Q529" t="n">
-        <v>31.56</v>
+        <v>33.17</v>
       </c>
       <c r="R529" t="n">
         <v>0</v>
@@ -43792,7 +43792,7 @@
         <v>5.9</v>
       </c>
       <c r="Q531" t="n">
-        <v>27.02</v>
+        <v>27.45</v>
       </c>
       <c r="R531" t="n">
         <v>1</v>
@@ -43871,7 +43871,7 @@
         <v>0</v>
       </c>
       <c r="Q532" t="n">
-        <v>31.56</v>
+        <v>33.17</v>
       </c>
       <c r="R532" t="n">
         <v>0</v>
@@ -43950,7 +43950,7 @@
         <v>5.9</v>
       </c>
       <c r="Q533" t="n">
-        <v>27.02</v>
+        <v>27.45</v>
       </c>
       <c r="R533" t="n">
         <v>1</v>
@@ -44029,7 +44029,7 @@
         <v>0</v>
       </c>
       <c r="Q534" t="n">
-        <v>31.56</v>
+        <v>33.17</v>
       </c>
       <c r="R534" t="n">
         <v>0</v>
@@ -44187,7 +44187,7 @@
         <v>5.9</v>
       </c>
       <c r="Q536" t="n">
-        <v>27.02</v>
+        <v>27.45</v>
       </c>
       <c r="R536" t="n">
         <v>1</v>
@@ -44266,7 +44266,7 @@
         <v>0</v>
       </c>
       <c r="Q537" t="n">
-        <v>31.56</v>
+        <v>33.17</v>
       </c>
       <c r="R537" t="n">
         <v>0</v>
@@ -44345,7 +44345,7 @@
         <v>5.9</v>
       </c>
       <c r="Q538" t="n">
-        <v>27.02</v>
+        <v>27.45</v>
       </c>
       <c r="R538" t="n">
         <v>1</v>
@@ -44424,7 +44424,7 @@
         <v>0</v>
       </c>
       <c r="Q539" t="n">
-        <v>31.56</v>
+        <v>33.17</v>
       </c>
       <c r="R539" t="n">
         <v>0</v>
@@ -44582,7 +44582,7 @@
         <v>5.9</v>
       </c>
       <c r="Q541" t="n">
-        <v>27.02</v>
+        <v>27.45</v>
       </c>
       <c r="R541" t="n">
         <v>1</v>
@@ -44661,7 +44661,7 @@
         <v>0</v>
       </c>
       <c r="Q542" t="n">
-        <v>31.56</v>
+        <v>33.17</v>
       </c>
       <c r="R542" t="n">
         <v>0</v>
@@ -44737,10 +44737,10 @@
       </c>
       <c r="O543" t="inlineStr"/>
       <c r="P543" t="n">
-        <v>27</v>
+        <v>27.5</v>
       </c>
       <c r="Q543" t="n">
-        <v>27.02</v>
+        <v>27.45</v>
       </c>
       <c r="R543" t="n">
         <v>0</v>
@@ -44816,10 +44816,10 @@
       </c>
       <c r="O544" t="inlineStr"/>
       <c r="P544" t="n">
-        <v>31.6</v>
+        <v>33.2</v>
       </c>
       <c r="Q544" t="n">
-        <v>31.56</v>
+        <v>33.17</v>
       </c>
       <c r="R544" t="n">
         <v>0</v>
@@ -44974,10 +44974,10 @@
       </c>
       <c r="O546" t="inlineStr"/>
       <c r="P546" t="n">
-        <v>27</v>
+        <v>27.5</v>
       </c>
       <c r="Q546" t="n">
-        <v>27.02</v>
+        <v>27.45</v>
       </c>
       <c r="R546" t="n">
         <v>0</v>
@@ -45053,10 +45053,10 @@
       </c>
       <c r="O547" t="inlineStr"/>
       <c r="P547" t="n">
-        <v>31.6</v>
+        <v>33.2</v>
       </c>
       <c r="Q547" t="n">
-        <v>31.56</v>
+        <v>33.17</v>
       </c>
       <c r="R547" t="n">
         <v>0</v>
@@ -45222,7 +45222,7 @@
         <v>100</v>
       </c>
       <c r="Q549" t="n">
-        <v>91.36</v>
+        <v>93.83</v>
       </c>
       <c r="R549" t="n">
         <v>9</v>
@@ -45467,7 +45467,7 @@
         <v>100</v>
       </c>
       <c r="Q552" t="n">
-        <v>91.36</v>
+        <v>93.83</v>
       </c>
       <c r="R552" t="n">
         <v>9</v>
@@ -45708,7 +45708,7 @@
         <v>55.6</v>
       </c>
       <c r="Q555" t="n">
-        <v>91.36</v>
+        <v>93.83</v>
       </c>
       <c r="R555" t="n">
         <v>5</v>
@@ -45945,7 +45945,7 @@
         <v>55.6</v>
       </c>
       <c r="Q558" t="n">
-        <v>91.36</v>
+        <v>93.83</v>
       </c>
       <c r="R558" t="n">
         <v>5</v>
@@ -46186,7 +46186,7 @@
         <v>100</v>
       </c>
       <c r="Q561" t="n">
-        <v>91.36</v>
+        <v>93.83</v>
       </c>
       <c r="R561" t="n">
         <v>9</v>
@@ -46427,7 +46427,7 @@
         <v>100</v>
       </c>
       <c r="Q564" t="n">
-        <v>91.36</v>
+        <v>93.83</v>
       </c>
       <c r="R564" t="n">
         <v>9</v>
@@ -46668,7 +46668,7 @@
         <v>100</v>
       </c>
       <c r="Q567" t="n">
-        <v>91.36</v>
+        <v>93.83</v>
       </c>
       <c r="R567" t="n">
         <v>9</v>
@@ -46909,7 +46909,7 @@
         <v>100</v>
       </c>
       <c r="Q570" t="n">
-        <v>91.36</v>
+        <v>93.83</v>
       </c>
       <c r="R570" t="n">
         <v>9</v>
@@ -47150,7 +47150,7 @@
         <v>100</v>
       </c>
       <c r="Q573" t="n">
-        <v>91.36</v>
+        <v>93.83</v>
       </c>
       <c r="R573" t="n">
         <v>9</v>
@@ -47391,7 +47391,7 @@
         <v>100</v>
       </c>
       <c r="Q576" t="n">
-        <v>91.36</v>
+        <v>93.83</v>
       </c>
       <c r="R576" t="n">
         <v>9</v>
@@ -47632,7 +47632,7 @@
         <v>100</v>
       </c>
       <c r="Q579" t="n">
-        <v>91.36</v>
+        <v>93.83</v>
       </c>
       <c r="R579" t="n">
         <v>9</v>
@@ -47873,7 +47873,7 @@
         <v>100</v>
       </c>
       <c r="Q582" t="n">
-        <v>91.36</v>
+        <v>93.83</v>
       </c>
       <c r="R582" t="n">
         <v>9</v>
@@ -48105,15 +48105,19 @@
           <t>programada</t>
         </is>
       </c>
-      <c r="O585" t="inlineStr"/>
+      <c r="O585" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
       <c r="P585" t="n">
-        <v>88.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="Q585" t="n">
-        <v>91.36</v>
+        <v>93.83</v>
       </c>
       <c r="R585" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S585" t="n">
         <v>9</v>
@@ -48344,13 +48348,13 @@
       </c>
       <c r="O588" t="inlineStr"/>
       <c r="P588" t="n">
-        <v>55.6</v>
+        <v>66.7</v>
       </c>
       <c r="Q588" t="n">
-        <v>91.36</v>
+        <v>93.83</v>
       </c>
       <c r="R588" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S588" t="n">
         <v>9</v>
@@ -48581,13 +48585,13 @@
       </c>
       <c r="O591" t="inlineStr"/>
       <c r="P591" t="n">
-        <v>55.6</v>
+        <v>66.7</v>
       </c>
       <c r="Q591" t="n">
-        <v>91.36</v>
+        <v>93.83</v>
       </c>
       <c r="R591" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S591" t="n">
         <v>9</v>
@@ -48818,13 +48822,13 @@
       </c>
       <c r="O594" t="inlineStr"/>
       <c r="P594" t="n">
-        <v>55.6</v>
+        <v>66.7</v>
       </c>
       <c r="Q594" t="n">
-        <v>91.36</v>
+        <v>93.83</v>
       </c>
       <c r="R594" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S594" t="n">
         <v>9</v>
@@ -49055,13 +49059,13 @@
       </c>
       <c r="O597" t="inlineStr"/>
       <c r="P597" t="n">
-        <v>91.40000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="Q597" t="n">
-        <v>91.36</v>
+        <v>93.83</v>
       </c>
       <c r="R597" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S597" t="n">
         <v>9</v>
@@ -67888,7 +67892,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>77.78</v>
+        <v>100</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -68818,7 +68822,7 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -68848,7 +68852,7 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -68878,7 +68882,7 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -68908,7 +68912,7 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -68968,7 +68972,7 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -68998,7 +69002,7 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -69028,7 +69032,7 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -69058,7 +69062,7 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -69088,7 +69092,7 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -69148,7 +69152,7 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -69178,7 +69182,7 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -69208,7 +69212,7 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -69238,7 +69242,7 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -69328,7 +69332,7 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -69358,7 +69362,7 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -69448,7 +69452,7 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -69478,7 +69482,7 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -69508,7 +69512,7 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -69538,7 +69542,7 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -69568,7 +69572,7 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -69598,7 +69602,7 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -69628,7 +69632,7 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -69658,7 +69662,7 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -69688,7 +69692,7 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -69718,7 +69722,7 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -69748,7 +69752,7 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -69778,7 +69782,7 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -69838,7 +69842,7 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -69898,7 +69902,7 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -69988,7 +69992,7 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -70018,7 +70022,7 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>24.07</v>
+        <v>31.48</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -70528,7 +70532,7 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>77.78</v>
+        <v>100</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -70692,7 +70696,7 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>77.78</v>
+        <v>88.89</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -74202,7 +74206,7 @@
         </is>
       </c>
       <c r="E295" t="n">
-        <v>25.93</v>
+        <v>33.33</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -74562,7 +74566,7 @@
         </is>
       </c>
       <c r="E307" t="n">
-        <v>100</v>
+        <v>88.89</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -78432,7 +78436,7 @@
         </is>
       </c>
       <c r="E436" t="n">
-        <v>25.93</v>
+        <v>33.33</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -78492,7 +78496,7 @@
         </is>
       </c>
       <c r="E438" t="n">
-        <v>25.93</v>
+        <v>33.33</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -78522,7 +78526,7 @@
         </is>
       </c>
       <c r="E439" t="n">
-        <v>25.93</v>
+        <v>33.33</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -78732,7 +78736,7 @@
         </is>
       </c>
       <c r="E446" t="n">
-        <v>25.93</v>
+        <v>33.33</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -78792,7 +78796,7 @@
         </is>
       </c>
       <c r="E448" t="n">
-        <v>25.93</v>
+        <v>33.33</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -79002,7 +79006,7 @@
         </is>
       </c>
       <c r="E455" t="n">
-        <v>88.89</v>
+        <v>100</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -80202,7 +80206,7 @@
         </is>
       </c>
       <c r="E495" t="n">
-        <v>88.89</v>
+        <v>100</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -83756,7 +83760,7 @@
       <c r="C614" t="inlineStr"/>
       <c r="D614" t="inlineStr">
         <is>
-          <t>Célula 43</t>
+          <t>Célula 44</t>
         </is>
       </c>
       <c r="E614" t="n">
